--- a/excel/斗鸡配置.xlsx
+++ b/excel/斗鸡配置.xlsx
@@ -2,22 +2,24 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R434beddaf44a4d1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字典" sheetId="2" r:id="R26c10150e2344258"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player" sheetId="3" r:id="R6aaa24a8d6ff46e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stage" sheetId="4" r:id="R099afda5a6614af1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemy" sheetId="6" r:id="R640f8a74765f44ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item" sheetId="7" r:id="Rdae7d7de7cec4ce6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set" sheetId="8" r:id="Rf1ba2553978c4499"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Part" sheetId="9" r:id="R274c3a08269d465e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reward" sheetId="10" r:id="R5bf02d8238e640aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Language" sheetId="11" r:id="Rf96bac313669491a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route" sheetId="5" r:id="Rc134954f6f0041ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danmaku" sheetId="12" r:id="R41a2728d36264c9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Map" sheetId="13" r:id="R24dc3a67404c4fe9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiText" sheetId="14" r:id="R62133d78698c41fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameRule" sheetId="15" r:id="R03c30d5d8054468f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DanmakuRule" sheetId="16" r:id="Reddbbb18c0c448df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R00c305d45ade4f58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字典" sheetId="2" r:id="R6fa48892677747cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player" sheetId="3" r:id="Ra7dcffa3bd534b0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stage" sheetId="4" r:id="R986c9350e78f40eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enemy" sheetId="6" r:id="Re8f1b9475ddb428a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item" sheetId="7" r:id="R38cdb9a815bd40cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Set" sheetId="8" r:id="Rc84c306841314e15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Part" sheetId="9" r:id="Re594694a602545c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reward" sheetId="10" r:id="Rc5e0fc45b0594d1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Language" sheetId="11" r:id="R9ca044d8149247c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Route" sheetId="5" r:id="R1a353631362149ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danmaku" sheetId="12" r:id="R45a6fa7d0ccf4919"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Map" sheetId="13" r:id="R734606e50a634ac6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UiText" sheetId="14" r:id="R5e906ae9b4ca43a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GameRule" sheetId="15" r:id="Rad4b2a3dd2d040dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DanmakuRule" sheetId="16" r:id="R3a5c9390b9ce4a47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Story" sheetId="17" r:id="R5ef6790f2d6745f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taunt" sheetId="18" r:id="Rbf1d406e6c50484c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -188,7 +190,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="17">
+  <x:fills count="20">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -223,6 +225,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFAFCFE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF214F75"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF0F5FA"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -337,7 +354,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="130">
+  <x:cellXfs count="138">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -740,6 +757,30 @@
     <x:xf numFmtId="0" fontId="9" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -993,7 +1034,7 @@
         <x:v>导出</x:v>
       </x:c>
       <x:c r="B3" s="119" t="str">
-        <x:v>双击同目录“导出配置.bat”，成功后回 Creator 刷新资源并预览。</x:v>
+        <x:v>在 Creator 配表面板修改并保存 Excel，再导出并刷新资源，重新预览游戏。</x:v>
       </x:c>
       <x:c r="C3" s="119" t="str"/>
       <x:c r="D3" s="119" t="str"/>
@@ -1128,21 +1169,33 @@
       <x:c r="C16" s="119" t="str"/>
       <x:c r="D16" s="119" t="str"/>
     </x:row>
-    <x:row r="17" ht="28" customHeight="1">
-      <x:c r="A17"/>
-      <x:c r="B17"/>
+    <x:row r="17" ht="60" customHeight="1">
+      <x:c r="A17" s="119" t="str">
+        <x:v>剧情</x:v>
+      </x:c>
+      <x:c r="B17" s="119" t="str">
+        <x:v>Story 每行一段剧情；intro 为开场，ending 为结局。Map.storyId 指定地图剧情，Route.storyId 可覆盖。</x:v>
+      </x:c>
       <x:c r="C17"/>
       <x:c r="D17"/>
     </x:row>
-    <x:row r="18" ht="28" customHeight="1">
-      <x:c r="A18"/>
-      <x:c r="B18"/>
+    <x:row r="18" ht="60" customHeight="1">
+      <x:c r="A18" s="119" t="str">
+        <x:v>台词</x:v>
+      </x:c>
+      <x:c r="B18" s="119" t="str">
+        <x:v>Taunt 每行一句，按 group 分组、order 排序；Player 和 Enemy 通过 tauntGroup 引用，可增删台词。</x:v>
+      </x:c>
       <x:c r="C18"/>
       <x:c r="D18"/>
     </x:row>
-    <x:row r="19" ht="28" customHeight="1">
-      <x:c r="A19"/>
-      <x:c r="B19"/>
+    <x:row r="19" ht="60" customHeight="1">
+      <x:c r="A19" s="119" t="str">
+        <x:v>角色与路线</x:v>
+      </x:c>
+      <x:c r="B19" s="119" t="str">
+        <x:v>Player 仅维护玩家初始配置。最终敌人和奖励统一配置在 Route，剧情与台词在各自表中维护。</x:v>
+      </x:c>
       <x:c r="C19"/>
       <x:c r="D19"/>
     </x:row>
@@ -2443,166 +2496,182 @@
   <x:cols>
     <x:col min="1" max="7" width="22" customWidth="1"/>
     <x:col min="1" max="1" width="29" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="35" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="54" customHeight="1">
-      <x:c r="A1" s="121" t="str">
+      <x:c r="A1" s="132" t="str">
         <x:v>编号</x:v>
       </x:c>
-      <x:c r="B1" s="121" t="str">
+      <x:c r="B1" s="132" t="str">
         <x:v>地图编号</x:v>
       </x:c>
-      <x:c r="C1" s="121" t="str">
+      <x:c r="C1" s="132" t="str">
         <x:v>节点类型</x:v>
       </x:c>
-      <x:c r="D1" s="121" t="str">
+      <x:c r="D1" s="132" t="str">
         <x:v>节点名</x:v>
       </x:c>
-      <x:c r="E1" s="121" t="str">
+      <x:c r="E1" s="132" t="str">
         <x:v>敌人id</x:v>
       </x:c>
-      <x:c r="F1" s="121" t="str">
+      <x:c r="F1" s="132" t="str">
         <x:v>胜利金币</x:v>
       </x:c>
-      <x:c r="G1" s="121" t="str">
+      <x:c r="G1" s="132" t="str">
         <x:v>失败金币</x:v>
       </x:c>
-      <x:c r="H1" s="121" t="str">
+      <x:c r="H1" s="132" t="str">
         <x:v>比赛类型 warmup/official/final</x:v>
       </x:c>
-      <x:c r="I1" s="121" t="str">
+      <x:c r="I1" s="132" t="str">
         <x:v>战后打开商店</x:v>
       </x:c>
+      <x:c r="J1" s="132" t="str">
+        <x:v>剧情覆盖ID（空=地图剧情）</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
-      <x:c r="A2" s="122" t="str">
+      <x:c r="A2" s="135" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="B2" s="122" t="str">
+      <x:c r="B2" s="135" t="str">
         <x:v>mapId</x:v>
       </x:c>
-      <x:c r="C2" s="122" t="str">
+      <x:c r="C2" s="135" t="str">
         <x:v>kind</x:v>
       </x:c>
-      <x:c r="D2" s="122" t="str">
+      <x:c r="D2" s="135" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="E2" s="122" t="str">
+      <x:c r="E2" s="135" t="str">
         <x:v>enemyId</x:v>
       </x:c>
-      <x:c r="F2" s="122" t="str">
+      <x:c r="F2" s="135" t="str">
         <x:v>goldWin</x:v>
       </x:c>
-      <x:c r="G2" s="122" t="str">
+      <x:c r="G2" s="135" t="str">
         <x:v>goldLose</x:v>
       </x:c>
-      <x:c r="H2" s="122" t="str">
+      <x:c r="H2" s="135" t="str">
         <x:v>encounter</x:v>
       </x:c>
-      <x:c r="I2" s="122" t="str">
+      <x:c r="I2" s="135" t="str">
         <x:v>shopAfter</x:v>
       </x:c>
+      <x:c r="J2" s="135" t="str">
+        <x:v>storyId</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="124" t="str">
+      <x:c r="A3" s="137" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="B3" s="124" t="str">
+      <x:c r="B3" s="137" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="C3" s="124" t="str">
+      <x:c r="C3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D3" s="124" t="str">
+      <x:c r="D3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="E3" s="124" t="str">
+      <x:c r="E3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="F3" s="124" t="str">
+      <x:c r="F3" s="137" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="G3" s="124" t="str">
+      <x:c r="G3" s="137" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="H3" s="124" t="str">
+      <x:c r="H3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="I3" s="124" t="str">
+      <x:c r="I3" s="137" t="str">
         <x:v>bool</x:v>
       </x:c>
+      <x:c r="J3" s="137" t="str">
+        <x:v>string</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="124" t="str">
+      <x:c r="A4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="B4" s="124" t="str">
+      <x:c r="B4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="C4" s="124" t="str">
+      <x:c r="C4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="D4" s="124" t="str">
+      <x:c r="D4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="E4" s="124" t="str">
+      <x:c r="E4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="F4" s="124" t="str">
+      <x:c r="F4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="G4" s="124" t="str">
+      <x:c r="G4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="H4" s="124" t="str">
+      <x:c r="H4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="I4" s="124" t="str">
+      <x:c r="I4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
+      <x:c r="J4" s="137" t="str">
+        <x:v>server_no</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="124" t="str">
+      <x:c r="A5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="B5" s="124" t="str">
+      <x:c r="B5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="C5" s="124" t="str">
+      <x:c r="C5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="D5" s="124" t="str">
+      <x:c r="D5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="E5" s="124" t="str">
+      <x:c r="E5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="F5" s="124" t="str">
+      <x:c r="F5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="G5" s="124" t="str">
+      <x:c r="G5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="H5" s="124" t="str">
+      <x:c r="H5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="I5" s="124" t="str">
+      <x:c r="I5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="J5" s="137" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="67" t="n">
+      <x:c r="A6" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B6" s="67" t="n">
+      <x:c r="B6" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="37" t="str">
@@ -2614,10 +2683,10 @@
       <x:c r="E6" s="37" t="str">
         <x:v>s1_warmup_1</x:v>
       </x:c>
-      <x:c r="F6" s="67" t="n">
+      <x:c r="F6" s="37" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G6" s="67" t="n">
+      <x:c r="G6" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H6" s="37" t="str">
@@ -2626,12 +2695,13 @@
       <x:c r="I6" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J6" s="37" t="str"/>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="67" t="n">
+      <x:c r="A7" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="67" t="n">
+      <x:c r="B7" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C7" s="37" t="str">
@@ -2643,10 +2713,10 @@
       <x:c r="E7" s="37" t="str">
         <x:v>s1_warmup_2</x:v>
       </x:c>
-      <x:c r="F7" s="67" t="n">
+      <x:c r="F7" s="37" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G7" s="67" t="n">
+      <x:c r="G7" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H7" s="37" t="str">
@@ -2655,12 +2725,13 @@
       <x:c r="I7" s="91" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J7" s="37" t="str"/>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="67" t="n">
+      <x:c r="A8" s="37" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B8" s="67" t="n">
+      <x:c r="B8" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C8" s="37" t="str">
@@ -2672,10 +2743,10 @@
       <x:c r="E8" s="37" t="str">
         <x:v>s1_warmup_3</x:v>
       </x:c>
-      <x:c r="F8" s="67" t="n">
+      <x:c r="F8" s="37" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G8" s="67" t="n">
+      <x:c r="G8" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="37" t="str">
@@ -2684,12 +2755,13 @@
       <x:c r="I8" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J8" s="37" t="str"/>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="67" t="n">
+      <x:c r="A9" s="37" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B9" s="67" t="n">
+      <x:c r="B9" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C9" s="37" t="str">
@@ -2701,10 +2773,10 @@
       <x:c r="E9" s="37" t="str">
         <x:v>s1_warmup_4</x:v>
       </x:c>
-      <x:c r="F9" s="67" t="n">
+      <x:c r="F9" s="37" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G9" s="67" t="n">
+      <x:c r="G9" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="37" t="str">
@@ -2713,12 +2785,13 @@
       <x:c r="I9" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J9" s="37" t="str"/>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="67" t="n">
+      <x:c r="A10" s="37" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B10" s="67" t="n">
+      <x:c r="B10" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="37" t="str">
@@ -2730,10 +2803,10 @@
       <x:c r="E10" s="37" t="str">
         <x:v>s1_warmup_5</x:v>
       </x:c>
-      <x:c r="F10" s="67" t="n">
+      <x:c r="F10" s="37" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G10" s="67" t="n">
+      <x:c r="G10" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H10" s="37" t="str">
@@ -2742,12 +2815,13 @@
       <x:c r="I10" s="91" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J10" s="37" t="str"/>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="67" t="n">
+      <x:c r="A11" s="37" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B11" s="67" t="n">
+      <x:c r="B11" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C11" s="37" t="str">
@@ -2759,10 +2833,10 @@
       <x:c r="E11" s="37" t="str">
         <x:v>s1_official</x:v>
       </x:c>
-      <x:c r="F11" s="67" t="n">
+      <x:c r="F11" s="37" t="n">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="G11" s="67" t="n">
+      <x:c r="G11" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H11" s="37" t="str">
@@ -2771,12 +2845,13 @@
       <x:c r="I11" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J11" s="37" t="str"/>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="67" t="n">
+      <x:c r="A12" s="37" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B12" s="67" t="n">
+      <x:c r="B12" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C12" s="37" t="str">
@@ -2788,10 +2863,10 @@
       <x:c r="E12" s="37" t="str">
         <x:v>s2_warmup_1</x:v>
       </x:c>
-      <x:c r="F12" s="67" t="n">
+      <x:c r="F12" s="37" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G12" s="67" t="n">
+      <x:c r="G12" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="37" t="str">
@@ -2800,12 +2875,13 @@
       <x:c r="I12" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J12" s="37" t="str"/>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="67" t="n">
+      <x:c r="A13" s="37" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B13" s="67" t="n">
+      <x:c r="B13" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C13" s="37" t="str">
@@ -2817,10 +2893,10 @@
       <x:c r="E13" s="37" t="str">
         <x:v>s2_warmup_2</x:v>
       </x:c>
-      <x:c r="F13" s="67" t="n">
+      <x:c r="F13" s="37" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G13" s="67" t="n">
+      <x:c r="G13" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H13" s="37" t="str">
@@ -2829,12 +2905,13 @@
       <x:c r="I13" s="91" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J13" s="37" t="str"/>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
-      <x:c r="A14" s="67" t="n">
+      <x:c r="A14" s="37" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B14" s="67" t="n">
+      <x:c r="B14" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C14" s="37" t="str">
@@ -2846,10 +2923,10 @@
       <x:c r="E14" s="37" t="str">
         <x:v>s2_warmup_3</x:v>
       </x:c>
-      <x:c r="F14" s="67" t="n">
+      <x:c r="F14" s="37" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G14" s="67" t="n">
+      <x:c r="G14" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H14" s="37" t="str">
@@ -2858,12 +2935,13 @@
       <x:c r="I14" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J14" s="37" t="str"/>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="67" t="n">
+      <x:c r="A15" s="37" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B15" s="67" t="n">
+      <x:c r="B15" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C15" s="37" t="str">
@@ -2875,10 +2953,10 @@
       <x:c r="E15" s="37" t="str">
         <x:v>s2_warmup_4</x:v>
       </x:c>
-      <x:c r="F15" s="67" t="n">
+      <x:c r="F15" s="37" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G15" s="67" t="n">
+      <x:c r="G15" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H15" s="37" t="str">
@@ -2887,12 +2965,13 @@
       <x:c r="I15" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J15" s="37" t="str"/>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
-      <x:c r="A16" s="67" t="n">
+      <x:c r="A16" s="37" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B16" s="67" t="n">
+      <x:c r="B16" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C16" s="37" t="str">
@@ -2904,10 +2983,10 @@
       <x:c r="E16" s="37" t="str">
         <x:v>s2_warmup_5</x:v>
       </x:c>
-      <x:c r="F16" s="67" t="n">
+      <x:c r="F16" s="37" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G16" s="67" t="n">
+      <x:c r="G16" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H16" s="37" t="str">
@@ -2916,12 +2995,13 @@
       <x:c r="I16" s="91" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J16" s="37" t="str"/>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
-      <x:c r="A17" s="67" t="n">
+      <x:c r="A17" s="37" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B17" s="67" t="n">
+      <x:c r="B17" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C17" s="37" t="str">
@@ -2933,10 +3013,10 @@
       <x:c r="E17" s="37" t="str">
         <x:v>s2_official</x:v>
       </x:c>
-      <x:c r="F17" s="67" t="n">
+      <x:c r="F17" s="37" t="n">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="G17" s="67" t="n">
+      <x:c r="G17" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H17" s="37" t="str">
@@ -2945,12 +3025,13 @@
       <x:c r="I17" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J17" s="37" t="str"/>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
-      <x:c r="A18" s="67" t="n">
+      <x:c r="A18" s="37" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B18" s="67" t="n">
+      <x:c r="B18" s="37" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C18" s="37" t="str">
@@ -2962,10 +3043,10 @@
       <x:c r="E18" s="37" t="str">
         <x:v>s3_warmup_1</x:v>
       </x:c>
-      <x:c r="F18" s="67" t="n">
+      <x:c r="F18" s="37" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G18" s="67" t="n">
+      <x:c r="G18" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H18" s="37" t="str">
@@ -2974,12 +3055,13 @@
       <x:c r="I18" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J18" s="37" t="str"/>
     </x:row>
     <x:row r="19" ht="30" customHeight="1">
-      <x:c r="A19" s="67" t="n">
+      <x:c r="A19" s="37" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B19" s="67" t="n">
+      <x:c r="B19" s="37" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C19" s="37" t="str">
@@ -2991,10 +3073,10 @@
       <x:c r="E19" s="37" t="str">
         <x:v>s3_warmup_2</x:v>
       </x:c>
-      <x:c r="F19" s="67" t="n">
+      <x:c r="F19" s="37" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G19" s="67" t="n">
+      <x:c r="G19" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H19" s="37" t="str">
@@ -3003,12 +3085,13 @@
       <x:c r="I19" s="91" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J19" s="37" t="str"/>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
-      <x:c r="A20" s="67" t="n">
+      <x:c r="A20" s="37" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B20" s="67" t="n">
+      <x:c r="B20" s="37" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C20" s="37" t="str">
@@ -3020,10 +3103,10 @@
       <x:c r="E20" s="37" t="str">
         <x:v>s3_warmup_3</x:v>
       </x:c>
-      <x:c r="F20" s="67" t="n">
+      <x:c r="F20" s="37" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G20" s="67" t="n">
+      <x:c r="G20" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H20" s="37" t="str">
@@ -3032,12 +3115,13 @@
       <x:c r="I20" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J20" s="37" t="str"/>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
-      <x:c r="A21" s="67" t="n">
+      <x:c r="A21" s="37" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B21" s="67" t="n">
+      <x:c r="B21" s="37" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C21" s="37" t="str">
@@ -3049,10 +3133,10 @@
       <x:c r="E21" s="37" t="str">
         <x:v>s3_warmup_4</x:v>
       </x:c>
-      <x:c r="F21" s="67" t="n">
+      <x:c r="F21" s="37" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G21" s="67" t="n">
+      <x:c r="G21" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H21" s="37" t="str">
@@ -3061,12 +3145,13 @@
       <x:c r="I21" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J21" s="37" t="str"/>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
-      <x:c r="A22" s="67" t="n">
+      <x:c r="A22" s="37" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B22" s="67" t="n">
+      <x:c r="B22" s="37" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C22" s="37" t="str">
@@ -3078,10 +3163,10 @@
       <x:c r="E22" s="37" t="str">
         <x:v>s3_warmup_5</x:v>
       </x:c>
-      <x:c r="F22" s="67" t="n">
+      <x:c r="F22" s="37" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G22" s="67" t="n">
+      <x:c r="G22" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H22" s="37" t="str">
@@ -3090,12 +3175,13 @@
       <x:c r="I22" s="91" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J22" s="37" t="str"/>
     </x:row>
     <x:row r="23" ht="30" customHeight="1">
-      <x:c r="A23" s="67" t="n">
+      <x:c r="A23" s="37" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B23" s="67" t="n">
+      <x:c r="B23" s="37" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C23" s="37" t="str">
@@ -3107,10 +3193,10 @@
       <x:c r="E23" s="37" t="str">
         <x:v>s3_official</x:v>
       </x:c>
-      <x:c r="F23" s="67" t="n">
+      <x:c r="F23" s="37" t="n">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="G23" s="67" t="n">
+      <x:c r="G23" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H23" s="37" t="str">
@@ -3119,12 +3205,13 @@
       <x:c r="I23" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J23" s="37" t="str"/>
     </x:row>
     <x:row r="24" ht="30" customHeight="1">
-      <x:c r="A24" s="67" t="n">
+      <x:c r="A24" s="37" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B24" s="67" t="n">
+      <x:c r="B24" s="37" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C24" s="37" t="str">
@@ -3136,10 +3223,10 @@
       <x:c r="E24" s="37" t="str">
         <x:v>s4_warmup_1</x:v>
       </x:c>
-      <x:c r="F24" s="67" t="n">
+      <x:c r="F24" s="37" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G24" s="67" t="n">
+      <x:c r="G24" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H24" s="37" t="str">
@@ -3148,12 +3235,13 @@
       <x:c r="I24" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J24" s="37" t="str"/>
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
-      <x:c r="A25" s="67" t="n">
+      <x:c r="A25" s="37" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B25" s="67" t="n">
+      <x:c r="B25" s="37" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C25" s="37" t="str">
@@ -3165,10 +3253,10 @@
       <x:c r="E25" s="37" t="str">
         <x:v>s4_warmup_2</x:v>
       </x:c>
-      <x:c r="F25" s="67" t="n">
+      <x:c r="F25" s="37" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G25" s="67" t="n">
+      <x:c r="G25" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H25" s="37" t="str">
@@ -3177,12 +3265,13 @@
       <x:c r="I25" s="91" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J25" s="37" t="str"/>
     </x:row>
     <x:row r="26" ht="30" customHeight="1">
-      <x:c r="A26" s="67" t="n">
+      <x:c r="A26" s="37" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B26" s="67" t="n">
+      <x:c r="B26" s="37" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C26" s="37" t="str">
@@ -3194,10 +3283,10 @@
       <x:c r="E26" s="37" t="str">
         <x:v>s4_warmup_3</x:v>
       </x:c>
-      <x:c r="F26" s="67" t="n">
+      <x:c r="F26" s="37" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G26" s="67" t="n">
+      <x:c r="G26" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H26" s="37" t="str">
@@ -3206,12 +3295,13 @@
       <x:c r="I26" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J26" s="37" t="str"/>
     </x:row>
     <x:row r="27" ht="30" customHeight="1">
-      <x:c r="A27" s="67" t="n">
+      <x:c r="A27" s="37" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B27" s="67" t="n">
+      <x:c r="B27" s="37" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C27" s="37" t="str">
@@ -3223,10 +3313,10 @@
       <x:c r="E27" s="37" t="str">
         <x:v>s4_warmup_4</x:v>
       </x:c>
-      <x:c r="F27" s="67" t="n">
+      <x:c r="F27" s="37" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G27" s="67" t="n">
+      <x:c r="G27" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H27" s="37" t="str">
@@ -3235,12 +3325,13 @@
       <x:c r="I27" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J27" s="37" t="str"/>
     </x:row>
     <x:row r="28" ht="30" customHeight="1">
-      <x:c r="A28" s="67" t="n">
+      <x:c r="A28" s="37" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B28" s="67" t="n">
+      <x:c r="B28" s="37" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C28" s="37" t="str">
@@ -3252,10 +3343,10 @@
       <x:c r="E28" s="37" t="str">
         <x:v>s4_warmup_5</x:v>
       </x:c>
-      <x:c r="F28" s="67" t="n">
+      <x:c r="F28" s="37" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G28" s="67" t="n">
+      <x:c r="G28" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H28" s="37" t="str">
@@ -3264,12 +3355,13 @@
       <x:c r="I28" s="91" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J28" s="37" t="str"/>
     </x:row>
     <x:row r="29" ht="30" customHeight="1">
-      <x:c r="A29" s="67" t="n">
+      <x:c r="A29" s="37" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B29" s="67" t="n">
+      <x:c r="B29" s="37" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C29" s="37" t="str">
@@ -3281,10 +3373,10 @@
       <x:c r="E29" s="37" t="str">
         <x:v>s4_official</x:v>
       </x:c>
-      <x:c r="F29" s="67" t="n">
+      <x:c r="F29" s="37" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="G29" s="67" t="n">
+      <x:c r="G29" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H29" s="37" t="str">
@@ -3293,12 +3385,13 @@
       <x:c r="I29" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J29" s="37" t="str"/>
     </x:row>
     <x:row r="30" ht="30" customHeight="1">
-      <x:c r="A30" s="67" t="n">
+      <x:c r="A30" s="37" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B30" s="67" t="n">
+      <x:c r="B30" s="37" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C30" s="37" t="str">
@@ -3310,10 +3403,10 @@
       <x:c r="E30" s="37" t="str">
         <x:v>s5_warmup_1</x:v>
       </x:c>
-      <x:c r="F30" s="67" t="n">
+      <x:c r="F30" s="37" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G30" s="67" t="n">
+      <x:c r="G30" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H30" s="37" t="str">
@@ -3322,12 +3415,13 @@
       <x:c r="I30" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J30" s="37" t="str"/>
     </x:row>
     <x:row r="31" ht="30" customHeight="1">
-      <x:c r="A31" s="67" t="n">
+      <x:c r="A31" s="37" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B31" s="67" t="n">
+      <x:c r="B31" s="37" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C31" s="37" t="str">
@@ -3339,10 +3433,10 @@
       <x:c r="E31" s="37" t="str">
         <x:v>s5_warmup_2</x:v>
       </x:c>
-      <x:c r="F31" s="67" t="n">
+      <x:c r="F31" s="37" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G31" s="67" t="n">
+      <x:c r="G31" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H31" s="37" t="str">
@@ -3351,12 +3445,13 @@
       <x:c r="I31" s="91" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J31" s="37" t="str"/>
     </x:row>
     <x:row r="32" ht="30" customHeight="1">
-      <x:c r="A32" s="67" t="n">
+      <x:c r="A32" s="37" t="n">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B32" s="67" t="n">
+      <x:c r="B32" s="37" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C32" s="37" t="str">
@@ -3368,10 +3463,10 @@
       <x:c r="E32" s="37" t="str">
         <x:v>s5_warmup_3</x:v>
       </x:c>
-      <x:c r="F32" s="67" t="n">
+      <x:c r="F32" s="37" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G32" s="67" t="n">
+      <x:c r="G32" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H32" s="37" t="str">
@@ -3380,12 +3475,13 @@
       <x:c r="I32" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J32" s="37" t="str"/>
     </x:row>
     <x:row r="33" ht="30" customHeight="1">
-      <x:c r="A33" s="67" t="n">
+      <x:c r="A33" s="37" t="n">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B33" s="67" t="n">
+      <x:c r="B33" s="37" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C33" s="37" t="str">
@@ -3397,10 +3493,10 @@
       <x:c r="E33" s="37" t="str">
         <x:v>s5_warmup_4</x:v>
       </x:c>
-      <x:c r="F33" s="67" t="n">
+      <x:c r="F33" s="37" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G33" s="67" t="n">
+      <x:c r="G33" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H33" s="37" t="str">
@@ -3409,12 +3505,13 @@
       <x:c r="I33" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J33" s="37" t="str"/>
     </x:row>
     <x:row r="34" ht="30" customHeight="1">
-      <x:c r="A34" s="67" t="n">
+      <x:c r="A34" s="37" t="n">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B34" s="67" t="n">
+      <x:c r="B34" s="37" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C34" s="37" t="str">
@@ -3426,10 +3523,10 @@
       <x:c r="E34" s="37" t="str">
         <x:v>s5_warmup_5</x:v>
       </x:c>
-      <x:c r="F34" s="67" t="n">
+      <x:c r="F34" s="37" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G34" s="67" t="n">
+      <x:c r="G34" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H34" s="37" t="str">
@@ -3438,12 +3535,13 @@
       <x:c r="I34" s="91" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J34" s="37" t="str"/>
     </x:row>
     <x:row r="35" ht="30" customHeight="1">
-      <x:c r="A35" s="67" t="n">
+      <x:c r="A35" s="37" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B35" s="67" t="n">
+      <x:c r="B35" s="37" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C35" s="37" t="str">
@@ -3455,10 +3553,10 @@
       <x:c r="E35" s="37" t="str">
         <x:v>s5_official</x:v>
       </x:c>
-      <x:c r="F35" s="67" t="n">
+      <x:c r="F35" s="37" t="n">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="G35" s="67" t="n">
+      <x:c r="G35" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H35" s="37" t="str">
@@ -3467,12 +3565,13 @@
       <x:c r="I35" s="91" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="J35" s="37" t="str"/>
     </x:row>
     <x:row r="36" ht="30" customHeight="1">
-      <x:c r="A36" s="67" t="n">
+      <x:c r="A36" s="37" t="n">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="B36" s="67" t="n">
+      <x:c r="B36" s="37" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C36" s="37" t="str">
@@ -3484,16 +3583,19 @@
       <x:c r="E36" s="37" t="str">
         <x:v>kun_boss</x:v>
       </x:c>
-      <x:c r="F36" s="67" t="n">
+      <x:c r="F36" s="37" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="G36" s="67" t="n">
+      <x:c r="G36" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H36" s="37" t="str">
         <x:v>final</x:v>
       </x:c>
       <x:c r="I36" s="37"/>
+      <x:c r="J36" s="37" t="str">
+        <x:v>boss</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5609,99 +5711,115 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="29" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="55" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="55" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="54" customHeight="1">
-      <x:c r="A1" s="121" t="str">
+      <x:c r="A1" s="132" t="str">
         <x:v>编号</x:v>
       </x:c>
-      <x:c r="B1" s="121" t="str">
+      <x:c r="B1" s="132" t="str">
         <x:v>地图名称</x:v>
       </x:c>
-      <x:c r="C1" s="121" t="str">
+      <x:c r="C1" s="132" t="str">
         <x:v>背景资源名</x:v>
       </x:c>
-      <x:c r="D1" s="121" t="str">
+      <x:c r="D1" s="132" t="str">
         <x:v>商店坐标及缩放（JSON）</x:v>
       </x:c>
-      <x:c r="E1" s="121" t="str">
+      <x:c r="E1" s="132" t="str">
         <x:v>关卡坐标（JSON数组）</x:v>
       </x:c>
+      <x:c r="F1" s="132" t="str">
+        <x:v>地图剧情ID</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
-      <x:c r="A2" s="122" t="str">
+      <x:c r="A2" s="135" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="B2" s="122" t="str">
+      <x:c r="B2" s="135" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="C2" s="122" t="str">
+      <x:c r="C2" s="135" t="str">
         <x:v>background</x:v>
       </x:c>
-      <x:c r="D2" s="122" t="str">
+      <x:c r="D2" s="135" t="str">
         <x:v>shop</x:v>
       </x:c>
-      <x:c r="E2" s="122" t="str">
+      <x:c r="E2" s="135" t="str">
         <x:v>entrances</x:v>
       </x:c>
+      <x:c r="F2" s="135" t="str">
+        <x:v>storyId</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="124" t="str">
+      <x:c r="A3" s="137" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="B3" s="124" t="str">
+      <x:c r="B3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C3" s="124" t="str">
+      <x:c r="C3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D3" s="124" t="str">
+      <x:c r="D3" s="137" t="str">
         <x:v>any</x:v>
       </x:c>
-      <x:c r="E3" s="124" t="str">
+      <x:c r="E3" s="137" t="str">
         <x:v>any</x:v>
       </x:c>
+      <x:c r="F3" s="137" t="str">
+        <x:v>string</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="124" t="str">
+      <x:c r="A4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="B4" s="124" t="str">
+      <x:c r="B4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="C4" s="124" t="str">
+      <x:c r="C4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="D4" s="124" t="str">
+      <x:c r="D4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="E4" s="124" t="str">
+      <x:c r="E4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
+      <x:c r="F4" s="137" t="str">
+        <x:v>server_no</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="124" t="str">
+      <x:c r="A5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="B5" s="124" t="str">
+      <x:c r="B5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="C5" s="124" t="str">
+      <x:c r="C5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="D5" s="124" t="str">
+      <x:c r="D5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="E5" s="124" t="str">
+      <x:c r="E5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="F5" s="137" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="67" t="n">
+      <x:c r="A6" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="37" t="str">
@@ -5716,9 +5834,12 @@
       <x:c r="E6" s="37" t="str">
         <x:v>[[0.583,0.867],[0.569,0.742],[0.479,0.617],[0.583,0.492],[0.493,0.375],[0.34,0.25]]</x:v>
       </x:c>
+      <x:c r="F6" s="37" t="str">
+        <x:v>map_1</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="67" t="n">
+      <x:c r="A7" s="37" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="37" t="str">
@@ -5733,9 +5854,12 @@
       <x:c r="E7" s="37" t="str">
         <x:v>[[0.549,0.867],[0.542,0.742],[0.493,0.617],[0.611,0.492],[0.431,0.375],[0.417,0.25]]</x:v>
       </x:c>
+      <x:c r="F7" s="37" t="str">
+        <x:v>map_2</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="67" t="n">
+      <x:c r="A8" s="37" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="37" t="str">
@@ -5750,9 +5874,12 @@
       <x:c r="E8" s="37" t="str">
         <x:v>[[0.451,0.867],[0.458,0.742],[0.486,0.617],[0.556,0.492],[0.486,0.375],[0.36,0.25]]</x:v>
       </x:c>
+      <x:c r="F8" s="37" t="str">
+        <x:v>map_3</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="67" t="n">
+      <x:c r="A9" s="37" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="37" t="str">
@@ -5767,9 +5894,12 @@
       <x:c r="E9" s="37" t="str">
         <x:v>[[0.438,0.867],[0.549,0.758],[0.486,0.645],[0.493,0.531],[0.458,0.418],[0.45,0.295]]</x:v>
       </x:c>
+      <x:c r="F9" s="37" t="str">
+        <x:v>map_4</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="67" t="n">
+      <x:c r="A10" s="37" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="37" t="str">
@@ -5783,6 +5913,9 @@
       </x:c>
       <x:c r="E10" s="37" t="str">
         <x:v>[[0.569,0.867],[0.583,0.746],[0.458,0.633],[0.625,0.52],[0.417,0.406],[0.52,0.28]]</x:v>
+      </x:c>
+      <x:c r="F10" s="37" t="str">
+        <x:v>map_5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7385,6 +7518,1762 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="29" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="100" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="54" customHeight="1">
+      <x:c r="A1" s="132" t="str">
+        <x:v>剧情ID</x:v>
+      </x:c>
+      <x:c r="B1" s="132" t="str">
+        <x:v>剧情正文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="38" customHeight="1">
+      <x:c r="A2" s="135" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B2" s="135" t="str">
+        <x:v>text</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="137" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="B3" s="137" t="str">
+        <x:v>string</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="137" t="str">
+        <x:v>server_no</x:v>
+      </x:c>
+      <x:c r="B4" s="137" t="str">
+        <x:v>server_no</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="137" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="B5" s="137" t="str">
+        <x:v>client</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="90" customHeight="1">
+      <x:c r="A6" s="37" t="str">
+        <x:v>intro</x:v>
+      </x:c>
+      <x:c r="B6" s="37" t="str">
+        <x:v>鸡鸣村的争霸赛开始了。无名的你，将用比赛、装备与成长，赢得全村的认可。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="90" customHeight="1">
+      <x:c r="A7" s="37" t="str">
+        <x:v>ending</x:v>
+      </x:c>
+      <x:c r="B7" s="37" t="str">
+        <x:v>全村见证新鸡王诞生。争霸赛年年有，挑战永不休。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="90" customHeight="1">
+      <x:c r="A8" s="37" t="str">
+        <x:v>boss</x:v>
+      </x:c>
+      <x:c r="B8" s="37" t="str">
+        <x:v>五图赛程已毕，鸡王坤坤在全村注视下等你。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="90" customHeight="1">
+      <x:c r="A9" s="37" t="str">
+        <x:v>map_1</x:v>
+      </x:c>
+      <x:c r="B9" s="37" t="str">
+        <x:v>村民还在笑：这只无名鸡，也想争王？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="90" customHeight="1">
+      <x:c r="A10" s="37" t="str">
+        <x:v>map_2</x:v>
+      </x:c>
+      <x:c r="B10" s="37" t="str">
+        <x:v>围观的鸡群渐渐安静，开始认真看你的比赛。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="90" customHeight="1">
+      <x:c r="A11" s="37" t="str">
+        <x:v>map_3</x:v>
+      </x:c>
+      <x:c r="B11" s="37" t="str">
+        <x:v>有人开始为你喝彩：无名鸡，继续冲！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="90" customHeight="1">
+      <x:c r="A12" s="37" t="str">
+        <x:v>map_4</x:v>
+      </x:c>
+      <x:c r="B12" s="37" t="str">
+        <x:v>全村都在期待，你能走到多远。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="90" customHeight="1">
+      <x:c r="A13" s="37" t="str">
+        <x:v>map_5</x:v>
+      </x:c>
+      <x:c r="B13" s="37" t="str">
+        <x:v>走完最后的赛程，在全村注视下挑战坤坤。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="29" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="100" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="54" customHeight="1">
+      <x:c r="A1" s="132" t="str">
+        <x:v>台词ID</x:v>
+      </x:c>
+      <x:c r="B1" s="132" t="str">
+        <x:v>台词组ID</x:v>
+      </x:c>
+      <x:c r="C1" s="132" t="str">
+        <x:v>组内顺序</x:v>
+      </x:c>
+      <x:c r="D1" s="132" t="str">
+        <x:v>台词正文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="38" customHeight="1">
+      <x:c r="A2" s="135" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B2" s="135" t="str">
+        <x:v>group</x:v>
+      </x:c>
+      <x:c r="C2" s="135" t="str">
+        <x:v>order</x:v>
+      </x:c>
+      <x:c r="D2" s="135" t="str">
+        <x:v>text</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="137" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="B3" s="137" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="C3" s="137" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="D3" s="137" t="str">
+        <x:v>string</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="137" t="str">
+        <x:v>server_no</x:v>
+      </x:c>
+      <x:c r="B4" s="137" t="str">
+        <x:v>server_no</x:v>
+      </x:c>
+      <x:c r="C4" s="137" t="str">
+        <x:v>server_no</x:v>
+      </x:c>
+      <x:c r="D4" s="137" t="str">
+        <x:v>server_no</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="137" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="B5" s="137" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="C5" s="137" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="D5" s="137" t="str">
+        <x:v>client</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="48" customHeight="1">
+      <x:c r="A6" s="37" t="str">
+        <x:v>player_1_1</x:v>
+      </x:c>
+      <x:c r="B6" s="37" t="str">
+        <x:v>player_1</x:v>
+      </x:c>
+      <x:c r="C6" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D6" s="37" t="str">
+        <x:v>今儿个让你见识村口一霸！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="48" customHeight="1">
+      <x:c r="A7" s="37" t="str">
+        <x:v>player_1_2</x:v>
+      </x:c>
+      <x:c r="B7" s="37" t="str">
+        <x:v>player_1</x:v>
+      </x:c>
+      <x:c r="C7" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="37" t="str">
+        <x:v>你这只鸡，看着就嫩。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="48" customHeight="1">
+      <x:c r="A8" s="37" t="str">
+        <x:v>player_1_3</x:v>
+      </x:c>
+      <x:c r="B8" s="37" t="str">
+        <x:v>player_1</x:v>
+      </x:c>
+      <x:c r="C8" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D8" s="37" t="str">
+        <x:v>热身都站不稳？正式赛更别来。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="48" customHeight="1">
+      <x:c r="A9" s="37" t="str">
+        <x:v>enemy_s1_warmup_1</x:v>
+      </x:c>
+      <x:c r="B9" s="37" t="str">
+        <x:v>enemy_s1_warmup</x:v>
+      </x:c>
+      <x:c r="C9" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D9" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="48" customHeight="1">
+      <x:c r="A10" s="37" t="str">
+        <x:v>enemy_s1_warmup_2</x:v>
+      </x:c>
+      <x:c r="B10" s="37" t="str">
+        <x:v>enemy_s1_warmup</x:v>
+      </x:c>
+      <x:c r="C10" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D10" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="48" customHeight="1">
+      <x:c r="A11" s="37" t="str">
+        <x:v>enemy_s1_warmup_3</x:v>
+      </x:c>
+      <x:c r="B11" s="37" t="str">
+        <x:v>enemy_s1_warmup</x:v>
+      </x:c>
+      <x:c r="C11" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D11" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="48" customHeight="1">
+      <x:c r="A12" s="37" t="str">
+        <x:v>enemy_s1_official_1</x:v>
+      </x:c>
+      <x:c r="B12" s="37" t="str">
+        <x:v>enemy_s1_official</x:v>
+      </x:c>
+      <x:c r="C12" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D12" s="37" t="str">
+        <x:v>我的战术目前只有勇气！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="48" customHeight="1">
+      <x:c r="A13" s="37" t="str">
+        <x:v>enemy_s1_official_2</x:v>
+      </x:c>
+      <x:c r="B13" s="37" t="str">
+        <x:v>enemy_s1_official</x:v>
+      </x:c>
+      <x:c r="C13" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D13" s="37" t="str">
+        <x:v>这鸡的装备比它本人有自信</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="48" customHeight="1">
+      <x:c r="A14" s="37" t="str">
+        <x:v>enemy_s1_official_3</x:v>
+      </x:c>
+      <x:c r="B14" s="37" t="str">
+        <x:v>enemy_s1_official</x:v>
+      </x:c>
+      <x:c r="C14" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D14" s="37" t="str">
+        <x:v>盾牌已经替它投降了</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="48" customHeight="1">
+      <x:c r="A15" s="37" t="str">
+        <x:v>enemy_s2_warmup_1</x:v>
+      </x:c>
+      <x:c r="B15" s="37" t="str">
+        <x:v>enemy_s2_warmup</x:v>
+      </x:c>
+      <x:c r="C15" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D15" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="48" customHeight="1">
+      <x:c r="A16" s="37" t="str">
+        <x:v>enemy_s2_warmup_2</x:v>
+      </x:c>
+      <x:c r="B16" s="37" t="str">
+        <x:v>enemy_s2_warmup</x:v>
+      </x:c>
+      <x:c r="C16" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D16" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="48" customHeight="1">
+      <x:c r="A17" s="37" t="str">
+        <x:v>enemy_s2_warmup_3</x:v>
+      </x:c>
+      <x:c r="B17" s="37" t="str">
+        <x:v>enemy_s2_warmup</x:v>
+      </x:c>
+      <x:c r="C17" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D17" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="48" customHeight="1">
+      <x:c r="A18" s="37" t="str">
+        <x:v>enemy_s2_official_1</x:v>
+      </x:c>
+      <x:c r="B18" s="37" t="str">
+        <x:v>enemy_s2_official</x:v>
+      </x:c>
+      <x:c r="C18" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D18" s="37" t="str">
+        <x:v>胜负不重要，火候很重要！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="48" customHeight="1">
+      <x:c r="A19" s="37" t="str">
+        <x:v>enemy_s2_official_2</x:v>
+      </x:c>
+      <x:c r="B19" s="37" t="str">
+        <x:v>enemy_s2_official</x:v>
+      </x:c>
+      <x:c r="C19" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D19" s="37" t="str">
+        <x:v>这鸡看起来已经腌入味了</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="48" customHeight="1">
+      <x:c r="A20" s="37" t="str">
+        <x:v>enemy_s2_official_3</x:v>
+      </x:c>
+      <x:c r="B20" s="37" t="str">
+        <x:v>enemy_s2_official</x:v>
+      </x:c>
+      <x:c r="C20" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D20" s="37" t="str">
+        <x:v>对面打轻点，别提前出锅</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="48" customHeight="1">
+      <x:c r="A21" s="37" t="str">
+        <x:v>enemy_s3_warmup_1</x:v>
+      </x:c>
+      <x:c r="B21" s="37" t="str">
+        <x:v>enemy_s3_warmup</x:v>
+      </x:c>
+      <x:c r="C21" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D21" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="48" customHeight="1">
+      <x:c r="A22" s="37" t="str">
+        <x:v>enemy_s3_warmup_2</x:v>
+      </x:c>
+      <x:c r="B22" s="37" t="str">
+        <x:v>enemy_s3_warmup</x:v>
+      </x:c>
+      <x:c r="C22" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D22" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="48" customHeight="1">
+      <x:c r="A23" s="37" t="str">
+        <x:v>enemy_s3_warmup_3</x:v>
+      </x:c>
+      <x:c r="B23" s="37" t="str">
+        <x:v>enemy_s3_warmup</x:v>
+      </x:c>
+      <x:c r="C23" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D23" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="48" customHeight="1">
+      <x:c r="A24" s="37" t="str">
+        <x:v>enemy_s3_official_1</x:v>
+      </x:c>
+      <x:c r="B24" s="37" t="str">
+        <x:v>enemy_s3_official</x:v>
+      </x:c>
+      <x:c r="C24" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D24" s="37" t="str">
+        <x:v>先喵再说！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="48" customHeight="1">
+      <x:c r="A25" s="37" t="str">
+        <x:v>enemy_s3_official_2</x:v>
+      </x:c>
+      <x:c r="B25" s="37" t="str">
+        <x:v>enemy_s3_official</x:v>
+      </x:c>
+      <x:c r="C25" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D25" s="37" t="str">
+        <x:v>这鸡怎么开始猫叫了</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="48" customHeight="1">
+      <x:c r="A26" s="37" t="str">
+        <x:v>enemy_s3_official_3</x:v>
+      </x:c>
+      <x:c r="B26" s="37" t="str">
+        <x:v>enemy_s3_official</x:v>
+      </x:c>
+      <x:c r="C26" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D26" s="37" t="str">
+        <x:v>可爱是可爱，物种有点复杂</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="48" customHeight="1">
+      <x:c r="A27" s="37" t="str">
+        <x:v>enemy_s4_warmup_1</x:v>
+      </x:c>
+      <x:c r="B27" s="37" t="str">
+        <x:v>enemy_s4_warmup</x:v>
+      </x:c>
+      <x:c r="C27" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D27" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="48" customHeight="1">
+      <x:c r="A28" s="37" t="str">
+        <x:v>enemy_s4_warmup_2</x:v>
+      </x:c>
+      <x:c r="B28" s="37" t="str">
+        <x:v>enemy_s4_warmup</x:v>
+      </x:c>
+      <x:c r="C28" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D28" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="48" customHeight="1">
+      <x:c r="A29" s="37" t="str">
+        <x:v>enemy_s4_warmup_3</x:v>
+      </x:c>
+      <x:c r="B29" s="37" t="str">
+        <x:v>enemy_s4_warmup</x:v>
+      </x:c>
+      <x:c r="C29" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D29" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="48" customHeight="1">
+      <x:c r="A30" s="37" t="str">
+        <x:v>enemy_s4_official_1</x:v>
+      </x:c>
+      <x:c r="B30" s="37" t="str">
+        <x:v>enemy_s4_official</x:v>
+      </x:c>
+      <x:c r="C30" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D30" s="37" t="str">
+        <x:v>真相只有一个！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="48" customHeight="1">
+      <x:c r="A31" s="37" t="str">
+        <x:v>enemy_s4_official_2</x:v>
+      </x:c>
+      <x:c r="B31" s="37" t="str">
+        <x:v>enemy_s4_official</x:v>
+      </x:c>
+      <x:c r="C31" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D31" s="37" t="str">
+        <x:v>这鸡已经推理出对面要挨打</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="48" customHeight="1">
+      <x:c r="A32" s="37" t="str">
+        <x:v>enemy_s4_official_3</x:v>
+      </x:c>
+      <x:c r="B32" s="37" t="str">
+        <x:v>enemy_s4_official</x:v>
+      </x:c>
+      <x:c r="C32" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D32" s="37" t="str">
+        <x:v>现场留下了三根鸡毛</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="48" customHeight="1">
+      <x:c r="A33" s="37" t="str">
+        <x:v>enemy_s5_warmup_1</x:v>
+      </x:c>
+      <x:c r="B33" s="37" t="str">
+        <x:v>enemy_s5_warmup</x:v>
+      </x:c>
+      <x:c r="C33" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D33" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="48" customHeight="1">
+      <x:c r="A34" s="37" t="str">
+        <x:v>enemy_s5_warmup_2</x:v>
+      </x:c>
+      <x:c r="B34" s="37" t="str">
+        <x:v>enemy_s5_warmup</x:v>
+      </x:c>
+      <x:c r="C34" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D34" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="48" customHeight="1">
+      <x:c r="A35" s="37" t="str">
+        <x:v>enemy_s5_warmup_3</x:v>
+      </x:c>
+      <x:c r="B35" s="37" t="str">
+        <x:v>enemy_s5_warmup</x:v>
+      </x:c>
+      <x:c r="C35" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D35" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="48" customHeight="1">
+      <x:c r="A36" s="37" t="str">
+        <x:v>enemy_s5_official_1</x:v>
+      </x:c>
+      <x:c r="B36" s="37" t="str">
+        <x:v>enemy_s5_official</x:v>
+      </x:c>
+      <x:c r="C36" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D36" s="37" t="str">
+        <x:v>大针宽线，安排上了！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="48" customHeight="1">
+      <x:c r="A37" s="37" t="str">
+        <x:v>enemy_s5_official_2</x:v>
+      </x:c>
+      <x:c r="B37" s="37" t="str">
+        <x:v>enemy_s5_official</x:v>
+      </x:c>
+      <x:c r="C37" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D37" s="37" t="str">
+        <x:v>这根线它又长又宽</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="48" customHeight="1">
+      <x:c r="A38" s="37" t="str">
+        <x:v>enemy_s5_official_3</x:v>
+      </x:c>
+      <x:c r="B38" s="37" t="str">
+        <x:v>enemy_s5_official</x:v>
+      </x:c>
+      <x:c r="C38" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D38" s="37" t="str">
+        <x:v>大针宽线，安排上了</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="48" customHeight="1">
+      <x:c r="A39" s="37" t="str">
+        <x:v>enemy_kun_boss_1</x:v>
+      </x:c>
+      <x:c r="B39" s="37" t="str">
+        <x:v>enemy_kun_boss</x:v>
+      </x:c>
+      <x:c r="C39" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D39" s="37" t="str">
+        <x:v>鸡你太美</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="48" customHeight="1">
+      <x:c r="A40" s="37" t="str">
+        <x:v>enemy_kun_boss_2</x:v>
+      </x:c>
+      <x:c r="B40" s="37" t="str">
+        <x:v>enemy_kun_boss</x:v>
+      </x:c>
+      <x:c r="C40" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D40" s="37" t="str">
+        <x:v>唱、跳、Rap、篮球……再加一脚蹬！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="48" customHeight="1">
+      <x:c r="A41" s="37" t="str">
+        <x:v>enemy_kun_boss_3</x:v>
+      </x:c>
+      <x:c r="B41" s="37" t="str">
+        <x:v>enemy_kun_boss</x:v>
+      </x:c>
+      <x:c r="C41" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D41" s="37" t="str">
+        <x:v>坤坤在此，谁敢争锋！</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="48" customHeight="1">
+      <x:c r="A42" s="37" t="str">
+        <x:v>enemy_s1_warmup_1_1</x:v>
+      </x:c>
+      <x:c r="B42" s="37" t="str">
+        <x:v>enemy_s1_warmup_1</x:v>
+      </x:c>
+      <x:c r="C42" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D42" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="48" customHeight="1">
+      <x:c r="A43" s="37" t="str">
+        <x:v>enemy_s1_warmup_1_2</x:v>
+      </x:c>
+      <x:c r="B43" s="37" t="str">
+        <x:v>enemy_s1_warmup_1</x:v>
+      </x:c>
+      <x:c r="C43" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D43" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="48" customHeight="1">
+      <x:c r="A44" s="37" t="str">
+        <x:v>enemy_s1_warmup_1_3</x:v>
+      </x:c>
+      <x:c r="B44" s="37" t="str">
+        <x:v>enemy_s1_warmup_1</x:v>
+      </x:c>
+      <x:c r="C44" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D44" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="48" customHeight="1">
+      <x:c r="A45" s="37" t="str">
+        <x:v>enemy_s1_warmup_2_1</x:v>
+      </x:c>
+      <x:c r="B45" s="37" t="str">
+        <x:v>enemy_s1_warmup_2</x:v>
+      </x:c>
+      <x:c r="C45" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D45" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="48" customHeight="1">
+      <x:c r="A46" s="37" t="str">
+        <x:v>enemy_s1_warmup_2_2</x:v>
+      </x:c>
+      <x:c r="B46" s="37" t="str">
+        <x:v>enemy_s1_warmup_2</x:v>
+      </x:c>
+      <x:c r="C46" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D46" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="48" customHeight="1">
+      <x:c r="A47" s="37" t="str">
+        <x:v>enemy_s1_warmup_2_3</x:v>
+      </x:c>
+      <x:c r="B47" s="37" t="str">
+        <x:v>enemy_s1_warmup_2</x:v>
+      </x:c>
+      <x:c r="C47" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D47" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="48" customHeight="1">
+      <x:c r="A48" s="37" t="str">
+        <x:v>enemy_s1_warmup_3_1</x:v>
+      </x:c>
+      <x:c r="B48" s="37" t="str">
+        <x:v>enemy_s1_warmup_3</x:v>
+      </x:c>
+      <x:c r="C48" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D48" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="48" customHeight="1">
+      <x:c r="A49" s="37" t="str">
+        <x:v>enemy_s1_warmup_3_2</x:v>
+      </x:c>
+      <x:c r="B49" s="37" t="str">
+        <x:v>enemy_s1_warmup_3</x:v>
+      </x:c>
+      <x:c r="C49" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D49" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="48" customHeight="1">
+      <x:c r="A50" s="37" t="str">
+        <x:v>enemy_s1_warmup_3_3</x:v>
+      </x:c>
+      <x:c r="B50" s="37" t="str">
+        <x:v>enemy_s1_warmup_3</x:v>
+      </x:c>
+      <x:c r="C50" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D50" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="48" customHeight="1">
+      <x:c r="A51" s="37" t="str">
+        <x:v>enemy_s1_warmup_4_1</x:v>
+      </x:c>
+      <x:c r="B51" s="37" t="str">
+        <x:v>enemy_s1_warmup_4</x:v>
+      </x:c>
+      <x:c r="C51" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D51" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="48" customHeight="1">
+      <x:c r="A52" s="37" t="str">
+        <x:v>enemy_s1_warmup_4_2</x:v>
+      </x:c>
+      <x:c r="B52" s="37" t="str">
+        <x:v>enemy_s1_warmup_4</x:v>
+      </x:c>
+      <x:c r="C52" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D52" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="48" customHeight="1">
+      <x:c r="A53" s="37" t="str">
+        <x:v>enemy_s1_warmup_4_3</x:v>
+      </x:c>
+      <x:c r="B53" s="37" t="str">
+        <x:v>enemy_s1_warmup_4</x:v>
+      </x:c>
+      <x:c r="C53" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D53" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="48" customHeight="1">
+      <x:c r="A54" s="37" t="str">
+        <x:v>enemy_s1_warmup_5_1</x:v>
+      </x:c>
+      <x:c r="B54" s="37" t="str">
+        <x:v>enemy_s1_warmup_5</x:v>
+      </x:c>
+      <x:c r="C54" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D54" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="48" customHeight="1">
+      <x:c r="A55" s="37" t="str">
+        <x:v>enemy_s1_warmup_5_2</x:v>
+      </x:c>
+      <x:c r="B55" s="37" t="str">
+        <x:v>enemy_s1_warmup_5</x:v>
+      </x:c>
+      <x:c r="C55" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D55" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="48" customHeight="1">
+      <x:c r="A56" s="37" t="str">
+        <x:v>enemy_s1_warmup_5_3</x:v>
+      </x:c>
+      <x:c r="B56" s="37" t="str">
+        <x:v>enemy_s1_warmup_5</x:v>
+      </x:c>
+      <x:c r="C56" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D56" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="48" customHeight="1">
+      <x:c r="A57" s="37" t="str">
+        <x:v>enemy_s2_warmup_1_1</x:v>
+      </x:c>
+      <x:c r="B57" s="37" t="str">
+        <x:v>enemy_s2_warmup_1</x:v>
+      </x:c>
+      <x:c r="C57" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D57" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="48" customHeight="1">
+      <x:c r="A58" s="37" t="str">
+        <x:v>enemy_s2_warmup_1_2</x:v>
+      </x:c>
+      <x:c r="B58" s="37" t="str">
+        <x:v>enemy_s2_warmup_1</x:v>
+      </x:c>
+      <x:c r="C58" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D58" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="48" customHeight="1">
+      <x:c r="A59" s="37" t="str">
+        <x:v>enemy_s2_warmup_1_3</x:v>
+      </x:c>
+      <x:c r="B59" s="37" t="str">
+        <x:v>enemy_s2_warmup_1</x:v>
+      </x:c>
+      <x:c r="C59" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D59" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="48" customHeight="1">
+      <x:c r="A60" s="37" t="str">
+        <x:v>enemy_s2_warmup_2_1</x:v>
+      </x:c>
+      <x:c r="B60" s="37" t="str">
+        <x:v>enemy_s2_warmup_2</x:v>
+      </x:c>
+      <x:c r="C60" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D60" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="48" customHeight="1">
+      <x:c r="A61" s="37" t="str">
+        <x:v>enemy_s2_warmup_2_2</x:v>
+      </x:c>
+      <x:c r="B61" s="37" t="str">
+        <x:v>enemy_s2_warmup_2</x:v>
+      </x:c>
+      <x:c r="C61" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D61" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="48" customHeight="1">
+      <x:c r="A62" s="37" t="str">
+        <x:v>enemy_s2_warmup_2_3</x:v>
+      </x:c>
+      <x:c r="B62" s="37" t="str">
+        <x:v>enemy_s2_warmup_2</x:v>
+      </x:c>
+      <x:c r="C62" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D62" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="48" customHeight="1">
+      <x:c r="A63" s="37" t="str">
+        <x:v>enemy_s2_warmup_3_1</x:v>
+      </x:c>
+      <x:c r="B63" s="37" t="str">
+        <x:v>enemy_s2_warmup_3</x:v>
+      </x:c>
+      <x:c r="C63" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D63" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="48" customHeight="1">
+      <x:c r="A64" s="37" t="str">
+        <x:v>enemy_s2_warmup_3_2</x:v>
+      </x:c>
+      <x:c r="B64" s="37" t="str">
+        <x:v>enemy_s2_warmup_3</x:v>
+      </x:c>
+      <x:c r="C64" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D64" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="48" customHeight="1">
+      <x:c r="A65" s="37" t="str">
+        <x:v>enemy_s2_warmup_3_3</x:v>
+      </x:c>
+      <x:c r="B65" s="37" t="str">
+        <x:v>enemy_s2_warmup_3</x:v>
+      </x:c>
+      <x:c r="C65" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D65" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="48" customHeight="1">
+      <x:c r="A66" s="37" t="str">
+        <x:v>enemy_s2_warmup_4_1</x:v>
+      </x:c>
+      <x:c r="B66" s="37" t="str">
+        <x:v>enemy_s2_warmup_4</x:v>
+      </x:c>
+      <x:c r="C66" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D66" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="48" customHeight="1">
+      <x:c r="A67" s="37" t="str">
+        <x:v>enemy_s2_warmup_4_2</x:v>
+      </x:c>
+      <x:c r="B67" s="37" t="str">
+        <x:v>enemy_s2_warmup_4</x:v>
+      </x:c>
+      <x:c r="C67" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D67" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="48" customHeight="1">
+      <x:c r="A68" s="37" t="str">
+        <x:v>enemy_s2_warmup_4_3</x:v>
+      </x:c>
+      <x:c r="B68" s="37" t="str">
+        <x:v>enemy_s2_warmup_4</x:v>
+      </x:c>
+      <x:c r="C68" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D68" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="48" customHeight="1">
+      <x:c r="A69" s="37" t="str">
+        <x:v>enemy_s2_warmup_5_1</x:v>
+      </x:c>
+      <x:c r="B69" s="37" t="str">
+        <x:v>enemy_s2_warmup_5</x:v>
+      </x:c>
+      <x:c r="C69" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D69" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="48" customHeight="1">
+      <x:c r="A70" s="37" t="str">
+        <x:v>enemy_s2_warmup_5_2</x:v>
+      </x:c>
+      <x:c r="B70" s="37" t="str">
+        <x:v>enemy_s2_warmup_5</x:v>
+      </x:c>
+      <x:c r="C70" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D70" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="48" customHeight="1">
+      <x:c r="A71" s="37" t="str">
+        <x:v>enemy_s2_warmup_5_3</x:v>
+      </x:c>
+      <x:c r="B71" s="37" t="str">
+        <x:v>enemy_s2_warmup_5</x:v>
+      </x:c>
+      <x:c r="C71" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D71" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="48" customHeight="1">
+      <x:c r="A72" s="37" t="str">
+        <x:v>enemy_s3_warmup_1_1</x:v>
+      </x:c>
+      <x:c r="B72" s="37" t="str">
+        <x:v>enemy_s3_warmup_1</x:v>
+      </x:c>
+      <x:c r="C72" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D72" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="48" customHeight="1">
+      <x:c r="A73" s="37" t="str">
+        <x:v>enemy_s3_warmup_1_2</x:v>
+      </x:c>
+      <x:c r="B73" s="37" t="str">
+        <x:v>enemy_s3_warmup_1</x:v>
+      </x:c>
+      <x:c r="C73" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D73" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="48" customHeight="1">
+      <x:c r="A74" s="37" t="str">
+        <x:v>enemy_s3_warmup_1_3</x:v>
+      </x:c>
+      <x:c r="B74" s="37" t="str">
+        <x:v>enemy_s3_warmup_1</x:v>
+      </x:c>
+      <x:c r="C74" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D74" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="48" customHeight="1">
+      <x:c r="A75" s="37" t="str">
+        <x:v>enemy_s3_warmup_2_1</x:v>
+      </x:c>
+      <x:c r="B75" s="37" t="str">
+        <x:v>enemy_s3_warmup_2</x:v>
+      </x:c>
+      <x:c r="C75" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D75" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="48" customHeight="1">
+      <x:c r="A76" s="37" t="str">
+        <x:v>enemy_s3_warmup_2_2</x:v>
+      </x:c>
+      <x:c r="B76" s="37" t="str">
+        <x:v>enemy_s3_warmup_2</x:v>
+      </x:c>
+      <x:c r="C76" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D76" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="48" customHeight="1">
+      <x:c r="A77" s="37" t="str">
+        <x:v>enemy_s3_warmup_2_3</x:v>
+      </x:c>
+      <x:c r="B77" s="37" t="str">
+        <x:v>enemy_s3_warmup_2</x:v>
+      </x:c>
+      <x:c r="C77" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D77" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="48" customHeight="1">
+      <x:c r="A78" s="37" t="str">
+        <x:v>enemy_s3_warmup_3_1</x:v>
+      </x:c>
+      <x:c r="B78" s="37" t="str">
+        <x:v>enemy_s3_warmup_3</x:v>
+      </x:c>
+      <x:c r="C78" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D78" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="48" customHeight="1">
+      <x:c r="A79" s="37" t="str">
+        <x:v>enemy_s3_warmup_3_2</x:v>
+      </x:c>
+      <x:c r="B79" s="37" t="str">
+        <x:v>enemy_s3_warmup_3</x:v>
+      </x:c>
+      <x:c r="C79" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D79" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="48" customHeight="1">
+      <x:c r="A80" s="37" t="str">
+        <x:v>enemy_s3_warmup_3_3</x:v>
+      </x:c>
+      <x:c r="B80" s="37" t="str">
+        <x:v>enemy_s3_warmup_3</x:v>
+      </x:c>
+      <x:c r="C80" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D80" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="48" customHeight="1">
+      <x:c r="A81" s="37" t="str">
+        <x:v>enemy_s3_warmup_4_1</x:v>
+      </x:c>
+      <x:c r="B81" s="37" t="str">
+        <x:v>enemy_s3_warmup_4</x:v>
+      </x:c>
+      <x:c r="C81" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D81" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="48" customHeight="1">
+      <x:c r="A82" s="37" t="str">
+        <x:v>enemy_s3_warmup_4_2</x:v>
+      </x:c>
+      <x:c r="B82" s="37" t="str">
+        <x:v>enemy_s3_warmup_4</x:v>
+      </x:c>
+      <x:c r="C82" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D82" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="48" customHeight="1">
+      <x:c r="A83" s="37" t="str">
+        <x:v>enemy_s3_warmup_4_3</x:v>
+      </x:c>
+      <x:c r="B83" s="37" t="str">
+        <x:v>enemy_s3_warmup_4</x:v>
+      </x:c>
+      <x:c r="C83" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D83" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="48" customHeight="1">
+      <x:c r="A84" s="37" t="str">
+        <x:v>enemy_s3_warmup_5_1</x:v>
+      </x:c>
+      <x:c r="B84" s="37" t="str">
+        <x:v>enemy_s3_warmup_5</x:v>
+      </x:c>
+      <x:c r="C84" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D84" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="48" customHeight="1">
+      <x:c r="A85" s="37" t="str">
+        <x:v>enemy_s3_warmup_5_2</x:v>
+      </x:c>
+      <x:c r="B85" s="37" t="str">
+        <x:v>enemy_s3_warmup_5</x:v>
+      </x:c>
+      <x:c r="C85" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D85" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="48" customHeight="1">
+      <x:c r="A86" s="37" t="str">
+        <x:v>enemy_s3_warmup_5_3</x:v>
+      </x:c>
+      <x:c r="B86" s="37" t="str">
+        <x:v>enemy_s3_warmup_5</x:v>
+      </x:c>
+      <x:c r="C86" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D86" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="48" customHeight="1">
+      <x:c r="A87" s="37" t="str">
+        <x:v>enemy_s4_warmup_1_1</x:v>
+      </x:c>
+      <x:c r="B87" s="37" t="str">
+        <x:v>enemy_s4_warmup_1</x:v>
+      </x:c>
+      <x:c r="C87" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D87" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="48" customHeight="1">
+      <x:c r="A88" s="37" t="str">
+        <x:v>enemy_s4_warmup_1_2</x:v>
+      </x:c>
+      <x:c r="B88" s="37" t="str">
+        <x:v>enemy_s4_warmup_1</x:v>
+      </x:c>
+      <x:c r="C88" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D88" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="48" customHeight="1">
+      <x:c r="A89" s="37" t="str">
+        <x:v>enemy_s4_warmup_1_3</x:v>
+      </x:c>
+      <x:c r="B89" s="37" t="str">
+        <x:v>enemy_s4_warmup_1</x:v>
+      </x:c>
+      <x:c r="C89" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D89" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="48" customHeight="1">
+      <x:c r="A90" s="37" t="str">
+        <x:v>enemy_s4_warmup_2_1</x:v>
+      </x:c>
+      <x:c r="B90" s="37" t="str">
+        <x:v>enemy_s4_warmup_2</x:v>
+      </x:c>
+      <x:c r="C90" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D90" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="48" customHeight="1">
+      <x:c r="A91" s="37" t="str">
+        <x:v>enemy_s4_warmup_2_2</x:v>
+      </x:c>
+      <x:c r="B91" s="37" t="str">
+        <x:v>enemy_s4_warmup_2</x:v>
+      </x:c>
+      <x:c r="C91" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D91" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="48" customHeight="1">
+      <x:c r="A92" s="37" t="str">
+        <x:v>enemy_s4_warmup_2_3</x:v>
+      </x:c>
+      <x:c r="B92" s="37" t="str">
+        <x:v>enemy_s4_warmup_2</x:v>
+      </x:c>
+      <x:c r="C92" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D92" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="48" customHeight="1">
+      <x:c r="A93" s="37" t="str">
+        <x:v>enemy_s4_warmup_3_1</x:v>
+      </x:c>
+      <x:c r="B93" s="37" t="str">
+        <x:v>enemy_s4_warmup_3</x:v>
+      </x:c>
+      <x:c r="C93" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D93" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="48" customHeight="1">
+      <x:c r="A94" s="37" t="str">
+        <x:v>enemy_s4_warmup_3_2</x:v>
+      </x:c>
+      <x:c r="B94" s="37" t="str">
+        <x:v>enemy_s4_warmup_3</x:v>
+      </x:c>
+      <x:c r="C94" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D94" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="48" customHeight="1">
+      <x:c r="A95" s="37" t="str">
+        <x:v>enemy_s4_warmup_3_3</x:v>
+      </x:c>
+      <x:c r="B95" s="37" t="str">
+        <x:v>enemy_s4_warmup_3</x:v>
+      </x:c>
+      <x:c r="C95" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D95" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="48" customHeight="1">
+      <x:c r="A96" s="37" t="str">
+        <x:v>enemy_s4_warmup_4_1</x:v>
+      </x:c>
+      <x:c r="B96" s="37" t="str">
+        <x:v>enemy_s4_warmup_4</x:v>
+      </x:c>
+      <x:c r="C96" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D96" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="48" customHeight="1">
+      <x:c r="A97" s="37" t="str">
+        <x:v>enemy_s4_warmup_4_2</x:v>
+      </x:c>
+      <x:c r="B97" s="37" t="str">
+        <x:v>enemy_s4_warmup_4</x:v>
+      </x:c>
+      <x:c r="C97" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D97" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="48" customHeight="1">
+      <x:c r="A98" s="37" t="str">
+        <x:v>enemy_s4_warmup_4_3</x:v>
+      </x:c>
+      <x:c r="B98" s="37" t="str">
+        <x:v>enemy_s4_warmup_4</x:v>
+      </x:c>
+      <x:c r="C98" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D98" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="48" customHeight="1">
+      <x:c r="A99" s="37" t="str">
+        <x:v>enemy_s4_warmup_5_1</x:v>
+      </x:c>
+      <x:c r="B99" s="37" t="str">
+        <x:v>enemy_s4_warmup_5</x:v>
+      </x:c>
+      <x:c r="C99" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D99" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="48" customHeight="1">
+      <x:c r="A100" s="37" t="str">
+        <x:v>enemy_s4_warmup_5_2</x:v>
+      </x:c>
+      <x:c r="B100" s="37" t="str">
+        <x:v>enemy_s4_warmup_5</x:v>
+      </x:c>
+      <x:c r="C100" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D100" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="48" customHeight="1">
+      <x:c r="A101" s="37" t="str">
+        <x:v>enemy_s4_warmup_5_3</x:v>
+      </x:c>
+      <x:c r="B101" s="37" t="str">
+        <x:v>enemy_s4_warmup_5</x:v>
+      </x:c>
+      <x:c r="C101" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D101" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="48" customHeight="1">
+      <x:c r="A102" s="37" t="str">
+        <x:v>enemy_s5_warmup_1_1</x:v>
+      </x:c>
+      <x:c r="B102" s="37" t="str">
+        <x:v>enemy_s5_warmup_1</x:v>
+      </x:c>
+      <x:c r="C102" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D102" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="48" customHeight="1">
+      <x:c r="A103" s="37" t="str">
+        <x:v>enemy_s5_warmup_1_2</x:v>
+      </x:c>
+      <x:c r="B103" s="37" t="str">
+        <x:v>enemy_s5_warmup_1</x:v>
+      </x:c>
+      <x:c r="C103" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D103" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="48" customHeight="1">
+      <x:c r="A104" s="37" t="str">
+        <x:v>enemy_s5_warmup_1_3</x:v>
+      </x:c>
+      <x:c r="B104" s="37" t="str">
+        <x:v>enemy_s5_warmup_1</x:v>
+      </x:c>
+      <x:c r="C104" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D104" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="48" customHeight="1">
+      <x:c r="A105" s="37" t="str">
+        <x:v>enemy_s5_warmup_2_1</x:v>
+      </x:c>
+      <x:c r="B105" s="37" t="str">
+        <x:v>enemy_s5_warmup_2</x:v>
+      </x:c>
+      <x:c r="C105" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D105" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="48" customHeight="1">
+      <x:c r="A106" s="37" t="str">
+        <x:v>enemy_s5_warmup_2_2</x:v>
+      </x:c>
+      <x:c r="B106" s="37" t="str">
+        <x:v>enemy_s5_warmup_2</x:v>
+      </x:c>
+      <x:c r="C106" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D106" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="48" customHeight="1">
+      <x:c r="A107" s="37" t="str">
+        <x:v>enemy_s5_warmup_2_3</x:v>
+      </x:c>
+      <x:c r="B107" s="37" t="str">
+        <x:v>enemy_s5_warmup_2</x:v>
+      </x:c>
+      <x:c r="C107" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D107" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="48" customHeight="1">
+      <x:c r="A108" s="37" t="str">
+        <x:v>enemy_s5_warmup_3_1</x:v>
+      </x:c>
+      <x:c r="B108" s="37" t="str">
+        <x:v>enemy_s5_warmup_3</x:v>
+      </x:c>
+      <x:c r="C108" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D108" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="48" customHeight="1">
+      <x:c r="A109" s="37" t="str">
+        <x:v>enemy_s5_warmup_3_2</x:v>
+      </x:c>
+      <x:c r="B109" s="37" t="str">
+        <x:v>enemy_s5_warmup_3</x:v>
+      </x:c>
+      <x:c r="C109" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D109" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="48" customHeight="1">
+      <x:c r="A110" s="37" t="str">
+        <x:v>enemy_s5_warmup_3_3</x:v>
+      </x:c>
+      <x:c r="B110" s="37" t="str">
+        <x:v>enemy_s5_warmup_3</x:v>
+      </x:c>
+      <x:c r="C110" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D110" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="48" customHeight="1">
+      <x:c r="A111" s="37" t="str">
+        <x:v>enemy_s5_warmup_4_1</x:v>
+      </x:c>
+      <x:c r="B111" s="37" t="str">
+        <x:v>enemy_s5_warmup_4</x:v>
+      </x:c>
+      <x:c r="C111" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D111" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="48" customHeight="1">
+      <x:c r="A112" s="37" t="str">
+        <x:v>enemy_s5_warmup_4_2</x:v>
+      </x:c>
+      <x:c r="B112" s="37" t="str">
+        <x:v>enemy_s5_warmup_4</x:v>
+      </x:c>
+      <x:c r="C112" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D112" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="48" customHeight="1">
+      <x:c r="A113" s="37" t="str">
+        <x:v>enemy_s5_warmup_4_3</x:v>
+      </x:c>
+      <x:c r="B113" s="37" t="str">
+        <x:v>enemy_s5_warmup_4</x:v>
+      </x:c>
+      <x:c r="C113" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D113" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="48" customHeight="1">
+      <x:c r="A114" s="37" t="str">
+        <x:v>enemy_s5_warmup_5_1</x:v>
+      </x:c>
+      <x:c r="B114" s="37" t="str">
+        <x:v>enemy_s5_warmup_5</x:v>
+      </x:c>
+      <x:c r="C114" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D114" s="37" t="str">
+        <x:v>咯咯咯，你也配上擂台？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="48" customHeight="1">
+      <x:c r="A115" s="37" t="str">
+        <x:v>enemy_s5_warmup_5_2</x:v>
+      </x:c>
+      <x:c r="B115" s="37" t="str">
+        <x:v>enemy_s5_warmup_5</x:v>
+      </x:c>
+      <x:c r="C115" s="37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D115" s="37" t="str">
+        <x:v>羽毛挺花，打人不行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="48" customHeight="1">
+      <x:c r="A116" s="37" t="str">
+        <x:v>enemy_s5_warmup_5_3</x:v>
+      </x:c>
+      <x:c r="B116" s="37" t="str">
+        <x:v>enemy_s5_warmup_5</x:v>
+      </x:c>
+      <x:c r="C116" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D116" s="37" t="str">
+        <x:v>回去喝汤吧。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -7503,29 +9392,29 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="29" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="7" width="12" customWidth="1"/>
-    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="62" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="55" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
     <x:col min="11" max="12" width="14" customWidth="1"/>
-    <x:col min="13" max="13" width="15" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="15" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="15" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="15" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="15" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="15" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="15" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="15" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="15" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="55" hidden="0" customWidth="1"/>
-    <x:col min="22" max="22" width="15" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="18" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="18" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="18" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="18" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="18" hidden="0" customWidth="1"/>
     <x:col min="23" max="23" width="15" hidden="0" customWidth="1"/>
     <x:col min="24" max="24" width="15" hidden="0" customWidth="1"/>
     <x:col min="25" max="25" width="15" hidden="0" customWidth="1"/>
@@ -7541,628 +9430,484 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="54" customHeight="1">
-      <x:c r="A1" s="126" t="str">
+      <x:c r="A1" s="132" t="str">
         <x:v>编号</x:v>
       </x:c>
-      <x:c r="B1" s="126" t="str">
+      <x:c r="B1" s="132" t="str">
         <x:v>玩家名</x:v>
       </x:c>
-      <x:c r="C1" s="126" t="str">
+      <x:c r="C1" s="132" t="str">
         <x:v>生命</x:v>
       </x:c>
-      <x:c r="D1" s="126" t="str">
+      <x:c r="D1" s="132" t="str">
         <x:v>攻击</x:v>
       </x:c>
-      <x:c r="E1" s="126" t="str">
+      <x:c r="E1" s="132" t="str">
         <x:v>防御</x:v>
       </x:c>
-      <x:c r="F1" s="126" t="str">
+      <x:c r="F1" s="132" t="str">
         <x:v>速度</x:v>
       </x:c>
-      <x:c r="G1" s="126" t="str">
+      <x:c r="G1" s="132" t="str">
         <x:v>暴击</x:v>
       </x:c>
-      <x:c r="H1" s="126" t="str">
-        <x:v>鸡王敌人id</x:v>
-      </x:c>
-      <x:c r="I1" s="126" t="str">
-        <x:v>击败鸡王金币</x:v>
-      </x:c>
-      <x:c r="J1" s="126" t="str">
-        <x:v>鸡王提示</x:v>
-      </x:c>
-      <x:c r="K1" s="126" t="str">
-        <x:v>垃圾话1</x:v>
-      </x:c>
-      <x:c r="L1" s="126" t="str">
-        <x:v>垃圾话2</x:v>
-      </x:c>
-      <x:c r="M1" s="126" t="str">
-        <x:v>垃圾话3</x:v>
-      </x:c>
-      <x:c r="N1" s="121" t="str">
-        <x:v>开场剧情</x:v>
-      </x:c>
-      <x:c r="O1" s="121" t="str">
-        <x:v>结局剧情</x:v>
-      </x:c>
-      <x:c r="P1" s="121" t="str">
-        <x:v>第1图剧情</x:v>
-      </x:c>
-      <x:c r="Q1" s="121" t="str">
-        <x:v>第2图剧情</x:v>
-      </x:c>
-      <x:c r="R1" s="121" t="str">
-        <x:v>第3图剧情</x:v>
-      </x:c>
-      <x:c r="S1" s="121" t="str">
-        <x:v>第4图剧情</x:v>
-      </x:c>
-      <x:c r="T1" s="121" t="str">
-        <x:v>第5图剧情</x:v>
-      </x:c>
-      <x:c r="U1" s="121" t="str">
+      <x:c r="H1" s="132" t="str">
         <x:v>随机名称池（JSON数组）</x:v>
       </x:c>
-      <x:c r="V1" s="121" t="str">
+      <x:c r="I1" s="132" t="str">
         <x:v>连击</x:v>
       </x:c>
-      <x:c r="W1" s="121" t="str">
+      <x:c r="J1" s="132" t="str">
         <x:v>初始鸡冠颜色</x:v>
       </x:c>
-      <x:c r="X1" s="121" t="str">
+      <x:c r="K1" s="132" t="str">
         <x:v>初始头颜色</x:v>
       </x:c>
-      <x:c r="Y1" s="121" t="str">
+      <x:c r="L1" s="132" t="str">
         <x:v>初始脖子颜色</x:v>
       </x:c>
-      <x:c r="Z1" s="121" t="str">
+      <x:c r="M1" s="132" t="str">
         <x:v>初始躯干颜色</x:v>
       </x:c>
-      <x:c r="AA1" s="121" t="str">
+      <x:c r="N1" s="132" t="str">
         <x:v>初始翅膀颜色</x:v>
       </x:c>
-      <x:c r="AB1" s="121" t="str">
+      <x:c r="O1" s="132" t="str">
         <x:v>初始尾巴颜色</x:v>
       </x:c>
-      <x:c r="AC1" s="121" t="str">
+      <x:c r="P1" s="132" t="str">
         <x:v>初始腿颜色</x:v>
       </x:c>
-      <x:c r="AD1" s="121" t="str">
+      <x:c r="Q1" s="132" t="str">
         <x:v>face</x:v>
       </x:c>
-      <x:c r="AE1" s="121" t="str">
+      <x:c r="R1" s="132" t="str">
         <x:v>初始金币</x:v>
       </x:c>
-      <x:c r="AF1" s="121" t="str">
+      <x:c r="S1" s="132" t="str">
         <x:v>基础复活次数</x:v>
       </x:c>
-      <x:c r="AG1" s="121" t="str">
+      <x:c r="T1" s="132" t="str">
         <x:v>基础回血量</x:v>
       </x:c>
-      <x:c r="AH1" s="121" t="str">
+      <x:c r="U1" s="132" t="str">
         <x:v>基础锁血能力</x:v>
       </x:c>
+      <x:c r="V1" s="132" t="str">
+        <x:v>台词组ID</x:v>
+      </x:c>
+      <x:c r="W1"/>
+      <x:c r="X1"/>
+      <x:c r="Y1"/>
+      <x:c r="Z1"/>
+      <x:c r="AA1"/>
+      <x:c r="AB1"/>
+      <x:c r="AC1"/>
+      <x:c r="AD1"/>
+      <x:c r="AE1"/>
+      <x:c r="AF1"/>
+      <x:c r="AG1"/>
+      <x:c r="AH1"/>
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
-      <x:c r="A2" s="127" t="str">
+      <x:c r="A2" s="135" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="B2" s="127" t="str">
+      <x:c r="B2" s="135" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="C2" s="127" t="str">
+      <x:c r="C2" s="135" t="str">
         <x:v>maxHp</x:v>
       </x:c>
-      <x:c r="D2" s="127" t="str">
+      <x:c r="D2" s="135" t="str">
         <x:v>atk</x:v>
       </x:c>
-      <x:c r="E2" s="127" t="str">
+      <x:c r="E2" s="135" t="str">
         <x:v>def</x:v>
       </x:c>
-      <x:c r="F2" s="127" t="str">
+      <x:c r="F2" s="135" t="str">
         <x:v>spd</x:v>
       </x:c>
-      <x:c r="G2" s="127" t="str">
+      <x:c r="G2" s="135" t="str">
         <x:v>crit</x:v>
       </x:c>
-      <x:c r="H2" s="127" t="str">
-        <x:v>bossEnemyId</x:v>
-      </x:c>
-      <x:c r="I2" s="127" t="str">
-        <x:v>bossGoldWin</x:v>
-      </x:c>
-      <x:c r="J2" s="127" t="str">
-        <x:v>hintBoss</x:v>
-      </x:c>
-      <x:c r="K2" s="127" t="str">
-        <x:v>taunt1</x:v>
-      </x:c>
-      <x:c r="L2" s="127" t="str">
-        <x:v>taunt2</x:v>
-      </x:c>
-      <x:c r="M2" s="127" t="str">
-        <x:v>taunt3</x:v>
-      </x:c>
-      <x:c r="N2" s="122" t="str">
-        <x:v>storyIntro</x:v>
-      </x:c>
-      <x:c r="O2" s="122" t="str">
-        <x:v>storyEnding</x:v>
-      </x:c>
-      <x:c r="P2" s="122" t="str">
-        <x:v>story1</x:v>
-      </x:c>
-      <x:c r="Q2" s="122" t="str">
-        <x:v>story2</x:v>
-      </x:c>
-      <x:c r="R2" s="122" t="str">
-        <x:v>story3</x:v>
-      </x:c>
-      <x:c r="S2" s="122" t="str">
-        <x:v>story4</x:v>
-      </x:c>
-      <x:c r="T2" s="122" t="str">
-        <x:v>story5</x:v>
-      </x:c>
-      <x:c r="U2" s="122" t="str">
+      <x:c r="H2" s="135" t="str">
         <x:v>randomNames</x:v>
       </x:c>
-      <x:c r="V2" s="122" t="str">
+      <x:c r="I2" s="135" t="str">
         <x:v>combo</x:v>
       </x:c>
-      <x:c r="W2" s="122" t="str">
+      <x:c r="J2" s="135" t="str">
         <x:v>colorComb</x:v>
       </x:c>
-      <x:c r="X2" s="122" t="str">
+      <x:c r="K2" s="135" t="str">
         <x:v>colorHead</x:v>
       </x:c>
-      <x:c r="Y2" s="122" t="str">
+      <x:c r="L2" s="135" t="str">
         <x:v>colorNeck</x:v>
       </x:c>
-      <x:c r="Z2" s="122" t="str">
+      <x:c r="M2" s="135" t="str">
         <x:v>colorBody</x:v>
       </x:c>
-      <x:c r="AA2" s="122" t="str">
+      <x:c r="N2" s="135" t="str">
         <x:v>colorWing</x:v>
       </x:c>
-      <x:c r="AB2" s="122" t="str">
+      <x:c r="O2" s="135" t="str">
         <x:v>colorTail</x:v>
       </x:c>
-      <x:c r="AC2" s="122" t="str">
+      <x:c r="P2" s="135" t="str">
         <x:v>colorLeg</x:v>
       </x:c>
-      <x:c r="AD2" s="122" t="str">
+      <x:c r="Q2" s="135" t="str">
         <x:v>face</x:v>
       </x:c>
-      <x:c r="AE2" s="122" t="str">
+      <x:c r="R2" s="135" t="str">
         <x:v>initialGold</x:v>
       </x:c>
-      <x:c r="AF2" s="122" t="str">
+      <x:c r="S2" s="135" t="str">
         <x:v>revive</x:v>
       </x:c>
-      <x:c r="AG2" s="122" t="str">
+      <x:c r="T2" s="135" t="str">
         <x:v>healPerTurn</x:v>
       </x:c>
-      <x:c r="AH2" s="122" t="str">
+      <x:c r="U2" s="135" t="str">
         <x:v>lockHp</x:v>
       </x:c>
+      <x:c r="V2" s="135" t="str">
+        <x:v>tauntGroup</x:v>
+      </x:c>
+      <x:c r="W2"/>
+      <x:c r="X2"/>
+      <x:c r="Y2"/>
+      <x:c r="Z2"/>
+      <x:c r="AA2"/>
+      <x:c r="AB2"/>
+      <x:c r="AC2"/>
+      <x:c r="AD2"/>
+      <x:c r="AE2"/>
+      <x:c r="AF2"/>
+      <x:c r="AG2"/>
+      <x:c r="AH2"/>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="129" t="str">
+      <x:c r="A3" s="137" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="B3" s="129" t="str">
+      <x:c r="B3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C3" s="129" t="str">
+      <x:c r="C3" s="137" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="D3" s="129" t="str">
+      <x:c r="D3" s="137" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="E3" s="129" t="str">
+      <x:c r="E3" s="137" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="F3" s="129" t="str">
+      <x:c r="F3" s="137" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="G3" s="129" t="str">
+      <x:c r="G3" s="137" t="str">
         <x:v>float</x:v>
       </x:c>
-      <x:c r="H3" s="129" t="str">
+      <x:c r="H3" s="137" t="str">
+        <x:v>any</x:v>
+      </x:c>
+      <x:c r="I3" s="137" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="J3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="I3" s="129" t="str">
+      <x:c r="K3" s="137" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="L3" s="137" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="M3" s="137" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="N3" s="137" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="O3" s="137" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="P3" s="137" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="Q3" s="137" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="R3" s="137" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="J3" s="129" t="str">
+      <x:c r="S3" s="137" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="T3" s="137" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="U3" s="137" t="str">
+        <x:v>bool</x:v>
+      </x:c>
+      <x:c r="V3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="K3" s="129" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="L3" s="129" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="M3" s="129" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="N3" s="124" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="O3" s="124" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="P3" s="124" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="Q3" s="124" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="R3" s="124" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="S3" s="124" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="T3" s="124" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="U3" s="124" t="str">
-        <x:v>any</x:v>
-      </x:c>
-      <x:c r="V3" s="124" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="W3" s="124" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="X3" s="124" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="Y3" s="124" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="Z3" s="124" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="AA3" s="124" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="AB3" s="124" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="AC3" s="124" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="AD3" s="124" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="AE3" s="124" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="AF3" s="124" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="AG3" s="124" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="AH3" s="124" t="str">
-        <x:v>bool</x:v>
-      </x:c>
+      <x:c r="W3"/>
+      <x:c r="X3"/>
+      <x:c r="Y3"/>
+      <x:c r="Z3"/>
+      <x:c r="AA3"/>
+      <x:c r="AB3"/>
+      <x:c r="AC3"/>
+      <x:c r="AD3"/>
+      <x:c r="AE3"/>
+      <x:c r="AF3"/>
+      <x:c r="AG3"/>
+      <x:c r="AH3"/>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="129" t="str">
+      <x:c r="A4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="B4" s="129" t="str">
+      <x:c r="B4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="C4" s="129" t="str">
+      <x:c r="C4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="D4" s="129" t="str">
+      <x:c r="D4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="E4" s="129" t="str">
+      <x:c r="E4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="F4" s="129" t="str">
+      <x:c r="F4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="G4" s="129" t="str">
+      <x:c r="G4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="H4" s="129" t="str">
+      <x:c r="H4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="I4" s="129" t="str">
+      <x:c r="I4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="J4" s="129" t="str">
+      <x:c r="J4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="K4" s="129" t="str">
+      <x:c r="K4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="L4" s="129" t="str">
+      <x:c r="L4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="M4" s="129" t="str">
+      <x:c r="M4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="N4" s="124" t="str">
+      <x:c r="N4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="O4" s="124" t="str">
+      <x:c r="O4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="P4" s="124" t="str">
+      <x:c r="P4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="Q4" s="124" t="str">
+      <x:c r="Q4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="R4" s="124" t="str">
+      <x:c r="R4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="S4" s="124" t="str">
+      <x:c r="S4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="T4" s="124" t="str">
+      <x:c r="T4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="U4" s="124" t="str">
+      <x:c r="U4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="V4" s="124" t="str">
+      <x:c r="V4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="W4" s="124" t="str">
-        <x:v>server_no</x:v>
-      </x:c>
-      <x:c r="X4" s="124" t="str">
-        <x:v>server_no</x:v>
-      </x:c>
-      <x:c r="Y4" s="124" t="str">
-        <x:v>server_no</x:v>
-      </x:c>
-      <x:c r="Z4" s="124" t="str">
-        <x:v>server_no</x:v>
-      </x:c>
-      <x:c r="AA4" s="124" t="str">
-        <x:v>server_no</x:v>
-      </x:c>
-      <x:c r="AB4" s="124" t="str">
-        <x:v>server_no</x:v>
-      </x:c>
-      <x:c r="AC4" s="124" t="str">
-        <x:v>server_no</x:v>
-      </x:c>
-      <x:c r="AD4" s="124" t="str">
-        <x:v>server_no</x:v>
-      </x:c>
-      <x:c r="AE4" s="124" t="str">
-        <x:v>server_no</x:v>
-      </x:c>
-      <x:c r="AF4" s="124" t="str">
-        <x:v>server_no</x:v>
-      </x:c>
-      <x:c r="AG4" s="124" t="str">
-        <x:v>server_no</x:v>
-      </x:c>
-      <x:c r="AH4" s="124" t="str">
-        <x:v>server_no</x:v>
-      </x:c>
+      <x:c r="W4"/>
+      <x:c r="X4"/>
+      <x:c r="Y4"/>
+      <x:c r="Z4"/>
+      <x:c r="AA4"/>
+      <x:c r="AB4"/>
+      <x:c r="AC4"/>
+      <x:c r="AD4"/>
+      <x:c r="AE4"/>
+      <x:c r="AF4"/>
+      <x:c r="AG4"/>
+      <x:c r="AH4"/>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="129" t="str">
+      <x:c r="A5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="B5" s="129" t="str">
+      <x:c r="B5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="C5" s="129" t="str">
+      <x:c r="C5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="D5" s="129" t="str">
+      <x:c r="D5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="E5" s="129" t="str">
+      <x:c r="E5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="F5" s="129" t="str">
+      <x:c r="F5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="G5" s="129" t="str">
+      <x:c r="G5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="H5" s="129" t="str">
+      <x:c r="H5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="I5" s="129" t="str">
+      <x:c r="I5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="J5" s="129" t="str">
+      <x:c r="J5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="K5" s="129" t="str">
+      <x:c r="K5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="L5" s="129" t="str">
+      <x:c r="L5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="M5" s="129" t="str">
+      <x:c r="M5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="N5" s="124" t="str">
+      <x:c r="N5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="O5" s="124" t="str">
+      <x:c r="O5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="P5" s="124" t="str">
+      <x:c r="P5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="Q5" s="124" t="str">
+      <x:c r="Q5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="R5" s="124" t="str">
+      <x:c r="R5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="S5" s="124" t="str">
+      <x:c r="S5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="T5" s="124" t="str">
+      <x:c r="T5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="U5" s="124" t="str">
+      <x:c r="U5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="V5" s="124" t="str">
+      <x:c r="V5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="W5" s="124" t="str">
-        <x:v>client</x:v>
-      </x:c>
-      <x:c r="X5" s="124" t="str">
-        <x:v>client</x:v>
-      </x:c>
-      <x:c r="Y5" s="124" t="str">
-        <x:v>client</x:v>
-      </x:c>
-      <x:c r="Z5" s="124" t="str">
-        <x:v>client</x:v>
-      </x:c>
-      <x:c r="AA5" s="124" t="str">
-        <x:v>client</x:v>
-      </x:c>
-      <x:c r="AB5" s="124" t="str">
-        <x:v>client</x:v>
-      </x:c>
-      <x:c r="AC5" s="124" t="str">
-        <x:v>client</x:v>
-      </x:c>
-      <x:c r="AD5" s="124" t="str">
-        <x:v>client</x:v>
-      </x:c>
-      <x:c r="AE5" s="124" t="str">
-        <x:v>client</x:v>
-      </x:c>
-      <x:c r="AF5" s="124" t="str">
-        <x:v>client</x:v>
-      </x:c>
-      <x:c r="AG5" s="124" t="str">
-        <x:v>client</x:v>
-      </x:c>
-      <x:c r="AH5" s="124" t="str">
-        <x:v>client</x:v>
-      </x:c>
+      <x:c r="W5"/>
+      <x:c r="X5"/>
+      <x:c r="Y5"/>
+      <x:c r="Z5"/>
+      <x:c r="AA5"/>
+      <x:c r="AB5"/>
+      <x:c r="AC5"/>
+      <x:c r="AD5"/>
+      <x:c r="AE5"/>
+      <x:c r="AF5"/>
+      <x:c r="AG5"/>
+      <x:c r="AH5"/>
     </x:row>
     <x:row r="6" ht="115" customHeight="1">
-      <x:c r="A6" s="67" t="n">
+      <x:c r="A6" s="37" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="37" t="str">
         <x:v>无名鸡</x:v>
       </x:c>
-      <x:c r="C6" s="67" t="n">
+      <x:c r="C6" s="37" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="D6" s="67" t="n">
+      <x:c r="D6" s="37" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="E6" s="67" t="n">
+      <x:c r="E6" s="37" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F6" s="67" t="n">
+      <x:c r="F6" s="37" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G6" s="112" t="n">
+      <x:c r="G6" s="37" t="n">
         <x:v>0.12</x:v>
       </x:c>
       <x:c r="H6" s="37" t="str">
-        <x:v>kun_boss</x:v>
-      </x:c>
-      <x:c r="I6" s="67" t="n">
-        <x:v>200</x:v>
+        <x:v>["呆头王鸡","铁嘴战鸡","闪电羽","村口霸王","小鸡大将","彩羽勇者"]</x:v>
+      </x:c>
+      <x:c r="I6" s="37" t="n">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J6" s="37" t="str">
-        <x:v>五图赛程已毕，鸡王坤坤在全村注视下等你。</x:v>
+        <x:v>#B91C1C</x:v>
       </x:c>
       <x:c r="K6" s="37" t="str">
-        <x:v>今儿个让你见识村口一霸！</x:v>
+        <x:v>#F03E53</x:v>
       </x:c>
       <x:c r="L6" s="37" t="str">
-        <x:v>你这只鸡，看着就嫩。</x:v>
+        <x:v>#F03E53</x:v>
       </x:c>
       <x:c r="M6" s="37" t="str">
-        <x:v>热身都站不稳？正式赛更别来。</x:v>
+        <x:v>#F03E53</x:v>
       </x:c>
       <x:c r="N6" s="37" t="str">
-        <x:v>鸡鸣村的争霸赛开始了。无名的你，将用比赛、装备与成长，赢得全村的认可。</x:v>
+        <x:v>#AD8E6A</x:v>
       </x:c>
       <x:c r="O6" s="37" t="str">
-        <x:v>全村见证新鸡王诞生。争霸赛年年有，挑战永不休。</x:v>
+        <x:v>#7B4B2A</x:v>
       </x:c>
       <x:c r="P6" s="37" t="str">
-        <x:v>村民还在笑：这只无名鸡，也想争王？</x:v>
+        <x:v>#C5A077</x:v>
       </x:c>
       <x:c r="Q6" s="37" t="str">
-        <x:v>围观的鸡群渐渐安静，开始认真看你的比赛。</x:v>
-      </x:c>
-      <x:c r="R6" s="37" t="str">
-        <x:v>有人开始为你喝彩：无名鸡，继续冲！</x:v>
-      </x:c>
-      <x:c r="S6" s="37" t="str">
-        <x:v>全村都在期待，你能走到多远。</x:v>
-      </x:c>
-      <x:c r="T6" s="37" t="str">
-        <x:v>走完最后的赛程，在全村注视下挑战坤坤。</x:v>
-      </x:c>
-      <x:c r="U6" s="37" t="str">
-        <x:v>["呆头王鸡","铁嘴战鸡","闪电羽","村口霸王","小鸡大将","彩羽勇者"]</x:v>
-      </x:c>
-      <x:c r="V6" s="67" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="W6" s="37" t="str">
-        <x:v>#B91C1C</x:v>
-      </x:c>
-      <x:c r="X6" s="37" t="str">
-        <x:v>#F03E53</x:v>
-      </x:c>
-      <x:c r="Y6" s="37" t="str">
-        <x:v>#F03E53</x:v>
-      </x:c>
-      <x:c r="Z6" s="37" t="str">
-        <x:v>#F03E53</x:v>
-      </x:c>
-      <x:c r="AA6" s="37" t="str">
-        <x:v>#AD8E6A</x:v>
-      </x:c>
-      <x:c r="AB6" s="37" t="str">
-        <x:v>#7B4B2A</x:v>
-      </x:c>
-      <x:c r="AC6" s="37" t="str">
-        <x:v>#C5A077</x:v>
-      </x:c>
-      <x:c r="AD6" s="37" t="str">
         <x:v>fierce</x:v>
       </x:c>
-      <x:c r="AE6" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AF6" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AG6" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AH6" s="91" t="b">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="R6" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S6" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T6" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U6" s="91" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V6" s="37" t="str">
+        <x:v>player_1</x:v>
+      </x:c>
+      <x:c r="W6"/>
+      <x:c r="X6"/>
+      <x:c r="Y6"/>
+      <x:c r="Z6"/>
+      <x:c r="AA6"/>
+      <x:c r="AB6"/>
+      <x:c r="AC6"/>
+      <x:c r="AD6"/>
+      <x:c r="AE6"/>
+      <x:c r="AF6"/>
+      <x:c r="AG6"/>
+      <x:c r="AH6"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8485,1265 +10230,1201 @@
   <x:cols>
     <x:col min="1" max="2" width="14" customWidth="1"/>
     <x:col min="3" max="8" width="12" customWidth="1"/>
-    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
     <x:col min="11" max="17" width="14" customWidth="1"/>
-    <x:col min="18" max="18" width="15" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="15" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="15" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="18" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="18" hidden="0" customWidth="1"/>
     <x:col min="1" max="1" width="29" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="15" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="15" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="15" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="15" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="15" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="18" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
     <x:col min="21" max="21" width="18" hidden="0" customWidth="1"/>
-    <x:col min="22" max="22" width="15" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="15" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="18" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="18" hidden="0" customWidth="1"/>
     <x:col min="24" max="24" width="15" hidden="0" customWidth="1"/>
     <x:col min="25" max="25" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="54" customHeight="1">
-      <x:c r="A1" s="126" t="str">
+      <x:c r="A1" s="132" t="str">
         <x:v>编号</x:v>
       </x:c>
-      <x:c r="B1" s="126" t="str">
+      <x:c r="B1" s="132" t="str">
         <x:v>名字</x:v>
       </x:c>
-      <x:c r="C1" s="126" t="str">
+      <x:c r="C1" s="132" t="str">
         <x:v>生命</x:v>
       </x:c>
-      <x:c r="D1" s="126" t="str">
+      <x:c r="D1" s="132" t="str">
         <x:v>攻击</x:v>
       </x:c>
-      <x:c r="E1" s="126" t="str">
+      <x:c r="E1" s="132" t="str">
         <x:v>防御</x:v>
       </x:c>
-      <x:c r="F1" s="126" t="str">
+      <x:c r="F1" s="132" t="str">
         <x:v>速度</x:v>
       </x:c>
-      <x:c r="G1" s="126" t="str">
+      <x:c r="G1" s="132" t="str">
         <x:v>暴击</x:v>
       </x:c>
-      <x:c r="H1" s="126" t="str">
+      <x:c r="H1" s="132" t="str">
         <x:v>复活</x:v>
       </x:c>
-      <x:c r="I1" s="126" t="str">
+      <x:c r="I1" s="132" t="str">
         <x:v>每回合回血</x:v>
       </x:c>
-      <x:c r="J1" s="126" t="str">
+      <x:c r="J1" s="132" t="str">
         <x:v>锁血</x:v>
       </x:c>
-      <x:c r="K1" s="126" t="str">
+      <x:c r="K1" s="132" t="str">
         <x:v>表情</x:v>
       </x:c>
-      <x:c r="L1" s="126" t="str">
+      <x:c r="L1" s="132" t="str">
         <x:v>鸡冠色</x:v>
       </x:c>
-      <x:c r="M1" s="126" t="str">
+      <x:c r="M1" s="132" t="str">
         <x:v>头色</x:v>
       </x:c>
-      <x:c r="N1" s="126" t="str">
+      <x:c r="N1" s="132" t="str">
         <x:v>身色</x:v>
       </x:c>
-      <x:c r="O1" s="126" t="str">
+      <x:c r="O1" s="132" t="str">
         <x:v>翅色</x:v>
       </x:c>
-      <x:c r="P1" s="126" t="str">
+      <x:c r="P1" s="132" t="str">
         <x:v>尾色</x:v>
       </x:c>
-      <x:c r="Q1" s="126" t="str">
+      <x:c r="Q1" s="132" t="str">
         <x:v>腿色</x:v>
       </x:c>
-      <x:c r="R1" s="126" t="str">
-        <x:v>垃圾话1</x:v>
-      </x:c>
-      <x:c r="S1" s="126" t="str">
-        <x:v>垃圾话2</x:v>
-      </x:c>
-      <x:c r="T1" s="126" t="str">
-        <x:v>垃圾话3</x:v>
-      </x:c>
-      <x:c r="U1" s="121" t="str">
+      <x:c r="R1" s="132" t="str">
         <x:v>目标战斗时长（秒）</x:v>
       </x:c>
-      <x:c r="V1" s="121" t="str">
+      <x:c r="S1" s="132" t="str">
         <x:v>弹幕分组</x:v>
       </x:c>
-      <x:c r="W1" s="121" t="str">
+      <x:c r="T1" s="132" t="str">
         <x:v>连击</x:v>
       </x:c>
-      <x:c r="X1" s="121" t="str">
+      <x:c r="U1" s="132" t="str">
         <x:v>脖子颜色</x:v>
       </x:c>
-      <x:c r="Y1" s="121" t="str">
+      <x:c r="V1" s="132" t="str">
         <x:v>立绘资源ID</x:v>
       </x:c>
+      <x:c r="W1" s="132" t="str">
+        <x:v>台词组ID</x:v>
+      </x:c>
+      <x:c r="X1"/>
+      <x:c r="Y1"/>
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
-      <x:c r="A2" s="127" t="str">
+      <x:c r="A2" s="135" t="str">
         <x:v>id</x:v>
       </x:c>
-      <x:c r="B2" s="127" t="str">
+      <x:c r="B2" s="135" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="C2" s="127" t="str">
+      <x:c r="C2" s="135" t="str">
         <x:v>maxHp</x:v>
       </x:c>
-      <x:c r="D2" s="127" t="str">
+      <x:c r="D2" s="135" t="str">
         <x:v>atk</x:v>
       </x:c>
-      <x:c r="E2" s="127" t="str">
+      <x:c r="E2" s="135" t="str">
         <x:v>def</x:v>
       </x:c>
-      <x:c r="F2" s="127" t="str">
+      <x:c r="F2" s="135" t="str">
         <x:v>spd</x:v>
       </x:c>
-      <x:c r="G2" s="127" t="str">
+      <x:c r="G2" s="135" t="str">
         <x:v>crit</x:v>
       </x:c>
-      <x:c r="H2" s="127" t="str">
+      <x:c r="H2" s="135" t="str">
         <x:v>revive</x:v>
       </x:c>
-      <x:c r="I2" s="127" t="str">
+      <x:c r="I2" s="135" t="str">
         <x:v>healPerTurn</x:v>
       </x:c>
-      <x:c r="J2" s="127" t="str">
+      <x:c r="J2" s="135" t="str">
         <x:v>lockHp</x:v>
       </x:c>
-      <x:c r="K2" s="127" t="str">
+      <x:c r="K2" s="135" t="str">
         <x:v>face</x:v>
       </x:c>
-      <x:c r="L2" s="127" t="str">
+      <x:c r="L2" s="135" t="str">
         <x:v>comb</x:v>
       </x:c>
-      <x:c r="M2" s="127" t="str">
+      <x:c r="M2" s="135" t="str">
         <x:v>head</x:v>
       </x:c>
-      <x:c r="N2" s="127" t="str">
+      <x:c r="N2" s="135" t="str">
         <x:v>body</x:v>
       </x:c>
-      <x:c r="O2" s="127" t="str">
+      <x:c r="O2" s="135" t="str">
         <x:v>wing</x:v>
       </x:c>
-      <x:c r="P2" s="127" t="str">
+      <x:c r="P2" s="135" t="str">
         <x:v>tail</x:v>
       </x:c>
-      <x:c r="Q2" s="127" t="str">
+      <x:c r="Q2" s="135" t="str">
         <x:v>leg</x:v>
       </x:c>
-      <x:c r="R2" s="127" t="str">
-        <x:v>taunt1</x:v>
-      </x:c>
-      <x:c r="S2" s="127" t="str">
-        <x:v>taunt2</x:v>
-      </x:c>
-      <x:c r="T2" s="127" t="str">
-        <x:v>taunt3</x:v>
-      </x:c>
-      <x:c r="U2" s="122" t="str">
+      <x:c r="R2" s="135" t="str">
         <x:v>targetBattleSeconds</x:v>
       </x:c>
-      <x:c r="V2" s="122" t="str">
+      <x:c r="S2" s="135" t="str">
         <x:v>danmakuGroup</x:v>
       </x:c>
-      <x:c r="W2" s="122" t="str">
+      <x:c r="T2" s="135" t="str">
         <x:v>combo</x:v>
       </x:c>
-      <x:c r="X2" s="122" t="str">
+      <x:c r="U2" s="135" t="str">
         <x:v>neck</x:v>
       </x:c>
-      <x:c r="Y2" s="122" t="str">
+      <x:c r="V2" s="135" t="str">
         <x:v>illustration</x:v>
       </x:c>
+      <x:c r="W2" s="135" t="str">
+        <x:v>tauntGroup</x:v>
+      </x:c>
+      <x:c r="X2"/>
+      <x:c r="Y2"/>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="129" t="str">
+      <x:c r="A3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="B3" s="129" t="str">
+      <x:c r="B3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C3" s="129" t="str">
+      <x:c r="C3" s="137" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="D3" s="129" t="str">
+      <x:c r="D3" s="137" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="E3" s="129" t="str">
+      <x:c r="E3" s="137" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="F3" s="129" t="str">
+      <x:c r="F3" s="137" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="G3" s="129" t="str">
+      <x:c r="G3" s="137" t="str">
         <x:v>float</x:v>
       </x:c>
-      <x:c r="H3" s="129" t="str">
+      <x:c r="H3" s="137" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="I3" s="129" t="str">
+      <x:c r="I3" s="137" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="J3" s="129" t="str">
+      <x:c r="J3" s="137" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="K3" s="129" t="str">
+      <x:c r="K3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="L3" s="129" t="str">
+      <x:c r="L3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="M3" s="129" t="str">
+      <x:c r="M3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="N3" s="129" t="str">
+      <x:c r="N3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="O3" s="129" t="str">
+      <x:c r="O3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="P3" s="129" t="str">
+      <x:c r="P3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="Q3" s="129" t="str">
+      <x:c r="Q3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="R3" s="129" t="str">
+      <x:c r="R3" s="137" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="S3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="S3" s="129" t="str">
+      <x:c r="T3" s="137" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="U3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="T3" s="129" t="str">
+      <x:c r="V3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="U3" s="124" t="str">
-        <x:v>float</x:v>
-      </x:c>
-      <x:c r="V3" s="124" t="str">
+      <x:c r="W3" s="137" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="W3" s="124" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="X3" s="124" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="Y3" s="124" t="str">
-        <x:v>string</x:v>
-      </x:c>
+      <x:c r="X3"/>
+      <x:c r="Y3"/>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="129" t="str">
+      <x:c r="A4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="B4" s="129" t="str">
+      <x:c r="B4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="C4" s="129" t="str">
+      <x:c r="C4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="D4" s="129" t="str">
+      <x:c r="D4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="E4" s="129" t="str">
+      <x:c r="E4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="F4" s="129" t="str">
+      <x:c r="F4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="G4" s="129" t="str">
+      <x:c r="G4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="H4" s="129" t="str">
+      <x:c r="H4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="I4" s="129" t="str">
+      <x:c r="I4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="J4" s="129" t="str">
+      <x:c r="J4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="K4" s="129" t="str">
+      <x:c r="K4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="L4" s="129" t="str">
+      <x:c r="L4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="M4" s="129" t="str">
+      <x:c r="M4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="N4" s="129" t="str">
+      <x:c r="N4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="O4" s="129" t="str">
+      <x:c r="O4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="P4" s="129" t="str">
+      <x:c r="P4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="Q4" s="129" t="str">
+      <x:c r="Q4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="R4" s="129" t="str">
+      <x:c r="R4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="S4" s="129" t="str">
+      <x:c r="S4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="T4" s="129" t="str">
+      <x:c r="T4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="U4" s="124" t="str">
+      <x:c r="U4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="V4" s="124" t="str">
+      <x:c r="V4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="W4" s="124" t="str">
+      <x:c r="W4" s="137" t="str">
         <x:v>server_no</x:v>
       </x:c>
-      <x:c r="X4" s="124" t="str">
-        <x:v>server_no</x:v>
-      </x:c>
-      <x:c r="Y4" s="124" t="str">
-        <x:v>server_no</x:v>
-      </x:c>
+      <x:c r="X4"/>
+      <x:c r="Y4"/>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="129" t="str">
+      <x:c r="A5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="B5" s="129" t="str">
+      <x:c r="B5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="C5" s="129" t="str">
+      <x:c r="C5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="D5" s="129" t="str">
+      <x:c r="D5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="E5" s="129" t="str">
+      <x:c r="E5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="F5" s="129" t="str">
+      <x:c r="F5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="G5" s="129" t="str">
+      <x:c r="G5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="H5" s="129" t="str">
+      <x:c r="H5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="I5" s="129" t="str">
+      <x:c r="I5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="J5" s="129" t="str">
+      <x:c r="J5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="K5" s="129" t="str">
+      <x:c r="K5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="L5" s="129" t="str">
+      <x:c r="L5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="M5" s="129" t="str">
+      <x:c r="M5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="N5" s="129" t="str">
+      <x:c r="N5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="O5" s="129" t="str">
+      <x:c r="O5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="P5" s="129" t="str">
+      <x:c r="P5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="Q5" s="129" t="str">
+      <x:c r="Q5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="R5" s="129" t="str">
+      <x:c r="R5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="S5" s="129" t="str">
+      <x:c r="S5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="T5" s="129" t="str">
+      <x:c r="T5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="U5" s="124" t="str">
+      <x:c r="U5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="V5" s="124" t="str">
+      <x:c r="V5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="W5" s="124" t="str">
+      <x:c r="W5" s="137" t="str">
         <x:v>client</x:v>
       </x:c>
-      <x:c r="X5" s="124" t="str">
-        <x:v>client</x:v>
-      </x:c>
-      <x:c r="Y5" s="124" t="str">
-        <x:v>client</x:v>
-      </x:c>
+      <x:c r="X5"/>
+      <x:c r="Y5"/>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="41" t="str">
+      <x:c r="A6" s="37" t="str">
         <x:v>s1_warmup</x:v>
       </x:c>
-      <x:c r="B6" s="41" t="str">
+      <x:c r="B6" s="37" t="str">
         <x:v>杂色鸡·1号</x:v>
       </x:c>
-      <x:c r="C6" s="63" t="n">
+      <x:c r="C6" s="37" t="n">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D6" s="63" t="n">
+      <x:c r="D6" s="37" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E6" s="63" t="n">
+      <x:c r="E6" s="37" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F6" s="63" t="n">
+      <x:c r="F6" s="37" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G6" s="108" t="n">
+      <x:c r="G6" s="37" t="n">
         <x:v>0.095</x:v>
       </x:c>
-      <x:c r="H6" s="63" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I6" s="63" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J6" s="63" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K6" s="41" t="str">
+      <x:c r="H6" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I6" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J6" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K6" s="37" t="str">
         <x:v>dumb</x:v>
       </x:c>
-      <x:c r="L6" s="41" t="str">
+      <x:c r="L6" s="37" t="str">
         <x:v>#EE964B</x:v>
       </x:c>
-      <x:c r="M6" s="41" t="str">
+      <x:c r="M6" s="37" t="str">
         <x:v>#2A9D8F</x:v>
       </x:c>
-      <x:c r="N6" s="41" t="str">
+      <x:c r="N6" s="37" t="str">
         <x:v>#F4D35E</x:v>
       </x:c>
-      <x:c r="O6" s="41" t="str">
+      <x:c r="O6" s="37" t="str">
         <x:v>#EE964B</x:v>
       </x:c>
-      <x:c r="P6" s="41" t="str">
+      <x:c r="P6" s="37" t="str">
         <x:v>#7B4B2A</x:v>
       </x:c>
-      <x:c r="Q6" s="41" t="str">
+      <x:c r="Q6" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R6" s="41" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
-      </x:c>
-      <x:c r="S6" s="41" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T6" s="41" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U6" s="112" t="n">
+      <x:c r="R6" s="37" t="n">
         <x:v>25</x:v>
       </x:c>
+      <x:c r="S6" s="37" t="str">
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T6" s="37" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="U6" s="37" t="str">
+        <x:v>#F4D35E</x:v>
+      </x:c>
       <x:c r="V6" s="37" t="str">
+        <x:v>s1_warmup</x:v>
+      </x:c>
+      <x:c r="W6" s="37" t="str">
+        <x:v>enemy_s1_warmup</x:v>
+      </x:c>
+      <x:c r="X6"/>
+      <x:c r="Y6"/>
+    </x:row>
+    <x:row r="7" ht="30" customHeight="1">
+      <x:c r="A7" s="37" t="str">
+        <x:v>s1_official</x:v>
+      </x:c>
+      <x:c r="B7" s="37" t="str">
+        <x:v>菜鸡</x:v>
+      </x:c>
+      <x:c r="C7" s="37" t="n">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D7" s="37" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E7" s="37" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F7" s="37" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G7" s="37" t="n">
+        <x:v>0.095</x:v>
+      </x:c>
+      <x:c r="H7" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I7" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J7" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7" s="37" t="str">
+        <x:v>dumb</x:v>
+      </x:c>
+      <x:c r="L7" s="37" t="str">
+        <x:v>#EE964B</x:v>
+      </x:c>
+      <x:c r="M7" s="37" t="str">
+        <x:v>#F4D35E</x:v>
+      </x:c>
+      <x:c r="N7" s="37" t="str">
+        <x:v>#F4D35E</x:v>
+      </x:c>
+      <x:c r="O7" s="37" t="str">
+        <x:v>#EE964B</x:v>
+      </x:c>
+      <x:c r="P7" s="37" t="str">
+        <x:v>#7B4B2A</x:v>
+      </x:c>
+      <x:c r="Q7" s="37" t="str">
+        <x:v>#E09F3E</x:v>
+      </x:c>
+      <x:c r="R7" s="37" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="S7" s="37" t="str">
+        <x:v>菜鸡</x:v>
+      </x:c>
+      <x:c r="T7" s="37" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="U7" s="37" t="str">
+        <x:v>#F4D35E</x:v>
+      </x:c>
+      <x:c r="V7" s="37" t="str">
+        <x:v>s1_official</x:v>
+      </x:c>
+      <x:c r="W7" s="37" t="str">
+        <x:v>enemy_s1_official</x:v>
+      </x:c>
+      <x:c r="X7"/>
+      <x:c r="Y7"/>
+    </x:row>
+    <x:row r="8" ht="30" customHeight="1">
+      <x:c r="A8" s="37" t="str">
+        <x:v>s2_warmup</x:v>
+      </x:c>
+      <x:c r="B8" s="37" t="str">
+        <x:v>杂色鸡·2号</x:v>
+      </x:c>
+      <x:c r="C8" s="37" t="n">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D8" s="37" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E8" s="37" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F8" s="37" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G8" s="37" t="n">
+        <x:v>0.11</x:v>
+      </x:c>
+      <x:c r="H8" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I8" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J8" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K8" s="37" t="str">
+        <x:v>proud</x:v>
+      </x:c>
+      <x:c r="L8" s="37" t="str">
+        <x:v>#7B4B2A</x:v>
+      </x:c>
+      <x:c r="M8" s="37" t="str">
+        <x:v>#264653</x:v>
+      </x:c>
+      <x:c r="N8" s="37" t="str">
+        <x:v>#EE964B</x:v>
+      </x:c>
+      <x:c r="O8" s="37" t="str">
+        <x:v>#EE964B</x:v>
+      </x:c>
+      <x:c r="P8" s="37" t="str">
+        <x:v>#7B4B2A</x:v>
+      </x:c>
+      <x:c r="Q8" s="37" t="str">
+        <x:v>#E09F3E</x:v>
+      </x:c>
+      <x:c r="R8" s="37" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="S8" s="37" t="str">
         <x:v>common</x:v>
       </x:c>
-      <x:c r="W6" s="67" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="X6" s="37" t="str">
-        <x:v>#F4D35E</x:v>
-      </x:c>
-      <x:c r="Y6" s="37" t="str">
-        <x:v>s1_warmup</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="44" t="str">
-        <x:v>s1_official</x:v>
-      </x:c>
-      <x:c r="B7" s="44" t="str">
-        <x:v>菜鸡</x:v>
-      </x:c>
-      <x:c r="C7" s="64" t="n">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="D7" s="64" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E7" s="64" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F7" s="64" t="n">
+      <x:c r="T8" s="37" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="U8" s="37" t="str">
+        <x:v>#EE964B</x:v>
+      </x:c>
+      <x:c r="V8" s="37" t="str">
+        <x:v>s2_warmup</x:v>
+      </x:c>
+      <x:c r="W8" s="37" t="str">
+        <x:v>enemy_s2_warmup</x:v>
+      </x:c>
+      <x:c r="X8"/>
+      <x:c r="Y8"/>
+    </x:row>
+    <x:row r="9" ht="30" customHeight="1">
+      <x:c r="A9" s="37" t="str">
+        <x:v>s2_official</x:v>
+      </x:c>
+      <x:c r="B9" s="37" t="str">
+        <x:v>肯德鸡</x:v>
+      </x:c>
+      <x:c r="C9" s="37" t="n">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="D9" s="37" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E9" s="37" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F9" s="37" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G9" s="37" t="n">
+        <x:v>0.11</x:v>
+      </x:c>
+      <x:c r="H9" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I9" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K9" s="37" t="str">
+        <x:v>proud</x:v>
+      </x:c>
+      <x:c r="L9" s="37" t="str">
+        <x:v>#7B4B2A</x:v>
+      </x:c>
+      <x:c r="M9" s="37" t="str">
+        <x:v>#C87438</x:v>
+      </x:c>
+      <x:c r="N9" s="37" t="str">
+        <x:v>#C87438</x:v>
+      </x:c>
+      <x:c r="O9" s="37" t="str">
+        <x:v>#EE964B</x:v>
+      </x:c>
+      <x:c r="P9" s="37" t="str">
+        <x:v>#7B4B2A</x:v>
+      </x:c>
+      <x:c r="Q9" s="37" t="str">
+        <x:v>#E09F3E</x:v>
+      </x:c>
+      <x:c r="R9" s="37" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="S9" s="37" t="str">
+        <x:v>肯德鸡</x:v>
+      </x:c>
+      <x:c r="T9" s="37" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="U9" s="37" t="str">
+        <x:v>#C87438</x:v>
+      </x:c>
+      <x:c r="V9" s="37" t="str">
+        <x:v>s2_official</x:v>
+      </x:c>
+      <x:c r="W9" s="37" t="str">
+        <x:v>enemy_s2_official</x:v>
+      </x:c>
+      <x:c r="X9"/>
+      <x:c r="Y9"/>
+    </x:row>
+    <x:row r="10" ht="30" customHeight="1">
+      <x:c r="A10" s="37" t="str">
+        <x:v>s3_warmup</x:v>
+      </x:c>
+      <x:c r="B10" s="37" t="str">
+        <x:v>杂色鸡·3号</x:v>
+      </x:c>
+      <x:c r="C10" s="37" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D10" s="37" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E10" s="37" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F10" s="37" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G10" s="37" t="n">
+        <x:v>0.125</x:v>
+      </x:c>
+      <x:c r="H10" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I10" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J10" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K10" s="37" t="str">
+        <x:v>cute</x:v>
+      </x:c>
+      <x:c r="L10" s="37" t="str">
+        <x:v>#2A9D8F</x:v>
+      </x:c>
+      <x:c r="M10" s="37" t="str">
+        <x:v>#E76F51</x:v>
+      </x:c>
+      <x:c r="N10" s="37" t="str">
+        <x:v>#7B4B2A</x:v>
+      </x:c>
+      <x:c r="O10" s="37" t="str">
+        <x:v>#EE964B</x:v>
+      </x:c>
+      <x:c r="P10" s="37" t="str">
+        <x:v>#7B4B2A</x:v>
+      </x:c>
+      <x:c r="Q10" s="37" t="str">
+        <x:v>#E09F3E</x:v>
+      </x:c>
+      <x:c r="R10" s="37" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="S10" s="37" t="str">
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T10" s="37" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="U10" s="37" t="str">
+        <x:v>#7B4B2A</x:v>
+      </x:c>
+      <x:c r="V10" s="37" t="str">
+        <x:v>s3_warmup</x:v>
+      </x:c>
+      <x:c r="W10" s="37" t="str">
+        <x:v>enemy_s3_warmup</x:v>
+      </x:c>
+      <x:c r="X10"/>
+      <x:c r="Y10"/>
+    </x:row>
+    <x:row r="11" ht="30" customHeight="1">
+      <x:c r="A11" s="37" t="str">
+        <x:v>s3_official</x:v>
+      </x:c>
+      <x:c r="B11" s="37" t="str">
+        <x:v>哈鸡米</x:v>
+      </x:c>
+      <x:c r="C11" s="37" t="n">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="D11" s="37" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E11" s="37" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F11" s="37" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G11" s="37" t="n">
+        <x:v>0.125</x:v>
+      </x:c>
+      <x:c r="H11" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I11" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J11" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K11" s="37" t="str">
+        <x:v>cute</x:v>
+      </x:c>
+      <x:c r="L11" s="37" t="str">
+        <x:v>#2A9D8F</x:v>
+      </x:c>
+      <x:c r="M11" s="37" t="str">
+        <x:v>#F5E7D0</x:v>
+      </x:c>
+      <x:c r="N11" s="37" t="str">
+        <x:v>#F5E7D0</x:v>
+      </x:c>
+      <x:c r="O11" s="37" t="str">
+        <x:v>#EE964B</x:v>
+      </x:c>
+      <x:c r="P11" s="37" t="str">
+        <x:v>#7B4B2A</x:v>
+      </x:c>
+      <x:c r="Q11" s="37" t="str">
+        <x:v>#E09F3E</x:v>
+      </x:c>
+      <x:c r="R11" s="37" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="S11" s="37" t="str">
+        <x:v>哈鸡米</x:v>
+      </x:c>
+      <x:c r="T11" s="37" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="U11" s="37" t="str">
+        <x:v>#F5E7D0</x:v>
+      </x:c>
+      <x:c r="V11" s="37" t="str">
+        <x:v>s3_official</x:v>
+      </x:c>
+      <x:c r="W11" s="37" t="str">
+        <x:v>enemy_s3_official</x:v>
+      </x:c>
+      <x:c r="X11"/>
+      <x:c r="Y11"/>
+    </x:row>
+    <x:row r="12" ht="30" customHeight="1">
+      <x:c r="A12" s="37" t="str">
+        <x:v>s4_warmup</x:v>
+      </x:c>
+      <x:c r="B12" s="37" t="str">
+        <x:v>杂色鸡·4号</x:v>
+      </x:c>
+      <x:c r="C12" s="37" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="D12" s="37" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E12" s="37" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G7" s="109" t="n">
-        <x:v>0.095</x:v>
-      </x:c>
-      <x:c r="H7" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I7" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J7" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K7" s="44" t="str">
+      <x:c r="F12" s="37" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G12" s="37" t="n">
+        <x:v>0.14</x:v>
+      </x:c>
+      <x:c r="H12" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I12" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J12" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K12" s="37" t="str">
+        <x:v>fierce</x:v>
+      </x:c>
+      <x:c r="L12" s="37" t="str">
+        <x:v>#264653</x:v>
+      </x:c>
+      <x:c r="M12" s="37" t="str">
+        <x:v>#FFFFFF</x:v>
+      </x:c>
+      <x:c r="N12" s="37" t="str">
+        <x:v>#2A9D8F</x:v>
+      </x:c>
+      <x:c r="O12" s="37" t="str">
+        <x:v>#EE964B</x:v>
+      </x:c>
+      <x:c r="P12" s="37" t="str">
+        <x:v>#7B4B2A</x:v>
+      </x:c>
+      <x:c r="Q12" s="37" t="str">
+        <x:v>#E09F3E</x:v>
+      </x:c>
+      <x:c r="R12" s="37" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="S12" s="37" t="str">
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T12" s="37" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="U12" s="37" t="str">
+        <x:v>#2A9D8F</x:v>
+      </x:c>
+      <x:c r="V12" s="37" t="str">
+        <x:v>s4_warmup</x:v>
+      </x:c>
+      <x:c r="W12" s="37" t="str">
+        <x:v>enemy_s4_warmup</x:v>
+      </x:c>
+      <x:c r="X12"/>
+      <x:c r="Y12"/>
+    </x:row>
+    <x:row r="13" ht="30" customHeight="1">
+      <x:c r="A13" s="37" t="str">
+        <x:v>s4_official</x:v>
+      </x:c>
+      <x:c r="B13" s="37" t="str">
+        <x:v>新一鸡</x:v>
+      </x:c>
+      <x:c r="C13" s="37" t="n">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D13" s="37" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E13" s="37" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F13" s="37" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G13" s="37" t="n">
+        <x:v>0.14</x:v>
+      </x:c>
+      <x:c r="H13" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I13" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="37" t="str">
+        <x:v>fierce</x:v>
+      </x:c>
+      <x:c r="L13" s="37" t="str">
+        <x:v>#264653</x:v>
+      </x:c>
+      <x:c r="M13" s="37" t="str">
+        <x:v>#3498DB</x:v>
+      </x:c>
+      <x:c r="N13" s="37" t="str">
+        <x:v>#3498DB</x:v>
+      </x:c>
+      <x:c r="O13" s="37" t="str">
+        <x:v>#EE964B</x:v>
+      </x:c>
+      <x:c r="P13" s="37" t="str">
+        <x:v>#7B4B2A</x:v>
+      </x:c>
+      <x:c r="Q13" s="37" t="str">
+        <x:v>#E09F3E</x:v>
+      </x:c>
+      <x:c r="R13" s="37" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="S13" s="37" t="str">
+        <x:v>新一鸡</x:v>
+      </x:c>
+      <x:c r="T13" s="37" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="U13" s="37" t="str">
+        <x:v>#3498DB</x:v>
+      </x:c>
+      <x:c r="V13" s="37" t="str">
+        <x:v>s4_official</x:v>
+      </x:c>
+      <x:c r="W13" s="37" t="str">
+        <x:v>enemy_s4_official</x:v>
+      </x:c>
+      <x:c r="X13"/>
+      <x:c r="Y13"/>
+    </x:row>
+    <x:row r="14" ht="30" customHeight="1">
+      <x:c r="A14" s="37" t="str">
+        <x:v>s5_warmup</x:v>
+      </x:c>
+      <x:c r="B14" s="37" t="str">
+        <x:v>杂色鸡·5号</x:v>
+      </x:c>
+      <x:c r="C14" s="37" t="n">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="D14" s="37" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E14" s="37" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F14" s="37" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G14" s="37" t="n">
+        <x:v>0.155</x:v>
+      </x:c>
+      <x:c r="H14" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I14" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J14" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K14" s="37" t="str">
         <x:v>dumb</x:v>
       </x:c>
-      <x:c r="L7" s="44" t="str">
+      <x:c r="L14" s="37" t="str">
+        <x:v>#E76F51</x:v>
+      </x:c>
+      <x:c r="M14" s="37" t="str">
+        <x:v>#8E44AD</x:v>
+      </x:c>
+      <x:c r="N14" s="37" t="str">
+        <x:v>#264653</x:v>
+      </x:c>
+      <x:c r="O14" s="37" t="str">
         <x:v>#EE964B</x:v>
       </x:c>
-      <x:c r="M7" s="44" t="str">
-        <x:v>#F4D35E</x:v>
-      </x:c>
-      <x:c r="N7" s="44" t="str">
-        <x:v>#F4D35E</x:v>
-      </x:c>
-      <x:c r="O7" s="44" t="str">
+      <x:c r="P14" s="37" t="str">
+        <x:v>#7B4B2A</x:v>
+      </x:c>
+      <x:c r="Q14" s="37" t="str">
+        <x:v>#E09F3E</x:v>
+      </x:c>
+      <x:c r="R14" s="37" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="S14" s="37" t="str">
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T14" s="37" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="U14" s="37" t="str">
+        <x:v>#264653</x:v>
+      </x:c>
+      <x:c r="V14" s="37" t="str">
+        <x:v>s5_warmup</x:v>
+      </x:c>
+      <x:c r="W14" s="37" t="str">
+        <x:v>enemy_s5_warmup</x:v>
+      </x:c>
+      <x:c r="X14"/>
+      <x:c r="Y14"/>
+    </x:row>
+    <x:row r="15" ht="30" customHeight="1">
+      <x:c r="A15" s="37" t="str">
+        <x:v>s5_official</x:v>
+      </x:c>
+      <x:c r="B15" s="37" t="str">
+        <x:v>缝纫鸡</x:v>
+      </x:c>
+      <x:c r="C15" s="37" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="D15" s="37" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E15" s="37" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="37" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G15" s="37" t="n">
+        <x:v>0.155</x:v>
+      </x:c>
+      <x:c r="H15" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I15" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J15" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="37" t="str">
+        <x:v>dumb</x:v>
+      </x:c>
+      <x:c r="L15" s="37" t="str">
+        <x:v>#E76F51</x:v>
+      </x:c>
+      <x:c r="M15" s="37" t="str">
+        <x:v>#AA77BB</x:v>
+      </x:c>
+      <x:c r="N15" s="37" t="str">
+        <x:v>#AA77BB</x:v>
+      </x:c>
+      <x:c r="O15" s="37" t="str">
         <x:v>#EE964B</x:v>
       </x:c>
-      <x:c r="P7" s="44" t="str">
+      <x:c r="P15" s="37" t="str">
         <x:v>#7B4B2A</x:v>
       </x:c>
-      <x:c r="Q7" s="44" t="str">
+      <x:c r="Q15" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R7" s="44" t="str">
-        <x:v>我的战术目前只有勇气！</x:v>
-      </x:c>
-      <x:c r="S7" s="44" t="str">
-        <x:v>这鸡的装备比它本人有自信</x:v>
-      </x:c>
-      <x:c r="T7" s="44" t="str">
-        <x:v>盾牌已经替它投降了</x:v>
-      </x:c>
-      <x:c r="U7" s="112" t="n">
+      <x:c r="R15" s="37" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="V7" s="37" t="str">
-        <x:v>菜鸡</x:v>
-      </x:c>
-      <x:c r="W7" s="67" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="X7" s="37" t="str">
-        <x:v>#F4D35E</x:v>
-      </x:c>
-      <x:c r="Y7" s="37" t="str">
-        <x:v>s1_official</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="47" t="str">
-        <x:v>s2_warmup</x:v>
-      </x:c>
-      <x:c r="B8" s="47" t="str">
-        <x:v>杂色鸡·2号</x:v>
-      </x:c>
-      <x:c r="C8" s="65" t="n">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="D8" s="65" t="n">
+      <x:c r="S15" s="37" t="str">
+        <x:v>缝纫鸡</x:v>
+      </x:c>
+      <x:c r="T15" s="37" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="U15" s="37" t="str">
+        <x:v>#AA77BB</x:v>
+      </x:c>
+      <x:c r="V15" s="37" t="str">
+        <x:v>s5_official</x:v>
+      </x:c>
+      <x:c r="W15" s="37" t="str">
+        <x:v>enemy_s5_official</x:v>
+      </x:c>
+      <x:c r="X15"/>
+      <x:c r="Y15"/>
+    </x:row>
+    <x:row r="16" ht="30" customHeight="1">
+      <x:c r="A16" s="37" t="str">
+        <x:v>kun_boss</x:v>
+      </x:c>
+      <x:c r="B16" s="37" t="str">
+        <x:v>鸡王坤坤</x:v>
+      </x:c>
+      <x:c r="C16" s="37" t="n">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="D16" s="37" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E16" s="37" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="65" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F8" s="65" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G8" s="110" t="n">
-        <x:v>0.11</x:v>
-      </x:c>
-      <x:c r="H8" s="65" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I8" s="65" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J8" s="65" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K8" s="47" t="str">
+      <x:c r="F16" s="37" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G16" s="37" t="n">
+        <x:v>0.17</x:v>
+      </x:c>
+      <x:c r="H16" s="37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I16" s="37" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J16" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" s="37" t="str">
         <x:v>proud</x:v>
       </x:c>
-      <x:c r="L8" s="47" t="str">
-        <x:v>#7B4B2A</x:v>
-      </x:c>
-      <x:c r="M8" s="47" t="str">
-        <x:v>#264653</x:v>
-      </x:c>
-      <x:c r="N8" s="47" t="str">
-        <x:v>#EE964B</x:v>
-      </x:c>
-      <x:c r="O8" s="47" t="str">
-        <x:v>#EE964B</x:v>
-      </x:c>
-      <x:c r="P8" s="47" t="str">
-        <x:v>#7B4B2A</x:v>
-      </x:c>
-      <x:c r="Q8" s="47" t="str">
+      <x:c r="L16" s="37" t="str">
+        <x:v>#FF4D6D</x:v>
+      </x:c>
+      <x:c r="M16" s="37" t="str">
+        <x:v>#222222</x:v>
+      </x:c>
+      <x:c r="N16" s="37" t="str">
+        <x:v>#111111</x:v>
+      </x:c>
+      <x:c r="O16" s="37" t="str">
+        <x:v>#444444</x:v>
+      </x:c>
+      <x:c r="P16" s="37" t="str">
+        <x:v>#FFD60A</x:v>
+      </x:c>
+      <x:c r="Q16" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R8" s="47" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
-      </x:c>
-      <x:c r="S8" s="47" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T8" s="47" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U8" s="112" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="V8" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W8" s="67" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="X8" s="37" t="str">
-        <x:v>#EE964B</x:v>
-      </x:c>
-      <x:c r="Y8" s="37" t="str">
-        <x:v>s2_warmup</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="44" t="str">
-        <x:v>s2_official</x:v>
-      </x:c>
-      <x:c r="B9" s="44" t="str">
-        <x:v>肯德鸡</x:v>
-      </x:c>
-      <x:c r="C9" s="64" t="n">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="D9" s="64" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E9" s="64" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F9" s="64" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G9" s="109" t="n">
-        <x:v>0.11</x:v>
-      </x:c>
-      <x:c r="H9" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I9" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J9" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K9" s="44" t="str">
-        <x:v>proud</x:v>
-      </x:c>
-      <x:c r="L9" s="44" t="str">
-        <x:v>#7B4B2A</x:v>
-      </x:c>
-      <x:c r="M9" s="44" t="str">
-        <x:v>#C87438</x:v>
-      </x:c>
-      <x:c r="N9" s="44" t="str">
-        <x:v>#C87438</x:v>
-      </x:c>
-      <x:c r="O9" s="44" t="str">
-        <x:v>#EE964B</x:v>
-      </x:c>
-      <x:c r="P9" s="44" t="str">
-        <x:v>#7B4B2A</x:v>
-      </x:c>
-      <x:c r="Q9" s="44" t="str">
-        <x:v>#E09F3E</x:v>
-      </x:c>
-      <x:c r="R9" s="44" t="str">
-        <x:v>胜负不重要，火候很重要！</x:v>
-      </x:c>
-      <x:c r="S9" s="44" t="str">
-        <x:v>这鸡看起来已经腌入味了</x:v>
-      </x:c>
-      <x:c r="T9" s="44" t="str">
-        <x:v>对面打轻点，别提前出锅</x:v>
-      </x:c>
-      <x:c r="U9" s="112" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="V9" s="37" t="str">
-        <x:v>肯德鸡</x:v>
-      </x:c>
-      <x:c r="W9" s="67" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="X9" s="37" t="str">
-        <x:v>#C87438</x:v>
-      </x:c>
-      <x:c r="Y9" s="37" t="str">
-        <x:v>s2_official</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="47" t="str">
-        <x:v>s3_warmup</x:v>
-      </x:c>
-      <x:c r="B10" s="47" t="str">
-        <x:v>杂色鸡·3号</x:v>
-      </x:c>
-      <x:c r="C10" s="65" t="n">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="D10" s="65" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E10" s="65" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F10" s="65" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G10" s="110" t="n">
-        <x:v>0.125</x:v>
-      </x:c>
-      <x:c r="H10" s="65" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I10" s="65" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J10" s="65" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K10" s="47" t="str">
-        <x:v>cute</x:v>
-      </x:c>
-      <x:c r="L10" s="47" t="str">
-        <x:v>#2A9D8F</x:v>
-      </x:c>
-      <x:c r="M10" s="47" t="str">
-        <x:v>#E76F51</x:v>
-      </x:c>
-      <x:c r="N10" s="47" t="str">
-        <x:v>#7B4B2A</x:v>
-      </x:c>
-      <x:c r="O10" s="47" t="str">
-        <x:v>#EE964B</x:v>
-      </x:c>
-      <x:c r="P10" s="47" t="str">
-        <x:v>#7B4B2A</x:v>
-      </x:c>
-      <x:c r="Q10" s="47" t="str">
-        <x:v>#E09F3E</x:v>
-      </x:c>
-      <x:c r="R10" s="47" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
-      </x:c>
-      <x:c r="S10" s="47" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T10" s="47" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U10" s="112" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="V10" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W10" s="67" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="X10" s="37" t="str">
-        <x:v>#7B4B2A</x:v>
-      </x:c>
-      <x:c r="Y10" s="37" t="str">
-        <x:v>s3_warmup</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="44" t="str">
-        <x:v>s3_official</x:v>
-      </x:c>
-      <x:c r="B11" s="44" t="str">
-        <x:v>哈鸡米</x:v>
-      </x:c>
-      <x:c r="C11" s="64" t="n">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="D11" s="64" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E11" s="64" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F11" s="64" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G11" s="109" t="n">
-        <x:v>0.125</x:v>
-      </x:c>
-      <x:c r="H11" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I11" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J11" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K11" s="44" t="str">
-        <x:v>cute</x:v>
-      </x:c>
-      <x:c r="L11" s="44" t="str">
-        <x:v>#2A9D8F</x:v>
-      </x:c>
-      <x:c r="M11" s="44" t="str">
-        <x:v>#F5E7D0</x:v>
-      </x:c>
-      <x:c r="N11" s="44" t="str">
-        <x:v>#F5E7D0</x:v>
-      </x:c>
-      <x:c r="O11" s="44" t="str">
-        <x:v>#EE964B</x:v>
-      </x:c>
-      <x:c r="P11" s="44" t="str">
-        <x:v>#7B4B2A</x:v>
-      </x:c>
-      <x:c r="Q11" s="44" t="str">
-        <x:v>#E09F3E</x:v>
-      </x:c>
-      <x:c r="R11" s="44" t="str">
-        <x:v>先喵再说！</x:v>
-      </x:c>
-      <x:c r="S11" s="44" t="str">
-        <x:v>这鸡怎么开始猫叫了</x:v>
-      </x:c>
-      <x:c r="T11" s="44" t="str">
-        <x:v>可爱是可爱，物种有点复杂</x:v>
-      </x:c>
-      <x:c r="U11" s="112" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="V11" s="37" t="str">
-        <x:v>哈鸡米</x:v>
-      </x:c>
-      <x:c r="W11" s="67" t="n">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="X11" s="37" t="str">
-        <x:v>#F5E7D0</x:v>
-      </x:c>
-      <x:c r="Y11" s="37" t="str">
-        <x:v>s3_official</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="47" t="str">
-        <x:v>s4_warmup</x:v>
-      </x:c>
-      <x:c r="B12" s="47" t="str">
-        <x:v>杂色鸡·4号</x:v>
-      </x:c>
-      <x:c r="C12" s="65" t="n">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="D12" s="65" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E12" s="65" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F12" s="65" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G12" s="110" t="n">
-        <x:v>0.14</x:v>
-      </x:c>
-      <x:c r="H12" s="65" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I12" s="65" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J12" s="65" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K12" s="47" t="str">
-        <x:v>fierce</x:v>
-      </x:c>
-      <x:c r="L12" s="47" t="str">
-        <x:v>#264653</x:v>
-      </x:c>
-      <x:c r="M12" s="47" t="str">
-        <x:v>#FFFFFF</x:v>
-      </x:c>
-      <x:c r="N12" s="47" t="str">
-        <x:v>#2A9D8F</x:v>
-      </x:c>
-      <x:c r="O12" s="47" t="str">
-        <x:v>#EE964B</x:v>
-      </x:c>
-      <x:c r="P12" s="47" t="str">
-        <x:v>#7B4B2A</x:v>
-      </x:c>
-      <x:c r="Q12" s="47" t="str">
-        <x:v>#E09F3E</x:v>
-      </x:c>
-      <x:c r="R12" s="47" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
-      </x:c>
-      <x:c r="S12" s="47" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T12" s="47" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U12" s="112" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="V12" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W12" s="67" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="X12" s="37" t="str">
-        <x:v>#2A9D8F</x:v>
-      </x:c>
-      <x:c r="Y12" s="37" t="str">
-        <x:v>s4_warmup</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="44" t="str">
-        <x:v>s4_official</x:v>
-      </x:c>
-      <x:c r="B13" s="44" t="str">
-        <x:v>新一鸡</x:v>
-      </x:c>
-      <x:c r="C13" s="64" t="n">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D13" s="64" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E13" s="64" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F13" s="64" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G13" s="109" t="n">
-        <x:v>0.14</x:v>
-      </x:c>
-      <x:c r="H13" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I13" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J13" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K13" s="44" t="str">
-        <x:v>fierce</x:v>
-      </x:c>
-      <x:c r="L13" s="44" t="str">
-        <x:v>#264653</x:v>
-      </x:c>
-      <x:c r="M13" s="44" t="str">
-        <x:v>#3498DB</x:v>
-      </x:c>
-      <x:c r="N13" s="44" t="str">
-        <x:v>#3498DB</x:v>
-      </x:c>
-      <x:c r="O13" s="44" t="str">
-        <x:v>#EE964B</x:v>
-      </x:c>
-      <x:c r="P13" s="44" t="str">
-        <x:v>#7B4B2A</x:v>
-      </x:c>
-      <x:c r="Q13" s="44" t="str">
-        <x:v>#E09F3E</x:v>
-      </x:c>
-      <x:c r="R13" s="44" t="str">
-        <x:v>真相只有一个！</x:v>
-      </x:c>
-      <x:c r="S13" s="44" t="str">
-        <x:v>这鸡已经推理出对面要挨打</x:v>
-      </x:c>
-      <x:c r="T13" s="44" t="str">
-        <x:v>现场留下了三根鸡毛</x:v>
-      </x:c>
-      <x:c r="U13" s="112" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="V13" s="37" t="str">
-        <x:v>新一鸡</x:v>
-      </x:c>
-      <x:c r="W13" s="67" t="n">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="X13" s="37" t="str">
-        <x:v>#3498DB</x:v>
-      </x:c>
-      <x:c r="Y13" s="37" t="str">
-        <x:v>s4_official</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="30" customHeight="1">
-      <x:c r="A14" s="47" t="str">
-        <x:v>s5_warmup</x:v>
-      </x:c>
-      <x:c r="B14" s="47" t="str">
-        <x:v>杂色鸡·5号</x:v>
-      </x:c>
-      <x:c r="C14" s="65" t="n">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="D14" s="65" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E14" s="65" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F14" s="65" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G14" s="110" t="n">
-        <x:v>0.155</x:v>
-      </x:c>
-      <x:c r="H14" s="65" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I14" s="65" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J14" s="65" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K14" s="47" t="str">
-        <x:v>dumb</x:v>
-      </x:c>
-      <x:c r="L14" s="47" t="str">
-        <x:v>#E76F51</x:v>
-      </x:c>
-      <x:c r="M14" s="47" t="str">
-        <x:v>#8E44AD</x:v>
-      </x:c>
-      <x:c r="N14" s="47" t="str">
-        <x:v>#264653</x:v>
-      </x:c>
-      <x:c r="O14" s="47" t="str">
-        <x:v>#EE964B</x:v>
-      </x:c>
-      <x:c r="P14" s="47" t="str">
-        <x:v>#7B4B2A</x:v>
-      </x:c>
-      <x:c r="Q14" s="47" t="str">
-        <x:v>#E09F3E</x:v>
-      </x:c>
-      <x:c r="R14" s="47" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
-      </x:c>
-      <x:c r="S14" s="47" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T14" s="47" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U14" s="112" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="V14" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W14" s="67" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="X14" s="37" t="str">
-        <x:v>#264653</x:v>
-      </x:c>
-      <x:c r="Y14" s="37" t="str">
-        <x:v>s5_warmup</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="44" t="str">
-        <x:v>s5_official</x:v>
-      </x:c>
-      <x:c r="B15" s="44" t="str">
-        <x:v>缝纫鸡</x:v>
-      </x:c>
-      <x:c r="C15" s="64" t="n">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="D15" s="64" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E15" s="64" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="64" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G15" s="109" t="n">
-        <x:v>0.155</x:v>
-      </x:c>
-      <x:c r="H15" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I15" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J15" s="64" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K15" s="44" t="str">
-        <x:v>dumb</x:v>
-      </x:c>
-      <x:c r="L15" s="44" t="str">
-        <x:v>#E76F51</x:v>
-      </x:c>
-      <x:c r="M15" s="44" t="str">
-        <x:v>#AA77BB</x:v>
-      </x:c>
-      <x:c r="N15" s="44" t="str">
-        <x:v>#AA77BB</x:v>
-      </x:c>
-      <x:c r="O15" s="44" t="str">
-        <x:v>#EE964B</x:v>
-      </x:c>
-      <x:c r="P15" s="44" t="str">
-        <x:v>#7B4B2A</x:v>
-      </x:c>
-      <x:c r="Q15" s="44" t="str">
-        <x:v>#E09F3E</x:v>
-      </x:c>
-      <x:c r="R15" s="44" t="str">
-        <x:v>大针宽线，安排上了！</x:v>
-      </x:c>
-      <x:c r="S15" s="44" t="str">
-        <x:v>这根线它又长又宽</x:v>
-      </x:c>
-      <x:c r="T15" s="44" t="str">
-        <x:v>大针宽线，安排上了</x:v>
-      </x:c>
-      <x:c r="U15" s="112" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="V15" s="37" t="str">
-        <x:v>缝纫鸡</x:v>
-      </x:c>
-      <x:c r="W15" s="67" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="X15" s="37" t="str">
-        <x:v>#AA77BB</x:v>
-      </x:c>
-      <x:c r="Y15" s="37" t="str">
-        <x:v>s5_official</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="30" customHeight="1">
-      <x:c r="A16" s="50" t="str">
+      <x:c r="R16" s="37" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="S16" s="37" t="str">
+        <x:v>坤坤鸡</x:v>
+      </x:c>
+      <x:c r="T16" s="37" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="U16" s="37" t="str">
+        <x:v>#111111</x:v>
+      </x:c>
+      <x:c r="V16" s="37" t="str">
         <x:v>kun_boss</x:v>
       </x:c>
-      <x:c r="B16" s="50" t="str">
-        <x:v>鸡王坤坤</x:v>
-      </x:c>
-      <x:c r="C16" s="66" t="n">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="D16" s="66" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E16" s="66" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F16" s="66" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G16" s="111" t="n">
-        <x:v>0.17</x:v>
-      </x:c>
-      <x:c r="H16" s="66" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I16" s="66" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="J16" s="66" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K16" s="50" t="str">
-        <x:v>proud</x:v>
-      </x:c>
-      <x:c r="L16" s="50" t="str">
-        <x:v>#FF4D6D</x:v>
-      </x:c>
-      <x:c r="M16" s="50" t="str">
-        <x:v>#222222</x:v>
-      </x:c>
-      <x:c r="N16" s="50" t="str">
-        <x:v>#111111</x:v>
-      </x:c>
-      <x:c r="O16" s="50" t="str">
-        <x:v>#444444</x:v>
-      </x:c>
-      <x:c r="P16" s="50" t="str">
-        <x:v>#FFD60A</x:v>
-      </x:c>
-      <x:c r="Q16" s="50" t="str">
-        <x:v>#E09F3E</x:v>
-      </x:c>
-      <x:c r="R16" s="50" t="str">
-        <x:v>鸡你太美</x:v>
-      </x:c>
-      <x:c r="S16" s="50" t="str">
-        <x:v>唱、跳、Rap、篮球……再加一脚蹬！</x:v>
-      </x:c>
-      <x:c r="T16" s="50" t="str">
-        <x:v>坤坤在此，谁敢争锋！</x:v>
-      </x:c>
-      <x:c r="U16" s="112" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="V16" s="37" t="str">
-        <x:v>坤坤鸡</x:v>
-      </x:c>
-      <x:c r="W16" s="67" t="n">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="X16" s="37" t="str">
-        <x:v>#111111</x:v>
-      </x:c>
-      <x:c r="Y16" s="37" t="str">
-        <x:v>kun_boss</x:v>
-      </x:c>
+      <x:c r="W16" s="37" t="str">
+        <x:v>enemy_kun_boss</x:v>
+      </x:c>
+      <x:c r="X16"/>
+      <x:c r="Y16"/>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
       <x:c r="A17" s="37" t="str">
@@ -9752,28 +11433,28 @@
       <x:c r="B17" s="37" t="str">
         <x:v>金颈鸡</x:v>
       </x:c>
-      <x:c r="C17" s="67" t="n">
+      <x:c r="C17" s="37" t="n">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D17" s="67" t="n">
+      <x:c r="D17" s="37" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E17" s="67" t="n">
+      <x:c r="E17" s="37" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F17" s="67" t="n">
+      <x:c r="F17" s="37" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G17" s="112" t="n">
+      <x:c r="G17" s="37" t="n">
         <x:v>0.095</x:v>
       </x:c>
-      <x:c r="H17" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I17" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J17" s="67" t="n">
+      <x:c r="H17" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I17" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J17" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K17" s="37" t="str">
@@ -9797,30 +11478,26 @@
       <x:c r="Q17" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R17" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R17" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S17" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T17" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U17" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T17" s="37" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="U17" s="37" t="str">
+        <x:v>#F4D35E</x:v>
       </x:c>
       <x:c r="V17" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W17" s="67" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="X17" s="37" t="str">
-        <x:v>#F4D35E</x:v>
-      </x:c>
-      <x:c r="Y17" s="37" t="str">
         <x:v>warmup_1</x:v>
       </x:c>
+      <x:c r="W17" s="37" t="str">
+        <x:v>enemy_s1_warmup_1</x:v>
+      </x:c>
+      <x:c r="X17"/>
+      <x:c r="Y17"/>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
       <x:c r="A18" s="37" t="str">
@@ -9829,28 +11506,28 @@
       <x:c r="B18" s="37" t="str">
         <x:v>细脖麻鸡</x:v>
       </x:c>
-      <x:c r="C18" s="67" t="n">
+      <x:c r="C18" s="37" t="n">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D18" s="67" t="n">
+      <x:c r="D18" s="37" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E18" s="67" t="n">
+      <x:c r="E18" s="37" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F18" s="67" t="n">
+      <x:c r="F18" s="37" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G18" s="112" t="n">
+      <x:c r="G18" s="37" t="n">
         <x:v>0.095</x:v>
       </x:c>
-      <x:c r="H18" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I18" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J18" s="67" t="n">
+      <x:c r="H18" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I18" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K18" s="37" t="str">
@@ -9874,30 +11551,26 @@
       <x:c r="Q18" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R18" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R18" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S18" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T18" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U18" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T18" s="37" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="U18" s="37" t="str">
+        <x:v>#F4D35E</x:v>
       </x:c>
       <x:c r="V18" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W18" s="67" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="X18" s="37" t="str">
-        <x:v>#F4D35E</x:v>
-      </x:c>
-      <x:c r="Y18" s="37" t="str">
         <x:v>warmup_2</x:v>
       </x:c>
+      <x:c r="W18" s="37" t="str">
+        <x:v>enemy_s1_warmup_2</x:v>
+      </x:c>
+      <x:c r="X18"/>
+      <x:c r="Y18"/>
     </x:row>
     <x:row r="19" ht="30" customHeight="1">
       <x:c r="A19" s="37" t="str">
@@ -9906,28 +11579,28 @@
       <x:c r="B19" s="37" t="str">
         <x:v>黄羽鸡</x:v>
       </x:c>
-      <x:c r="C19" s="67" t="n">
+      <x:c r="C19" s="37" t="n">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D19" s="67" t="n">
+      <x:c r="D19" s="37" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E19" s="67" t="n">
+      <x:c r="E19" s="37" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F19" s="67" t="n">
+      <x:c r="F19" s="37" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G19" s="112" t="n">
+      <x:c r="G19" s="37" t="n">
         <x:v>0.095</x:v>
       </x:c>
-      <x:c r="H19" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I19" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J19" s="67" t="n">
+      <x:c r="H19" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I19" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J19" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K19" s="37" t="str">
@@ -9951,30 +11624,26 @@
       <x:c r="Q19" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R19" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R19" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S19" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T19" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U19" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T19" s="37" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="U19" s="37" t="str">
+        <x:v>#F4D35E</x:v>
       </x:c>
       <x:c r="V19" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W19" s="67" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="X19" s="37" t="str">
-        <x:v>#F4D35E</x:v>
-      </x:c>
-      <x:c r="Y19" s="37" t="str">
         <x:v>warmup_3</x:v>
       </x:c>
+      <x:c r="W19" s="37" t="str">
+        <x:v>enemy_s1_warmup_3</x:v>
+      </x:c>
+      <x:c r="X19"/>
+      <x:c r="Y19"/>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
       <x:c r="A20" s="37" t="str">
@@ -9983,28 +11652,28 @@
       <x:c r="B20" s="37" t="str">
         <x:v>红冠青鸡</x:v>
       </x:c>
-      <x:c r="C20" s="67" t="n">
+      <x:c r="C20" s="37" t="n">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D20" s="67" t="n">
+      <x:c r="D20" s="37" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E20" s="67" t="n">
+      <x:c r="E20" s="37" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F20" s="67" t="n">
+      <x:c r="F20" s="37" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G20" s="112" t="n">
+      <x:c r="G20" s="37" t="n">
         <x:v>0.095</x:v>
       </x:c>
-      <x:c r="H20" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I20" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J20" s="67" t="n">
+      <x:c r="H20" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I20" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J20" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K20" s="37" t="str">
@@ -10028,30 +11697,26 @@
       <x:c r="Q20" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R20" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R20" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S20" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T20" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U20" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T20" s="37" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="U20" s="37" t="str">
+        <x:v>#F4D35E</x:v>
       </x:c>
       <x:c r="V20" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W20" s="67" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="X20" s="37" t="str">
-        <x:v>#F4D35E</x:v>
-      </x:c>
-      <x:c r="Y20" s="37" t="str">
         <x:v>warmup_4</x:v>
       </x:c>
+      <x:c r="W20" s="37" t="str">
+        <x:v>enemy_s1_warmup_4</x:v>
+      </x:c>
+      <x:c r="X20"/>
+      <x:c r="Y20"/>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
       <x:c r="A21" s="37" t="str">
@@ -10060,28 +11725,28 @@
       <x:c r="B21" s="37" t="str">
         <x:v>黑羽鸡</x:v>
       </x:c>
-      <x:c r="C21" s="67" t="n">
+      <x:c r="C21" s="37" t="n">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D21" s="67" t="n">
+      <x:c r="D21" s="37" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E21" s="67" t="n">
+      <x:c r="E21" s="37" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F21" s="67" t="n">
+      <x:c r="F21" s="37" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G21" s="112" t="n">
+      <x:c r="G21" s="37" t="n">
         <x:v>0.095</x:v>
       </x:c>
-      <x:c r="H21" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I21" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J21" s="67" t="n">
+      <x:c r="H21" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I21" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J21" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K21" s="37" t="str">
@@ -10105,30 +11770,26 @@
       <x:c r="Q21" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R21" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R21" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S21" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T21" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U21" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T21" s="37" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="U21" s="37" t="str">
+        <x:v>#F4D35E</x:v>
       </x:c>
       <x:c r="V21" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W21" s="67" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="X21" s="37" t="str">
-        <x:v>#F4D35E</x:v>
-      </x:c>
-      <x:c r="Y21" s="37" t="str">
         <x:v>warmup_5</x:v>
       </x:c>
+      <x:c r="W21" s="37" t="str">
+        <x:v>enemy_s1_warmup_5</x:v>
+      </x:c>
+      <x:c r="X21"/>
+      <x:c r="Y21"/>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
       <x:c r="A22" s="37" t="str">
@@ -10137,28 +11798,28 @@
       <x:c r="B22" s="37" t="str">
         <x:v>墨绿鸡</x:v>
       </x:c>
-      <x:c r="C22" s="67" t="n">
+      <x:c r="C22" s="37" t="n">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D22" s="67" t="n">
+      <x:c r="D22" s="37" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E22" s="67" t="n">
+      <x:c r="E22" s="37" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F22" s="67" t="n">
+      <x:c r="F22" s="37" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G22" s="112" t="n">
+      <x:c r="G22" s="37" t="n">
         <x:v>0.11</x:v>
       </x:c>
-      <x:c r="H22" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I22" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J22" s="67" t="n">
+      <x:c r="H22" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I22" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J22" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K22" s="37" t="str">
@@ -10182,30 +11843,26 @@
       <x:c r="Q22" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R22" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R22" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S22" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T22" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U22" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T22" s="37" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="U22" s="37" t="str">
+        <x:v>#EE964B</x:v>
       </x:c>
       <x:c r="V22" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W22" s="67" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="X22" s="37" t="str">
-        <x:v>#EE964B</x:v>
-      </x:c>
-      <x:c r="Y22" s="37" t="str">
         <x:v>warmup_6</x:v>
       </x:c>
+      <x:c r="W22" s="37" t="str">
+        <x:v>enemy_s2_warmup_1</x:v>
+      </x:c>
+      <x:c r="X22"/>
+      <x:c r="Y22"/>
     </x:row>
     <x:row r="23" ht="30" customHeight="1">
       <x:c r="A23" s="37" t="str">
@@ -10214,28 +11871,28 @@
       <x:c r="B23" s="37" t="str">
         <x:v>乌金鸡</x:v>
       </x:c>
-      <x:c r="C23" s="67" t="n">
+      <x:c r="C23" s="37" t="n">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D23" s="67" t="n">
+      <x:c r="D23" s="37" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E23" s="67" t="n">
+      <x:c r="E23" s="37" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F23" s="67" t="n">
+      <x:c r="F23" s="37" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G23" s="112" t="n">
+      <x:c r="G23" s="37" t="n">
         <x:v>0.11</x:v>
       </x:c>
-      <x:c r="H23" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I23" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J23" s="67" t="n">
+      <x:c r="H23" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I23" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J23" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K23" s="37" t="str">
@@ -10259,30 +11916,26 @@
       <x:c r="Q23" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R23" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R23" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S23" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T23" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U23" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T23" s="37" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="U23" s="37" t="str">
+        <x:v>#EE964B</x:v>
       </x:c>
       <x:c r="V23" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W23" s="67" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="X23" s="37" t="str">
-        <x:v>#EE964B</x:v>
-      </x:c>
-      <x:c r="Y23" s="37" t="str">
         <x:v>warmup_7</x:v>
       </x:c>
+      <x:c r="W23" s="37" t="str">
+        <x:v>enemy_s2_warmup_2</x:v>
+      </x:c>
+      <x:c r="X23"/>
+      <x:c r="Y23"/>
     </x:row>
     <x:row r="24" ht="30" customHeight="1">
       <x:c r="A24" s="37" t="str">
@@ -10291,28 +11944,28 @@
       <x:c r="B24" s="37" t="str">
         <x:v>斑点鸡</x:v>
       </x:c>
-      <x:c r="C24" s="67" t="n">
+      <x:c r="C24" s="37" t="n">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D24" s="67" t="n">
+      <x:c r="D24" s="37" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E24" s="67" t="n">
+      <x:c r="E24" s="37" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F24" s="67" t="n">
+      <x:c r="F24" s="37" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G24" s="112" t="n">
+      <x:c r="G24" s="37" t="n">
         <x:v>0.11</x:v>
       </x:c>
-      <x:c r="H24" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I24" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J24" s="67" t="n">
+      <x:c r="H24" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I24" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J24" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K24" s="37" t="str">
@@ -10336,30 +11989,26 @@
       <x:c r="Q24" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R24" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R24" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S24" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T24" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U24" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T24" s="37" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="U24" s="37" t="str">
+        <x:v>#EE964B</x:v>
       </x:c>
       <x:c r="V24" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W24" s="67" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="X24" s="37" t="str">
-        <x:v>#EE964B</x:v>
-      </x:c>
-      <x:c r="Y24" s="37" t="str">
         <x:v>warmup_8</x:v>
       </x:c>
+      <x:c r="W24" s="37" t="str">
+        <x:v>enemy_s2_warmup_3</x:v>
+      </x:c>
+      <x:c r="X24"/>
+      <x:c r="Y24"/>
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
       <x:c r="A25" s="37" t="str">
@@ -10368,28 +12017,28 @@
       <x:c r="B25" s="37" t="str">
         <x:v>长颈斗鸡</x:v>
       </x:c>
-      <x:c r="C25" s="67" t="n">
+      <x:c r="C25" s="37" t="n">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D25" s="67" t="n">
+      <x:c r="D25" s="37" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E25" s="67" t="n">
+      <x:c r="E25" s="37" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F25" s="67" t="n">
+      <x:c r="F25" s="37" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G25" s="112" t="n">
+      <x:c r="G25" s="37" t="n">
         <x:v>0.11</x:v>
       </x:c>
-      <x:c r="H25" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I25" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J25" s="67" t="n">
+      <x:c r="H25" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I25" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J25" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K25" s="37" t="str">
@@ -10413,30 +12062,26 @@
       <x:c r="Q25" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R25" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R25" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S25" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T25" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U25" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T25" s="37" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="U25" s="37" t="str">
+        <x:v>#EE964B</x:v>
       </x:c>
       <x:c r="V25" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W25" s="67" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="X25" s="37" t="str">
-        <x:v>#EE964B</x:v>
-      </x:c>
-      <x:c r="Y25" s="37" t="str">
         <x:v>warmup_9</x:v>
       </x:c>
+      <x:c r="W25" s="37" t="str">
+        <x:v>enemy_s2_warmup_4</x:v>
+      </x:c>
+      <x:c r="X25"/>
+      <x:c r="Y25"/>
     </x:row>
     <x:row r="26" ht="30" customHeight="1">
       <x:c r="A26" s="37" t="str">
@@ -10445,28 +12090,28 @@
       <x:c r="B26" s="37" t="str">
         <x:v>赤颈鸡</x:v>
       </x:c>
-      <x:c r="C26" s="67" t="n">
+      <x:c r="C26" s="37" t="n">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D26" s="67" t="n">
+      <x:c r="D26" s="37" t="n">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E26" s="67" t="n">
+      <x:c r="E26" s="37" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F26" s="67" t="n">
+      <x:c r="F26" s="37" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G26" s="112" t="n">
+      <x:c r="G26" s="37" t="n">
         <x:v>0.11</x:v>
       </x:c>
-      <x:c r="H26" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I26" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J26" s="67" t="n">
+      <x:c r="H26" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I26" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J26" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K26" s="37" t="str">
@@ -10490,30 +12135,26 @@
       <x:c r="Q26" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R26" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R26" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S26" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T26" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U26" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T26" s="37" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="U26" s="37" t="str">
+        <x:v>#EE964B</x:v>
       </x:c>
       <x:c r="V26" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W26" s="67" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="X26" s="37" t="str">
-        <x:v>#EE964B</x:v>
-      </x:c>
-      <x:c r="Y26" s="37" t="str">
         <x:v>warmup_10</x:v>
       </x:c>
+      <x:c r="W26" s="37" t="str">
+        <x:v>enemy_s2_warmup_5</x:v>
+      </x:c>
+      <x:c r="X26"/>
+      <x:c r="Y26"/>
     </x:row>
     <x:row r="27" ht="30" customHeight="1">
       <x:c r="A27" s="37" t="str">
@@ -10522,28 +12163,28 @@
       <x:c r="B27" s="37" t="str">
         <x:v>浅羽麻鸡</x:v>
       </x:c>
-      <x:c r="C27" s="67" t="n">
+      <x:c r="C27" s="37" t="n">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="D27" s="67" t="n">
+      <x:c r="D27" s="37" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E27" s="67" t="n">
+      <x:c r="E27" s="37" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F27" s="67" t="n">
+      <x:c r="F27" s="37" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G27" s="112" t="n">
+      <x:c r="G27" s="37" t="n">
         <x:v>0.125</x:v>
       </x:c>
-      <x:c r="H27" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I27" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J27" s="67" t="n">
+      <x:c r="H27" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I27" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J27" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K27" s="37" t="str">
@@ -10567,30 +12208,26 @@
       <x:c r="Q27" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R27" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R27" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S27" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T27" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U27" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T27" s="37" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="U27" s="37" t="str">
+        <x:v>#7B4B2A</x:v>
       </x:c>
       <x:c r="V27" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W27" s="67" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="X27" s="37" t="str">
-        <x:v>#7B4B2A</x:v>
-      </x:c>
-      <x:c r="Y27" s="37" t="str">
         <x:v>warmup_11</x:v>
       </x:c>
+      <x:c r="W27" s="37" t="str">
+        <x:v>enemy_s3_warmup_1</x:v>
+      </x:c>
+      <x:c r="X27"/>
+      <x:c r="Y27"/>
     </x:row>
     <x:row r="28" ht="30" customHeight="1">
       <x:c r="A28" s="37" t="str">
@@ -10599,28 +12236,28 @@
       <x:c r="B28" s="37" t="str">
         <x:v>蓬尾黄鸡</x:v>
       </x:c>
-      <x:c r="C28" s="67" t="n">
+      <x:c r="C28" s="37" t="n">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="D28" s="67" t="n">
+      <x:c r="D28" s="37" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E28" s="67" t="n">
+      <x:c r="E28" s="37" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F28" s="67" t="n">
+      <x:c r="F28" s="37" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G28" s="112" t="n">
+      <x:c r="G28" s="37" t="n">
         <x:v>0.125</x:v>
       </x:c>
-      <x:c r="H28" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I28" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J28" s="67" t="n">
+      <x:c r="H28" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I28" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J28" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K28" s="37" t="str">
@@ -10644,30 +12281,26 @@
       <x:c r="Q28" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R28" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R28" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S28" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T28" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U28" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T28" s="37" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="U28" s="37" t="str">
+        <x:v>#7B4B2A</x:v>
       </x:c>
       <x:c r="V28" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W28" s="67" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="X28" s="37" t="str">
-        <x:v>#7B4B2A</x:v>
-      </x:c>
-      <x:c r="Y28" s="37" t="str">
         <x:v>warmup_12</x:v>
       </x:c>
+      <x:c r="W28" s="37" t="str">
+        <x:v>enemy_s3_warmup_2</x:v>
+      </x:c>
+      <x:c r="X28"/>
+      <x:c r="Y28"/>
     </x:row>
     <x:row r="29" ht="30" customHeight="1">
       <x:c r="A29" s="37" t="str">
@@ -10676,28 +12309,28 @@
       <x:c r="B29" s="37" t="str">
         <x:v>金颈鸡</x:v>
       </x:c>
-      <x:c r="C29" s="67" t="n">
+      <x:c r="C29" s="37" t="n">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="D29" s="67" t="n">
+      <x:c r="D29" s="37" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E29" s="67" t="n">
+      <x:c r="E29" s="37" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F29" s="67" t="n">
+      <x:c r="F29" s="37" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G29" s="112" t="n">
+      <x:c r="G29" s="37" t="n">
         <x:v>0.125</x:v>
       </x:c>
-      <x:c r="H29" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I29" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J29" s="67" t="n">
+      <x:c r="H29" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I29" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J29" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K29" s="37" t="str">
@@ -10721,30 +12354,26 @@
       <x:c r="Q29" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R29" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R29" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S29" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T29" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U29" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T29" s="37" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="U29" s="37" t="str">
+        <x:v>#7B4B2A</x:v>
       </x:c>
       <x:c r="V29" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W29" s="67" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="X29" s="37" t="str">
-        <x:v>#7B4B2A</x:v>
-      </x:c>
-      <x:c r="Y29" s="37" t="str">
         <x:v>warmup_1</x:v>
       </x:c>
+      <x:c r="W29" s="37" t="str">
+        <x:v>enemy_s3_warmup_3</x:v>
+      </x:c>
+      <x:c r="X29"/>
+      <x:c r="Y29"/>
     </x:row>
     <x:row r="30" ht="30" customHeight="1">
       <x:c r="A30" s="37" t="str">
@@ -10753,28 +12382,28 @@
       <x:c r="B30" s="37" t="str">
         <x:v>细脖麻鸡</x:v>
       </x:c>
-      <x:c r="C30" s="67" t="n">
+      <x:c r="C30" s="37" t="n">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="D30" s="67" t="n">
+      <x:c r="D30" s="37" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E30" s="67" t="n">
+      <x:c r="E30" s="37" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F30" s="67" t="n">
+      <x:c r="F30" s="37" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G30" s="112" t="n">
+      <x:c r="G30" s="37" t="n">
         <x:v>0.125</x:v>
       </x:c>
-      <x:c r="H30" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I30" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J30" s="67" t="n">
+      <x:c r="H30" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I30" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J30" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K30" s="37" t="str">
@@ -10798,30 +12427,26 @@
       <x:c r="Q30" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R30" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R30" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S30" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T30" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U30" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T30" s="37" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="U30" s="37" t="str">
+        <x:v>#7B4B2A</x:v>
       </x:c>
       <x:c r="V30" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W30" s="67" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="X30" s="37" t="str">
-        <x:v>#7B4B2A</x:v>
-      </x:c>
-      <x:c r="Y30" s="37" t="str">
         <x:v>warmup_2</x:v>
       </x:c>
+      <x:c r="W30" s="37" t="str">
+        <x:v>enemy_s3_warmup_4</x:v>
+      </x:c>
+      <x:c r="X30"/>
+      <x:c r="Y30"/>
     </x:row>
     <x:row r="31" ht="30" customHeight="1">
       <x:c r="A31" s="37" t="str">
@@ -10830,28 +12455,28 @@
       <x:c r="B31" s="37" t="str">
         <x:v>黄羽鸡</x:v>
       </x:c>
-      <x:c r="C31" s="67" t="n">
+      <x:c r="C31" s="37" t="n">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="D31" s="67" t="n">
+      <x:c r="D31" s="37" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E31" s="67" t="n">
+      <x:c r="E31" s="37" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F31" s="67" t="n">
+      <x:c r="F31" s="37" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G31" s="112" t="n">
+      <x:c r="G31" s="37" t="n">
         <x:v>0.125</x:v>
       </x:c>
-      <x:c r="H31" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I31" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J31" s="67" t="n">
+      <x:c r="H31" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I31" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J31" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K31" s="37" t="str">
@@ -10875,30 +12500,26 @@
       <x:c r="Q31" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R31" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R31" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S31" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T31" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U31" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T31" s="37" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="U31" s="37" t="str">
+        <x:v>#7B4B2A</x:v>
       </x:c>
       <x:c r="V31" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W31" s="67" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="X31" s="37" t="str">
-        <x:v>#7B4B2A</x:v>
-      </x:c>
-      <x:c r="Y31" s="37" t="str">
         <x:v>warmup_3</x:v>
       </x:c>
+      <x:c r="W31" s="37" t="str">
+        <x:v>enemy_s3_warmup_5</x:v>
+      </x:c>
+      <x:c r="X31"/>
+      <x:c r="Y31"/>
     </x:row>
     <x:row r="32" ht="30" customHeight="1">
       <x:c r="A32" s="37" t="str">
@@ -10907,28 +12528,28 @@
       <x:c r="B32" s="37" t="str">
         <x:v>红冠青鸡</x:v>
       </x:c>
-      <x:c r="C32" s="67" t="n">
+      <x:c r="C32" s="37" t="n">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="D32" s="67" t="n">
+      <x:c r="D32" s="37" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E32" s="67" t="n">
+      <x:c r="E32" s="37" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F32" s="67" t="n">
+      <x:c r="F32" s="37" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G32" s="112" t="n">
+      <x:c r="G32" s="37" t="n">
         <x:v>0.14</x:v>
       </x:c>
-      <x:c r="H32" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I32" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J32" s="67" t="n">
+      <x:c r="H32" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I32" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J32" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K32" s="37" t="str">
@@ -10952,30 +12573,26 @@
       <x:c r="Q32" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R32" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R32" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S32" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T32" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U32" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T32" s="37" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="U32" s="37" t="str">
+        <x:v>#2A9D8F</x:v>
       </x:c>
       <x:c r="V32" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W32" s="67" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="X32" s="37" t="str">
-        <x:v>#2A9D8F</x:v>
-      </x:c>
-      <x:c r="Y32" s="37" t="str">
         <x:v>warmup_4</x:v>
       </x:c>
+      <x:c r="W32" s="37" t="str">
+        <x:v>enemy_s4_warmup_1</x:v>
+      </x:c>
+      <x:c r="X32"/>
+      <x:c r="Y32"/>
     </x:row>
     <x:row r="33" ht="30" customHeight="1">
       <x:c r="A33" s="37" t="str">
@@ -10984,28 +12601,28 @@
       <x:c r="B33" s="37" t="str">
         <x:v>黑羽鸡</x:v>
       </x:c>
-      <x:c r="C33" s="67" t="n">
+      <x:c r="C33" s="37" t="n">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="D33" s="67" t="n">
+      <x:c r="D33" s="37" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E33" s="67" t="n">
+      <x:c r="E33" s="37" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F33" s="67" t="n">
+      <x:c r="F33" s="37" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G33" s="112" t="n">
+      <x:c r="G33" s="37" t="n">
         <x:v>0.14</x:v>
       </x:c>
-      <x:c r="H33" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I33" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J33" s="67" t="n">
+      <x:c r="H33" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I33" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J33" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K33" s="37" t="str">
@@ -11029,30 +12646,26 @@
       <x:c r="Q33" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R33" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R33" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S33" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T33" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U33" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T33" s="37" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="U33" s="37" t="str">
+        <x:v>#2A9D8F</x:v>
       </x:c>
       <x:c r="V33" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W33" s="67" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="X33" s="37" t="str">
-        <x:v>#2A9D8F</x:v>
-      </x:c>
-      <x:c r="Y33" s="37" t="str">
         <x:v>warmup_5</x:v>
       </x:c>
+      <x:c r="W33" s="37" t="str">
+        <x:v>enemy_s4_warmup_2</x:v>
+      </x:c>
+      <x:c r="X33"/>
+      <x:c r="Y33"/>
     </x:row>
     <x:row r="34" ht="30" customHeight="1">
       <x:c r="A34" s="37" t="str">
@@ -11061,28 +12674,28 @@
       <x:c r="B34" s="37" t="str">
         <x:v>墨绿鸡</x:v>
       </x:c>
-      <x:c r="C34" s="67" t="n">
+      <x:c r="C34" s="37" t="n">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="D34" s="67" t="n">
+      <x:c r="D34" s="37" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E34" s="67" t="n">
+      <x:c r="E34" s="37" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F34" s="67" t="n">
+      <x:c r="F34" s="37" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G34" s="112" t="n">
+      <x:c r="G34" s="37" t="n">
         <x:v>0.14</x:v>
       </x:c>
-      <x:c r="H34" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I34" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J34" s="67" t="n">
+      <x:c r="H34" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I34" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J34" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K34" s="37" t="str">
@@ -11106,30 +12719,26 @@
       <x:c r="Q34" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R34" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R34" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S34" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T34" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U34" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T34" s="37" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="U34" s="37" t="str">
+        <x:v>#2A9D8F</x:v>
       </x:c>
       <x:c r="V34" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W34" s="67" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="X34" s="37" t="str">
-        <x:v>#2A9D8F</x:v>
-      </x:c>
-      <x:c r="Y34" s="37" t="str">
         <x:v>warmup_6</x:v>
       </x:c>
+      <x:c r="W34" s="37" t="str">
+        <x:v>enemy_s4_warmup_3</x:v>
+      </x:c>
+      <x:c r="X34"/>
+      <x:c r="Y34"/>
     </x:row>
     <x:row r="35" ht="30" customHeight="1">
       <x:c r="A35" s="37" t="str">
@@ -11138,28 +12747,28 @@
       <x:c r="B35" s="37" t="str">
         <x:v>乌金鸡</x:v>
       </x:c>
-      <x:c r="C35" s="67" t="n">
+      <x:c r="C35" s="37" t="n">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="D35" s="67" t="n">
+      <x:c r="D35" s="37" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E35" s="67" t="n">
+      <x:c r="E35" s="37" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F35" s="67" t="n">
+      <x:c r="F35" s="37" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G35" s="112" t="n">
+      <x:c r="G35" s="37" t="n">
         <x:v>0.14</x:v>
       </x:c>
-      <x:c r="H35" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I35" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J35" s="67" t="n">
+      <x:c r="H35" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I35" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J35" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K35" s="37" t="str">
@@ -11183,30 +12792,26 @@
       <x:c r="Q35" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R35" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R35" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S35" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T35" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U35" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T35" s="37" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="U35" s="37" t="str">
+        <x:v>#2A9D8F</x:v>
       </x:c>
       <x:c r="V35" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W35" s="67" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="X35" s="37" t="str">
-        <x:v>#2A9D8F</x:v>
-      </x:c>
-      <x:c r="Y35" s="37" t="str">
         <x:v>warmup_7</x:v>
       </x:c>
+      <x:c r="W35" s="37" t="str">
+        <x:v>enemy_s4_warmup_4</x:v>
+      </x:c>
+      <x:c r="X35"/>
+      <x:c r="Y35"/>
     </x:row>
     <x:row r="36" ht="30" customHeight="1">
       <x:c r="A36" s="37" t="str">
@@ -11215,28 +12820,28 @@
       <x:c r="B36" s="37" t="str">
         <x:v>斑点鸡</x:v>
       </x:c>
-      <x:c r="C36" s="67" t="n">
+      <x:c r="C36" s="37" t="n">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="D36" s="67" t="n">
+      <x:c r="D36" s="37" t="n">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E36" s="67" t="n">
+      <x:c r="E36" s="37" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F36" s="67" t="n">
+      <x:c r="F36" s="37" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G36" s="112" t="n">
+      <x:c r="G36" s="37" t="n">
         <x:v>0.14</x:v>
       </x:c>
-      <x:c r="H36" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I36" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J36" s="67" t="n">
+      <x:c r="H36" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I36" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J36" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K36" s="37" t="str">
@@ -11260,30 +12865,26 @@
       <x:c r="Q36" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R36" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R36" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S36" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T36" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U36" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T36" s="37" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="U36" s="37" t="str">
+        <x:v>#2A9D8F</x:v>
       </x:c>
       <x:c r="V36" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W36" s="67" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="X36" s="37" t="str">
-        <x:v>#2A9D8F</x:v>
-      </x:c>
-      <x:c r="Y36" s="37" t="str">
         <x:v>warmup_8</x:v>
       </x:c>
+      <x:c r="W36" s="37" t="str">
+        <x:v>enemy_s4_warmup_5</x:v>
+      </x:c>
+      <x:c r="X36"/>
+      <x:c r="Y36"/>
     </x:row>
     <x:row r="37" ht="30" customHeight="1">
       <x:c r="A37" s="37" t="str">
@@ -11292,28 +12893,28 @@
       <x:c r="B37" s="37" t="str">
         <x:v>长颈斗鸡</x:v>
       </x:c>
-      <x:c r="C37" s="67" t="n">
+      <x:c r="C37" s="37" t="n">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="D37" s="67" t="n">
+      <x:c r="D37" s="37" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E37" s="67" t="n">
+      <x:c r="E37" s="37" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F37" s="67" t="n">
+      <x:c r="F37" s="37" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G37" s="112" t="n">
+      <x:c r="G37" s="37" t="n">
         <x:v>0.155</x:v>
       </x:c>
-      <x:c r="H37" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I37" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J37" s="67" t="n">
+      <x:c r="H37" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I37" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J37" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K37" s="37" t="str">
@@ -11337,30 +12938,26 @@
       <x:c r="Q37" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R37" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R37" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S37" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T37" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U37" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T37" s="37" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="U37" s="37" t="str">
+        <x:v>#264653</x:v>
       </x:c>
       <x:c r="V37" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W37" s="67" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="X37" s="37" t="str">
-        <x:v>#264653</x:v>
-      </x:c>
-      <x:c r="Y37" s="37" t="str">
         <x:v>warmup_9</x:v>
       </x:c>
+      <x:c r="W37" s="37" t="str">
+        <x:v>enemy_s5_warmup_1</x:v>
+      </x:c>
+      <x:c r="X37"/>
+      <x:c r="Y37"/>
     </x:row>
     <x:row r="38" ht="30" customHeight="1">
       <x:c r="A38" s="37" t="str">
@@ -11369,28 +12966,28 @@
       <x:c r="B38" s="37" t="str">
         <x:v>赤颈鸡</x:v>
       </x:c>
-      <x:c r="C38" s="67" t="n">
+      <x:c r="C38" s="37" t="n">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="D38" s="67" t="n">
+      <x:c r="D38" s="37" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E38" s="67" t="n">
+      <x:c r="E38" s="37" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F38" s="67" t="n">
+      <x:c r="F38" s="37" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G38" s="112" t="n">
+      <x:c r="G38" s="37" t="n">
         <x:v>0.155</x:v>
       </x:c>
-      <x:c r="H38" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I38" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J38" s="67" t="n">
+      <x:c r="H38" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I38" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J38" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K38" s="37" t="str">
@@ -11414,30 +13011,26 @@
       <x:c r="Q38" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R38" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R38" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S38" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T38" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U38" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T38" s="37" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="U38" s="37" t="str">
+        <x:v>#264653</x:v>
       </x:c>
       <x:c r="V38" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W38" s="67" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="X38" s="37" t="str">
-        <x:v>#264653</x:v>
-      </x:c>
-      <x:c r="Y38" s="37" t="str">
         <x:v>warmup_10</x:v>
       </x:c>
+      <x:c r="W38" s="37" t="str">
+        <x:v>enemy_s5_warmup_2</x:v>
+      </x:c>
+      <x:c r="X38"/>
+      <x:c r="Y38"/>
     </x:row>
     <x:row r="39" ht="30" customHeight="1">
       <x:c r="A39" s="37" t="str">
@@ -11446,28 +13039,28 @@
       <x:c r="B39" s="37" t="str">
         <x:v>浅羽麻鸡</x:v>
       </x:c>
-      <x:c r="C39" s="67" t="n">
+      <x:c r="C39" s="37" t="n">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="D39" s="67" t="n">
+      <x:c r="D39" s="37" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E39" s="67" t="n">
+      <x:c r="E39" s="37" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F39" s="67" t="n">
+      <x:c r="F39" s="37" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G39" s="112" t="n">
+      <x:c r="G39" s="37" t="n">
         <x:v>0.155</x:v>
       </x:c>
-      <x:c r="H39" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I39" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J39" s="67" t="n">
+      <x:c r="H39" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I39" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J39" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K39" s="37" t="str">
@@ -11491,30 +13084,26 @@
       <x:c r="Q39" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R39" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R39" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S39" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T39" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U39" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T39" s="37" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="U39" s="37" t="str">
+        <x:v>#264653</x:v>
       </x:c>
       <x:c r="V39" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W39" s="67" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="X39" s="37" t="str">
-        <x:v>#264653</x:v>
-      </x:c>
-      <x:c r="Y39" s="37" t="str">
         <x:v>warmup_11</x:v>
       </x:c>
+      <x:c r="W39" s="37" t="str">
+        <x:v>enemy_s5_warmup_3</x:v>
+      </x:c>
+      <x:c r="X39"/>
+      <x:c r="Y39"/>
     </x:row>
     <x:row r="40" ht="30" customHeight="1">
       <x:c r="A40" s="37" t="str">
@@ -11523,28 +13112,28 @@
       <x:c r="B40" s="37" t="str">
         <x:v>蓬尾黄鸡</x:v>
       </x:c>
-      <x:c r="C40" s="67" t="n">
+      <x:c r="C40" s="37" t="n">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="D40" s="67" t="n">
+      <x:c r="D40" s="37" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E40" s="67" t="n">
+      <x:c r="E40" s="37" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F40" s="67" t="n">
+      <x:c r="F40" s="37" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G40" s="112" t="n">
+      <x:c r="G40" s="37" t="n">
         <x:v>0.155</x:v>
       </x:c>
-      <x:c r="H40" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I40" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J40" s="67" t="n">
+      <x:c r="H40" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I40" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J40" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K40" s="37" t="str">
@@ -11568,30 +13157,26 @@
       <x:c r="Q40" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R40" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R40" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S40" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T40" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U40" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T40" s="37" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="U40" s="37" t="str">
+        <x:v>#264653</x:v>
       </x:c>
       <x:c r="V40" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W40" s="67" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="X40" s="37" t="str">
-        <x:v>#264653</x:v>
-      </x:c>
-      <x:c r="Y40" s="37" t="str">
         <x:v>warmup_12</x:v>
       </x:c>
+      <x:c r="W40" s="37" t="str">
+        <x:v>enemy_s5_warmup_4</x:v>
+      </x:c>
+      <x:c r="X40"/>
+      <x:c r="Y40"/>
     </x:row>
     <x:row r="41" ht="30" customHeight="1">
       <x:c r="A41" s="37" t="str">
@@ -11600,28 +13185,28 @@
       <x:c r="B41" s="37" t="str">
         <x:v>金颈鸡</x:v>
       </x:c>
-      <x:c r="C41" s="67" t="n">
+      <x:c r="C41" s="37" t="n">
         <x:v>166</x:v>
       </x:c>
-      <x:c r="D41" s="67" t="n">
+      <x:c r="D41" s="37" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E41" s="67" t="n">
+      <x:c r="E41" s="37" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F41" s="67" t="n">
+      <x:c r="F41" s="37" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="G41" s="112" t="n">
+      <x:c r="G41" s="37" t="n">
         <x:v>0.155</x:v>
       </x:c>
-      <x:c r="H41" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I41" s="67" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J41" s="67" t="n">
+      <x:c r="H41" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I41" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J41" s="37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="K41" s="37" t="str">
@@ -11645,30 +13230,26 @@
       <x:c r="Q41" s="37" t="str">
         <x:v>#E09F3E</x:v>
       </x:c>
-      <x:c r="R41" s="37" t="str">
-        <x:v>咯咯咯，你也配上擂台？</x:v>
+      <x:c r="R41" s="37" t="n">
+        <x:v>25</x:v>
       </x:c>
       <x:c r="S41" s="37" t="str">
-        <x:v>羽毛挺花，打人不行。</x:v>
-      </x:c>
-      <x:c r="T41" s="37" t="str">
-        <x:v>回去喝汤吧。</x:v>
-      </x:c>
-      <x:c r="U41" s="112" t="n">
-        <x:v>25</x:v>
+        <x:v>common</x:v>
+      </x:c>
+      <x:c r="T41" s="37" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="U41" s="37" t="str">
+        <x:v>#264653</x:v>
       </x:c>
       <x:c r="V41" s="37" t="str">
-        <x:v>common</x:v>
-      </x:c>
-      <x:c r="W41" s="67" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="X41" s="37" t="str">
-        <x:v>#264653</x:v>
-      </x:c>
-      <x:c r="Y41" s="37" t="str">
         <x:v>warmup_1</x:v>
       </x:c>
+      <x:c r="W41" s="37" t="str">
+        <x:v>enemy_s5_warmup_5</x:v>
+      </x:c>
+      <x:c r="X41"/>
+      <x:c r="Y41"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="2">

--- a/excel/斗鸡配置.xlsx
+++ b/excel/斗鸡配置.xlsx
@@ -5636,8 +5636,10 @@
       <c r="M1" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="N1" s="8" t="s">
-        <v>571</v>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">放大上限</t>
+        </is>
       </c>
       <c r="O1" s="8" t="s">
         <v>572</v>
@@ -5892,8 +5894,8 @@
       <c r="N6" s="11">
         <v>5</v>
       </c>
-      <c r="O6" s="12">
-        <v>0.06</v>
+      <c r="O6">
+        <v>0.15</v>
       </c>
       <c r="P6" s="11">
         <v>10</v>
@@ -5941,8 +5943,8 @@
       <c r="N7" s="13">
         <v>5</v>
       </c>
-      <c r="O7" s="14">
-        <v>0.06</v>
+      <c r="O7">
+        <v>0.15</v>
       </c>
       <c r="P7" s="13">
         <v>10</v>
@@ -5990,8 +5992,8 @@
       <c r="N8" s="15">
         <v>5</v>
       </c>
-      <c r="O8" s="16">
-        <v>0.06</v>
+      <c r="O8">
+        <v>0.15</v>
       </c>
       <c r="P8" s="15">
         <v>10</v>
@@ -6041,8 +6043,8 @@
       <c r="N9" s="13">
         <v>5</v>
       </c>
-      <c r="O9" s="14">
-        <v>0.06</v>
+      <c r="O9">
+        <v>0.15</v>
       </c>
       <c r="P9" s="13">
         <v>10</v>
@@ -6090,8 +6092,8 @@
       <c r="N10" s="15">
         <v>5</v>
       </c>
-      <c r="O10" s="16">
-        <v>0.06</v>
+      <c r="O10">
+        <v>0.15</v>
       </c>
       <c r="P10" s="15">
         <v>10</v>
@@ -7004,8 +7006,11 @@
       <c r="A92" s="7" t="s">
         <v>764</v>
       </c>
-      <c r="B92" s="7" t="s">
-        <v>765</v>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0}强化
+Lv{1}</t>
+        </is>
       </c>
       <c r="C92" s="7"/>
     </row>

--- a/excel/斗鸡配置.xlsx
+++ b/excel/斗鸡配置.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3212" uniqueCount="1617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3262" uniqueCount="1644">
   <si>
     <t>斗鸡配置</t>
   </si>
@@ -1329,6 +1329,63 @@
     <t>竹签破阵靴</t>
   </si>
   <si>
+    <t>digger_head</t>
+  </si>
+  <si>
+    <t>安全帽</t>
+  </si>
+  <si>
+    <t>生命+8，防御+1</t>
+  </si>
+  <si>
+    <t>digger</t>
+  </si>
+  <si>
+    <t>digger_neck</t>
+  </si>
+  <si>
+    <t>反光背心</t>
+  </si>
+  <si>
+    <t>digger_wing</t>
+  </si>
+  <si>
+    <t>工程铲</t>
+  </si>
+  <si>
+    <t>digger_leg</t>
+  </si>
+  <si>
+    <t>防滑靴</t>
+  </si>
+  <si>
+    <t>coming_head</t>
+  </si>
+  <si>
+    <t>鸡来冠</t>
+  </si>
+  <si>
+    <t>coming</t>
+  </si>
+  <si>
+    <t>coming_neck</t>
+  </si>
+  <si>
+    <t>鸡来袍</t>
+  </si>
+  <si>
+    <t>coming_wing</t>
+  </si>
+  <si>
+    <t>鸡来翼</t>
+  </si>
+  <si>
+    <t>coming_leg</t>
+  </si>
+  <si>
+    <t>鸡来靴</t>
+  </si>
+  <si>
     <t>套装名</t>
   </si>
   <si>
@@ -1599,6 +1656,30 @@
     <t>通关奖励：专属加冕结算效果</t>
   </si>
   <si>
+    <t>挖掘鸡套</t>
+  </si>
+  <si>
+    <t>["digger_head","digger_neck","digger_wing","digger_leg"]</t>
+  </si>
+  <si>
+    <t>埋头苦干：生命+20，防御+3</t>
+  </si>
+  <si>
+    <t>深挖一层：每场一次，致命伤害时保留1点生命</t>
+  </si>
+  <si>
+    <t>鸡来套装</t>
+  </si>
+  <si>
+    <t>["coming_head","coming_neck","coming_wing","coming_leg"]</t>
+  </si>
+  <si>
+    <t>气场全开：攻击+6</t>
+  </si>
+  <si>
+    <t>大鸡大利：暴击+10%</t>
+  </si>
+  <si>
     <t>类型 color/face</t>
   </si>
   <si>
@@ -1746,7 +1827,7 @@
     <t>每节点金币</t>
   </si>
   <si>
-    <t>部位上限</t>
+    <t>放大上限</t>
   </si>
   <si>
     <t>每级放大</t>
@@ -2044,7 +2125,7 @@
     <t>CharacterViewComp_011</t>
   </si>
   <si>
-    <t>未集齐</t>
+    <t>未集齐任何套装</t>
   </si>
   <si>
     <t>CustomizeViewComp_001</t>
@@ -2330,7 +2411,7 @@
   </si>
   <si>
     <t xml:space="preserve">{0}强化
-Lv{1}/{2}</t>
+Lv{1}</t>
   </si>
   <si>
     <t>RewardViewComp_002</t>
@@ -5601,16 +5682,16 @@
         <v>65</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>568</v>
+        <v>595</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>291</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>569</v>
+        <v>596</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>570</v>
+        <v>597</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>67</v>
@@ -5636,16 +5717,14 @@
       <c r="M1" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">放大上限</t>
-        </is>
+      <c r="N1" t="s">
+        <v>598</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>572</v>
+        <v>599</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>573</v>
+        <v>600</v>
       </c>
       <c r="Q1" s="22"/>
     </row>
@@ -5654,16 +5733,16 @@
         <v>87</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>574</v>
+        <v>601</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>301</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>575</v>
+        <v>602</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>576</v>
+        <v>603</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>89</v>
@@ -5690,13 +5769,13 @@
         <v>105</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>577</v>
+        <v>604</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>578</v>
+        <v>605</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>579</v>
+        <v>606</v>
       </c>
       <c r="Q2" s="23"/>
     </row>
@@ -5855,13 +5934,13 @@
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>580</v>
+        <v>607</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>581</v>
+        <v>608</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>582</v>
+        <v>609</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>179</v>
@@ -5904,13 +5983,13 @@
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>583</v>
+        <v>610</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>584</v>
+        <v>611</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>585</v>
+        <v>612</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>186</v>
@@ -5953,13 +6032,13 @@
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>586</v>
+        <v>613</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>587</v>
+        <v>614</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>588</v>
+        <v>615</v>
       </c>
       <c r="D8" s="16" t="s">
         <v>180</v>
@@ -6002,13 +6081,13 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>589</v>
+        <v>616</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>590</v>
+        <v>617</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>591</v>
+        <v>618</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>181</v>
@@ -6053,13 +6132,13 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>592</v>
+        <v>619</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>593</v>
+        <v>620</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>594</v>
+        <v>621</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>183</v>
@@ -6102,13 +6181,13 @@
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>595</v>
+        <v>622</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>596</v>
+        <v>623</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>597</v>
+        <v>624</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="20">
@@ -6174,10 +6253,10 @@
         <v>65</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>598</v>
+        <v>625</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>599</v>
+        <v>626</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6185,10 +6264,10 @@
         <v>87</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>600</v>
+        <v>627</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>601</v>
+        <v>628</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -6226,119 +6305,119 @@
     </row>
     <row r="6" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>602</v>
+        <v>629</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>603</v>
+        <v>630</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>604</v>
+        <v>631</v>
       </c>
     </row>
     <row r="7" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>605</v>
+        <v>632</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>68</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>606</v>
+        <v>633</v>
       </c>
     </row>
     <row r="8" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>607</v>
+        <v>634</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>608</v>
+        <v>635</v>
       </c>
       <c r="C8" s="7"/>
     </row>
     <row r="9" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>609</v>
+        <v>636</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>610</v>
+        <v>637</v>
       </c>
       <c r="C9" s="7"/>
     </row>
     <row r="10" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>611</v>
+        <v>638</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>612</v>
+        <v>639</v>
       </c>
       <c r="C10" s="7"/>
     </row>
     <row r="11" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>613</v>
+        <v>640</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>614</v>
+        <v>641</v>
       </c>
       <c r="C11" s="7"/>
     </row>
     <row r="12" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>615</v>
+        <v>642</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>616</v>
+        <v>643</v>
       </c>
       <c r="C12" s="7"/>
     </row>
     <row r="13" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>617</v>
+        <v>644</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>618</v>
+        <v>645</v>
       </c>
       <c r="C13" s="7"/>
     </row>
     <row r="14" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>619</v>
+        <v>646</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>620</v>
+        <v>647</v>
       </c>
       <c r="C14" s="7"/>
     </row>
     <row r="15" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>621</v>
+        <v>648</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>622</v>
+        <v>649</v>
       </c>
       <c r="C15" s="7"/>
     </row>
     <row r="16" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>623</v>
+        <v>650</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>624</v>
+        <v>651</v>
       </c>
       <c r="C16" s="7"/>
     </row>
     <row r="17" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>625</v>
+        <v>652</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>626</v>
+        <v>653</v>
       </c>
       <c r="C17" s="7"/>
     </row>
     <row r="18" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>627</v>
+        <v>654</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>297</v>
@@ -6347,16 +6426,16 @@
     </row>
     <row r="19" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>628</v>
+        <v>655</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>629</v>
+        <v>656</v>
       </c>
       <c r="C19" s="7"/>
     </row>
     <row r="20" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>630</v>
+        <v>657</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>165</v>
@@ -6365,16 +6444,16 @@
     </row>
     <row r="21" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>631</v>
+        <v>658</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>632</v>
+        <v>659</v>
       </c>
       <c r="C21" s="7"/>
     </row>
     <row r="22" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>633</v>
+        <v>660</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>167</v>
@@ -6383,34 +6462,34 @@
     </row>
     <row r="23" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>634</v>
+        <v>661</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>635</v>
+        <v>662</v>
       </c>
       <c r="C23" s="7"/>
     </row>
     <row r="24" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>636</v>
+        <v>663</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>637</v>
+        <v>664</v>
       </c>
       <c r="C24" s="7"/>
     </row>
     <row r="25" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>638</v>
+        <v>665</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>639</v>
+        <v>666</v>
       </c>
       <c r="C25" s="7"/>
     </row>
     <row r="26" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>640</v>
+        <v>667</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>71</v>
@@ -6419,340 +6498,340 @@
     </row>
     <row r="27" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>641</v>
+        <v>668</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>642</v>
+        <v>669</v>
       </c>
       <c r="C27" s="7"/>
     </row>
     <row r="28" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>643</v>
+        <v>670</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>644</v>
+        <v>671</v>
       </c>
       <c r="C28" s="7"/>
     </row>
     <row r="29" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>645</v>
+        <v>672</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>646</v>
+        <v>673</v>
       </c>
       <c r="C29" s="7"/>
     </row>
     <row r="30" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>647</v>
+        <v>674</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>648</v>
+        <v>675</v>
       </c>
       <c r="C30" s="7"/>
     </row>
     <row r="31" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>649</v>
+        <v>676</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>650</v>
+        <v>677</v>
       </c>
       <c r="C31" s="7"/>
     </row>
     <row r="32" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>651</v>
+        <v>678</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>652</v>
+        <v>679</v>
       </c>
       <c r="C32" s="7"/>
     </row>
     <row r="33" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>653</v>
+        <v>680</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>654</v>
+        <v>681</v>
       </c>
       <c r="C33" s="7"/>
     </row>
     <row r="34" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>655</v>
+        <v>682</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>656</v>
+        <v>683</v>
       </c>
       <c r="C34" s="7"/>
     </row>
     <row r="35" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>657</v>
+        <v>684</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>658</v>
+        <v>685</v>
       </c>
       <c r="C35" s="7"/>
     </row>
     <row r="36" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>659</v>
+        <v>686</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>660</v>
+        <v>687</v>
       </c>
       <c r="C36" s="7"/>
     </row>
     <row r="37" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>661</v>
+        <v>688</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>662</v>
+        <v>689</v>
       </c>
       <c r="C37" s="7"/>
     </row>
     <row r="38" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>663</v>
+        <v>690</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>664</v>
+        <v>691</v>
       </c>
       <c r="C38" s="7"/>
     </row>
     <row r="39" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>665</v>
+        <v>692</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>666</v>
+        <v>693</v>
       </c>
       <c r="C39" s="7"/>
     </row>
     <row r="40" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>667</v>
+        <v>694</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>668</v>
+        <v>695</v>
       </c>
       <c r="C40" s="7"/>
     </row>
     <row r="41" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>669</v>
+        <v>696</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>670</v>
+        <v>697</v>
       </c>
       <c r="C41" s="7"/>
     </row>
     <row r="42" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>671</v>
+        <v>698</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>672</v>
+        <v>699</v>
       </c>
       <c r="C42" s="7"/>
     </row>
     <row r="43" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>673</v>
+        <v>700</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>674</v>
+        <v>701</v>
       </c>
       <c r="C43" s="7"/>
     </row>
     <row r="44" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>675</v>
+        <v>702</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>676</v>
+        <v>703</v>
       </c>
       <c r="C44" s="7"/>
     </row>
     <row r="45" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>677</v>
+        <v>704</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>672</v>
+        <v>699</v>
       </c>
       <c r="C45" s="7"/>
     </row>
     <row r="46" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>678</v>
+        <v>705</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>679</v>
+        <v>706</v>
       </c>
       <c r="C46" s="7"/>
     </row>
     <row r="47" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>680</v>
+        <v>707</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>681</v>
+        <v>708</v>
       </c>
       <c r="C47" s="7"/>
     </row>
     <row r="48" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>682</v>
+        <v>709</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>683</v>
+        <v>710</v>
       </c>
       <c r="C48" s="7"/>
     </row>
     <row r="49" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>684</v>
+        <v>711</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>685</v>
+        <v>712</v>
       </c>
       <c r="C49" s="7"/>
     </row>
     <row r="50" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>686</v>
+        <v>713</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>687</v>
+        <v>714</v>
       </c>
       <c r="C50" s="7"/>
     </row>
     <row r="51" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>688</v>
+        <v>715</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>689</v>
+        <v>716</v>
       </c>
       <c r="C51" s="7"/>
     </row>
     <row r="52" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>690</v>
+        <v>717</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>691</v>
+        <v>718</v>
       </c>
       <c r="C52" s="7"/>
     </row>
     <row r="53" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>692</v>
+        <v>719</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>693</v>
+        <v>720</v>
       </c>
       <c r="C53" s="7"/>
     </row>
     <row r="54" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>694</v>
+        <v>721</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>695</v>
+        <v>722</v>
       </c>
       <c r="C54" s="7"/>
     </row>
     <row r="55" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>696</v>
+        <v>723</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>697</v>
+        <v>724</v>
       </c>
       <c r="C55" s="7"/>
     </row>
     <row r="56" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>698</v>
+        <v>725</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>699</v>
+        <v>726</v>
       </c>
       <c r="C56" s="7"/>
     </row>
     <row r="57" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>700</v>
+        <v>727</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>701</v>
+        <v>728</v>
       </c>
       <c r="C57" s="7"/>
     </row>
     <row r="58" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>702</v>
+        <v>729</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>703</v>
+        <v>730</v>
       </c>
       <c r="C58" s="7"/>
     </row>
     <row r="59" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>704</v>
+        <v>731</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>705</v>
+        <v>732</v>
       </c>
       <c r="C59" s="7"/>
     </row>
     <row r="60" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>706</v>
+        <v>733</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>707</v>
+        <v>734</v>
       </c>
       <c r="C60" s="7"/>
     </row>
     <row r="61" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>708</v>
+        <v>735</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>709</v>
+        <v>736</v>
       </c>
       <c r="C61" s="7"/>
     </row>
     <row r="62" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>710</v>
+        <v>737</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>711</v>
+        <v>738</v>
       </c>
       <c r="C62" s="7"/>
     </row>
     <row r="63" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>712</v>
+        <v>739</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>713</v>
+        <v>740</v>
       </c>
       <c r="C63" s="7"/>
     </row>
     <row r="64" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>714</v>
+        <v>741</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>67</v>
@@ -6761,25 +6840,25 @@
     </row>
     <row r="65" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>715</v>
+        <v>742</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>716</v>
+        <v>743</v>
       </c>
       <c r="C65" s="7"/>
     </row>
     <row r="66" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>717</v>
+        <v>744</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>718</v>
+        <v>745</v>
       </c>
       <c r="C66" s="7"/>
     </row>
     <row r="67" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>719</v>
+        <v>746</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>73</v>
@@ -6788,7 +6867,7 @@
     </row>
     <row r="68" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>720</v>
+        <v>747</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>71</v>
@@ -6797,34 +6876,34 @@
     </row>
     <row r="69" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>721</v>
+        <v>748</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>722</v>
+        <v>749</v>
       </c>
       <c r="C69" s="7"/>
     </row>
     <row r="70" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>723</v>
+        <v>750</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>724</v>
+        <v>751</v>
       </c>
       <c r="C70" s="7"/>
     </row>
     <row r="71" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>725</v>
+        <v>752</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>726</v>
+        <v>753</v>
       </c>
       <c r="C71" s="7"/>
     </row>
     <row r="72" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>727</v>
+        <v>754</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>167</v>
@@ -6833,7 +6912,7 @@
     </row>
     <row r="73" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>728</v>
+        <v>755</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>68</v>
@@ -6842,658 +6921,655 @@
     </row>
     <row r="74" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>729</v>
+        <v>756</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>730</v>
+        <v>757</v>
       </c>
       <c r="C74" s="7"/>
     </row>
     <row r="75" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>731</v>
+        <v>758</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>732</v>
+        <v>759</v>
       </c>
       <c r="C75" s="7"/>
     </row>
     <row r="76" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>733</v>
+        <v>760</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>734</v>
+        <v>761</v>
       </c>
       <c r="C76" s="7"/>
     </row>
     <row r="77" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>735</v>
+        <v>762</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>732</v>
+        <v>759</v>
       </c>
       <c r="C77" s="7"/>
     </row>
     <row r="78" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>736</v>
+        <v>763</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>737</v>
+        <v>764</v>
       </c>
       <c r="C78" s="7"/>
     </row>
     <row r="79" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>738</v>
+        <v>765</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>739</v>
+        <v>766</v>
       </c>
       <c r="C79" s="7"/>
     </row>
     <row r="80" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>740</v>
+        <v>767</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>741</v>
+        <v>768</v>
       </c>
       <c r="C80" s="7"/>
     </row>
     <row r="81" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>742</v>
+        <v>769</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>743</v>
+        <v>770</v>
       </c>
       <c r="C81" s="7"/>
     </row>
     <row r="82" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>744</v>
+        <v>771</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>745</v>
+        <v>772</v>
       </c>
       <c r="C82" s="7"/>
     </row>
     <row r="83" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>746</v>
+        <v>773</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>747</v>
+        <v>774</v>
       </c>
       <c r="C83" s="7"/>
     </row>
     <row r="84" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>748</v>
+        <v>775</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>749</v>
+        <v>776</v>
       </c>
       <c r="C84" s="7"/>
     </row>
     <row r="85" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>750</v>
+        <v>777</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>751</v>
+        <v>778</v>
       </c>
       <c r="C85" s="7"/>
     </row>
     <row r="86" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>752</v>
+        <v>779</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>753</v>
+        <v>780</v>
       </c>
       <c r="C86" s="7"/>
     </row>
     <row r="87" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>754</v>
+        <v>781</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>755</v>
+        <v>782</v>
       </c>
       <c r="C87" s="7"/>
     </row>
     <row r="88" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>756</v>
+        <v>783</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>757</v>
+        <v>784</v>
       </c>
       <c r="C88" s="7"/>
     </row>
     <row r="89" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>758</v>
+        <v>785</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>759</v>
+        <v>786</v>
       </c>
       <c r="C89" s="7"/>
     </row>
     <row r="90" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>760</v>
+        <v>787</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>761</v>
+        <v>788</v>
       </c>
       <c r="C90" s="7"/>
     </row>
     <row r="91" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>762</v>
+        <v>789</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>763</v>
+        <v>790</v>
       </c>
       <c r="C91" s="7"/>
     </row>
     <row r="92" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
-        <v>764</v>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{0}强化
-Lv{1}</t>
-        </is>
+        <v>791</v>
+      </c>
+      <c r="B92" t="s">
+        <v>792</v>
       </c>
       <c r="C92" s="7"/>
     </row>
     <row r="93" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>766</v>
+        <v>793</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>767</v>
+        <v>794</v>
       </c>
       <c r="C93" s="7"/>
     </row>
     <row r="94" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>768</v>
+        <v>795</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>734</v>
+        <v>761</v>
       </c>
       <c r="C94" s="7"/>
     </row>
     <row r="95" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>769</v>
+        <v>796</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>770</v>
+        <v>797</v>
       </c>
       <c r="C95" s="7"/>
     </row>
     <row r="96" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>771</v>
+        <v>798</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>772</v>
+        <v>799</v>
       </c>
       <c r="C96" s="7"/>
     </row>
     <row r="97" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>773</v>
+        <v>800</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>774</v>
+        <v>801</v>
       </c>
       <c r="C97" s="7"/>
     </row>
     <row r="98" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>775</v>
+        <v>802</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>776</v>
+        <v>803</v>
       </c>
       <c r="C98" s="7"/>
     </row>
     <row r="99" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>777</v>
+        <v>804</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>778</v>
+        <v>805</v>
       </c>
       <c r="C99" s="7"/>
     </row>
     <row r="100" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>779</v>
+        <v>806</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>780</v>
+        <v>807</v>
       </c>
       <c r="C100" s="7"/>
     </row>
     <row r="101" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>781</v>
+        <v>808</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>782</v>
+        <v>809</v>
       </c>
       <c r="C101" s="7"/>
     </row>
     <row r="102" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
-        <v>783</v>
+        <v>810</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>784</v>
+        <v>811</v>
       </c>
       <c r="C102" s="7"/>
     </row>
     <row r="103" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>785</v>
+        <v>812</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>786</v>
+        <v>813</v>
       </c>
       <c r="C103" s="7"/>
     </row>
     <row r="104" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>787</v>
+        <v>814</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>788</v>
+        <v>815</v>
       </c>
       <c r="C104" s="7"/>
     </row>
     <row r="105" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>789</v>
+        <v>816</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>790</v>
+        <v>817</v>
       </c>
       <c r="C105" s="7"/>
     </row>
     <row r="106" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>791</v>
+        <v>818</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>792</v>
+        <v>819</v>
       </c>
       <c r="C106" s="7"/>
     </row>
     <row r="107" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>793</v>
+        <v>820</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>794</v>
+        <v>821</v>
       </c>
       <c r="C107" s="7"/>
     </row>
     <row r="108" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>795</v>
+        <v>822</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>780</v>
+        <v>807</v>
       </c>
       <c r="C108" s="7"/>
     </row>
     <row r="109" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>796</v>
+        <v>823</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>797</v>
+        <v>824</v>
       </c>
       <c r="C109" s="7"/>
     </row>
     <row r="110" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>798</v>
+        <v>825</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>799</v>
+        <v>826</v>
       </c>
       <c r="C110" s="7"/>
     </row>
     <row r="111" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>800</v>
+        <v>827</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>801</v>
+        <v>828</v>
       </c>
       <c r="C111" s="7"/>
     </row>
     <row r="112" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
-        <v>802</v>
+        <v>829</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>803</v>
+        <v>830</v>
       </c>
       <c r="C112" s="7"/>
     </row>
     <row r="113" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>804</v>
+        <v>831</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>805</v>
+        <v>832</v>
       </c>
       <c r="C113" s="7"/>
     </row>
     <row r="114" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>806</v>
+        <v>833</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>807</v>
+        <v>834</v>
       </c>
       <c r="C114" s="7"/>
     </row>
     <row r="115" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>808</v>
+        <v>835</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>809</v>
+        <v>836</v>
       </c>
       <c r="C115" s="7"/>
     </row>
     <row r="116" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
-        <v>810</v>
+        <v>837</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>811</v>
+        <v>838</v>
       </c>
       <c r="C116" s="7"/>
     </row>
     <row r="117" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>812</v>
+        <v>839</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>813</v>
+        <v>840</v>
       </c>
       <c r="C117" s="7"/>
     </row>
     <row r="118" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
-        <v>814</v>
+        <v>841</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>815</v>
+        <v>842</v>
       </c>
       <c r="C118" s="7"/>
     </row>
     <row r="119" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>816</v>
+        <v>843</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>817</v>
+        <v>844</v>
       </c>
       <c r="C119" s="7"/>
     </row>
     <row r="120" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
-        <v>818</v>
+        <v>845</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>819</v>
+        <v>846</v>
       </c>
       <c r="C120" s="7"/>
     </row>
     <row r="121" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>820</v>
+        <v>847</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>821</v>
+        <v>848</v>
       </c>
       <c r="C121" s="7"/>
     </row>
     <row r="122" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
-        <v>822</v>
+        <v>849</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>823</v>
+        <v>850</v>
       </c>
       <c r="C122" s="7"/>
     </row>
     <row r="123" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>824</v>
+        <v>851</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>555</v>
+        <v>582</v>
       </c>
       <c r="C123" s="7"/>
     </row>
     <row r="124" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
-        <v>825</v>
+        <v>852</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>557</v>
+        <v>584</v>
       </c>
       <c r="C124" s="7"/>
     </row>
     <row r="125" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>826</v>
+        <v>853</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>559</v>
+        <v>586</v>
       </c>
       <c r="C125" s="7"/>
     </row>
     <row r="126" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
-        <v>827</v>
+        <v>854</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>561</v>
+        <v>588</v>
       </c>
       <c r="C126" s="7"/>
     </row>
     <row r="127" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>828</v>
+        <v>855</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>563</v>
+        <v>590</v>
       </c>
       <c r="C127" s="7"/>
     </row>
     <row r="128" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
-        <v>829</v>
+        <v>856</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>566</v>
+        <v>593</v>
       </c>
       <c r="C128" s="7"/>
     </row>
     <row r="129" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>830</v>
+        <v>857</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>831</v>
+        <v>858</v>
       </c>
       <c r="C129" s="7"/>
     </row>
     <row r="130" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
-        <v>832</v>
+        <v>859</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>833</v>
+        <v>860</v>
       </c>
       <c r="C130" s="7"/>
     </row>
     <row r="131" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>834</v>
+        <v>861</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>835</v>
+        <v>862</v>
       </c>
       <c r="C131" s="7"/>
     </row>
     <row r="132" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
-        <v>836</v>
+        <v>863</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>654</v>
+        <v>681</v>
       </c>
       <c r="C132" s="7"/>
     </row>
     <row r="133" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>837</v>
+        <v>864</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>652</v>
+        <v>679</v>
       </c>
       <c r="C133" s="7"/>
     </row>
     <row r="134" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
-        <v>838</v>
+        <v>865</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>839</v>
+        <v>866</v>
       </c>
       <c r="C134" s="7"/>
     </row>
     <row r="135" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>840</v>
+        <v>867</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>841</v>
+        <v>868</v>
       </c>
       <c r="C135" s="7"/>
     </row>
     <row r="136" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
-        <v>842</v>
+        <v>869</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>843</v>
+        <v>870</v>
       </c>
       <c r="C136" s="7"/>
     </row>
     <row r="137" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>844</v>
+        <v>871</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>845</v>
+        <v>872</v>
       </c>
       <c r="C137" s="7"/>
     </row>
     <row r="138" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
-        <v>846</v>
+        <v>873</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>847</v>
+        <v>874</v>
       </c>
       <c r="C138" s="7"/>
     </row>
     <row r="139" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>848</v>
+        <v>875</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>849</v>
+        <v>876</v>
       </c>
       <c r="C139" s="7"/>
     </row>
     <row r="140" ht="16.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
-        <v>850</v>
+        <v>877</v>
       </c>
       <c r="B140" s="12" t="s">
-        <v>851</v>
+        <v>878</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>852</v>
+        <v>879</v>
       </c>
     </row>
     <row r="141" ht="16.5" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="12" t="s">
-        <v>853</v>
+        <v>880</v>
       </c>
       <c r="B141" s="12" t="s">
-        <v>854</v>
+        <v>881</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>852</v>
+        <v>879</v>
       </c>
     </row>
     <row r="142" ht="33" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
-        <v>855</v>
+        <v>882</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>856</v>
+        <v>883</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>852</v>
+        <v>879</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
-        <v>857</v>
+        <v>884</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>858</v>
+        <v>885</v>
       </c>
       <c r="C143" s="12"/>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
-        <v>859</v>
+        <v>886</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>860</v>
+        <v>887</v>
       </c>
       <c r="C144" s="12"/>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
-        <v>861</v>
+        <v>888</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>862</v>
+        <v>889</v>
       </c>
       <c r="C145" s="12"/>
     </row>
@@ -7517,10 +7593,10 @@
         <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>909</v>
+        <v>936</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>910</v>
+        <v>937</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -7528,10 +7604,10 @@
         <v>87</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>911</v>
+        <v>938</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>912</v>
+        <v>939</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -7569,2037 +7645,2037 @@
     </row>
     <row r="6" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>913</v>
+        <v>940</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>914</v>
+        <v>941</v>
       </c>
     </row>
     <row r="7" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>915</v>
+        <v>942</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>916</v>
+        <v>943</v>
       </c>
     </row>
     <row r="8" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>917</v>
+        <v>944</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>918</v>
+        <v>945</v>
       </c>
     </row>
     <row r="9" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>919</v>
+        <v>946</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>920</v>
+        <v>947</v>
       </c>
     </row>
     <row r="10" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>921</v>
+        <v>948</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>922</v>
+        <v>949</v>
       </c>
     </row>
     <row r="11" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>923</v>
+        <v>950</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>924</v>
+        <v>951</v>
       </c>
     </row>
     <row r="12" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>925</v>
+        <v>952</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>926</v>
+        <v>953</v>
       </c>
     </row>
     <row r="13" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>927</v>
+        <v>954</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>928</v>
+        <v>955</v>
       </c>
     </row>
     <row r="14" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>929</v>
+        <v>956</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>930</v>
+        <v>957</v>
       </c>
     </row>
     <row r="15" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>931</v>
+        <v>958</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>932</v>
+        <v>959</v>
       </c>
     </row>
     <row r="16" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>933</v>
+        <v>960</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>934</v>
+        <v>961</v>
       </c>
     </row>
     <row r="17" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>935</v>
+        <v>962</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>936</v>
+        <v>963</v>
       </c>
     </row>
     <row r="18" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>937</v>
+        <v>964</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>938</v>
+        <v>965</v>
       </c>
     </row>
     <row r="19" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>939</v>
+        <v>966</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>940</v>
+        <v>967</v>
       </c>
     </row>
     <row r="20" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>941</v>
+        <v>968</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>942</v>
+        <v>969</v>
       </c>
     </row>
     <row r="21" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>943</v>
+        <v>970</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>944</v>
+        <v>971</v>
       </c>
     </row>
     <row r="22" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>945</v>
+        <v>972</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>946</v>
+        <v>973</v>
       </c>
     </row>
     <row r="23" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>947</v>
+        <v>974</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>948</v>
+        <v>975</v>
       </c>
     </row>
     <row r="24" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>949</v>
+        <v>976</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>950</v>
+        <v>977</v>
       </c>
     </row>
     <row r="25" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>951</v>
+        <v>978</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>952</v>
+        <v>979</v>
       </c>
     </row>
     <row r="26" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>953</v>
+        <v>980</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>954</v>
+        <v>981</v>
       </c>
     </row>
     <row r="27" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>955</v>
+        <v>982</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>956</v>
+        <v>983</v>
       </c>
     </row>
     <row r="28" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>957</v>
+        <v>984</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>958</v>
+        <v>985</v>
       </c>
     </row>
     <row r="29" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>959</v>
+        <v>986</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>960</v>
+        <v>987</v>
       </c>
     </row>
     <row r="30" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>961</v>
+        <v>988</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>962</v>
+        <v>989</v>
       </c>
     </row>
     <row r="31" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>963</v>
+        <v>990</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>964</v>
+        <v>991</v>
       </c>
     </row>
     <row r="32" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>965</v>
+        <v>992</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>966</v>
+        <v>993</v>
       </c>
     </row>
     <row r="33" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>967</v>
+        <v>994</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>968</v>
+        <v>995</v>
       </c>
     </row>
     <row r="34" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>969</v>
+        <v>996</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>970</v>
+        <v>997</v>
       </c>
     </row>
     <row r="35" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>971</v>
+        <v>998</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>972</v>
+        <v>999</v>
       </c>
     </row>
     <row r="36" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>973</v>
+        <v>1000</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>974</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="37" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>975</v>
+        <v>1002</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>976</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="38" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>977</v>
+        <v>1004</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>978</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="39" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>979</v>
+        <v>1006</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>980</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="40" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>981</v>
+        <v>1008</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>982</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="41" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>983</v>
+        <v>1010</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>984</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="42" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>985</v>
+        <v>1012</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>986</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="43" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>987</v>
+        <v>1014</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>988</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="44" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>989</v>
+        <v>1016</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>990</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="45" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>991</v>
+        <v>1018</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>992</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="46" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>993</v>
+        <v>1020</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>994</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="47" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>995</v>
+        <v>1022</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>996</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="48" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>997</v>
+        <v>1024</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>998</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="49" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>999</v>
+        <v>1026</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>1000</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="50" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>1001</v>
+        <v>1028</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>1002</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="51" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>1003</v>
+        <v>1030</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>1004</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="52" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>1005</v>
+        <v>1032</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>1006</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="53" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>1007</v>
+        <v>1034</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>1008</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="54" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>1009</v>
+        <v>1036</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>1010</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="55" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>1011</v>
+        <v>1038</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>1012</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="56" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>1013</v>
+        <v>1040</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>1015</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="57" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>1016</v>
+        <v>1043</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>1017</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="58" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>1018</v>
+        <v>1045</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>1019</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="59" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>1020</v>
+        <v>1047</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>1021</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="60" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>1022</v>
+        <v>1049</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>1023</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="61" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>1024</v>
+        <v>1051</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>1025</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="62" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>1026</v>
+        <v>1053</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>1027</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="63" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>1028</v>
+        <v>1055</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>1029</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="64" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>1030</v>
+        <v>1057</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>1031</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="65" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>1032</v>
+        <v>1059</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>1033</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="66" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>1034</v>
+        <v>1061</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>1035</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="67" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>1036</v>
+        <v>1063</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>1037</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="68" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>1038</v>
+        <v>1065</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>1039</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="69" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>1040</v>
+        <v>1067</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>1041</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="70" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>1042</v>
+        <v>1069</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>1043</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="71" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>1044</v>
+        <v>1071</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>1045</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="72" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>1046</v>
+        <v>1073</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>1047</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="73" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>1048</v>
+        <v>1075</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>1049</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="74" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>1050</v>
+        <v>1077</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>1051</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="75" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>1052</v>
+        <v>1079</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>1053</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="76" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>1054</v>
+        <v>1081</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>1055</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="77" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>1056</v>
+        <v>1083</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>1057</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="78" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>1058</v>
+        <v>1085</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>1059</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="79" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>1060</v>
+        <v>1087</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>1061</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="80" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>1062</v>
+        <v>1089</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>1063</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="81" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>1064</v>
+        <v>1091</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>1065</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="82" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>1066</v>
+        <v>1093</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>1067</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="83" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>1068</v>
+        <v>1095</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>1069</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="84" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>1070</v>
+        <v>1097</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>1071</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="85" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>1072</v>
+        <v>1099</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>1073</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="86" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>1074</v>
+        <v>1101</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>1076</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="87" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>1077</v>
+        <v>1104</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>1078</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="88" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>1079</v>
+        <v>1106</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>1080</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="89" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>1081</v>
+        <v>1108</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>1082</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="90" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>1083</v>
+        <v>1110</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>1084</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="91" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>1085</v>
+        <v>1112</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>1086</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="92" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
-        <v>1087</v>
+        <v>1114</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>1088</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="93" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>1089</v>
+        <v>1116</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>1090</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="94" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>1091</v>
+        <v>1118</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>1092</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="95" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>1093</v>
+        <v>1120</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>1094</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="96" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>1095</v>
+        <v>1122</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>1096</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="97" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>1097</v>
+        <v>1124</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>1098</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="98" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>1099</v>
+        <v>1126</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>1100</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="99" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>1101</v>
+        <v>1128</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>1102</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="100" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>1103</v>
+        <v>1130</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>1104</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="101" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>1105</v>
+        <v>1132</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>1107</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="102" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
-        <v>1108</v>
+        <v>1135</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>1109</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="103" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>1110</v>
+        <v>1137</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>1111</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="104" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>1112</v>
+        <v>1139</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>1113</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="105" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>1114</v>
+        <v>1141</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>1115</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="106" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>1116</v>
+        <v>1143</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>1117</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="107" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>1118</v>
+        <v>1145</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>1119</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="108" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>1120</v>
+        <v>1147</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>1121</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="109" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>1122</v>
+        <v>1149</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>1123</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="110" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>1124</v>
+        <v>1151</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>1125</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="111" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>1126</v>
+        <v>1153</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>1127</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="112" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
-        <v>1128</v>
+        <v>1155</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>1129</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="113" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>1130</v>
+        <v>1157</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>1131</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="114" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>1132</v>
+        <v>1159</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>1133</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="115" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>1134</v>
+        <v>1161</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>1135</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="116" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
-        <v>1136</v>
+        <v>1163</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>1137</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="117" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>1138</v>
+        <v>1165</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>1139</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="118" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
-        <v>1140</v>
+        <v>1167</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>1141</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="119" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>1142</v>
+        <v>1169</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>1143</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="120" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
-        <v>1144</v>
+        <v>1171</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>1145</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="121" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>1146</v>
+        <v>1173</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>1147</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="122" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
-        <v>1148</v>
+        <v>1175</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>1149</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="123" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>1150</v>
+        <v>1177</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>1151</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="124" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
-        <v>1152</v>
+        <v>1179</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>1153</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="125" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>1154</v>
+        <v>1181</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>1155</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="126" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
-        <v>1156</v>
+        <v>1183</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>1157</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="127" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>1158</v>
+        <v>1185</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>1159</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="128" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
-        <v>1160</v>
+        <v>1187</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>1161</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="129" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>1162</v>
+        <v>1189</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>1163</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="130" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
-        <v>1164</v>
+        <v>1191</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>1165</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="131" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>1166</v>
+        <v>1193</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>1167</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="132" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
-        <v>1168</v>
+        <v>1195</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>1169</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="133" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>1170</v>
+        <v>1197</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>1171</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="134" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
-        <v>1172</v>
+        <v>1199</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>1173</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="135" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>1174</v>
+        <v>1201</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>1175</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="136" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
-        <v>1176</v>
+        <v>1203</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>1177</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="137" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>1178</v>
+        <v>1205</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>1179</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="138" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
-        <v>1180</v>
+        <v>1207</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>1181</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="139" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>1182</v>
+        <v>1209</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>1183</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="140" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
-        <v>1184</v>
+        <v>1211</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>1185</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="141" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>1186</v>
+        <v>1213</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>1187</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="142" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
-        <v>1188</v>
+        <v>1215</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>1189</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="143" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>1190</v>
+        <v>1217</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>1191</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="144" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="7" t="s">
-        <v>1192</v>
+        <v>1219</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>1193</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="145" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>1194</v>
+        <v>1221</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>1195</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="146" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
-        <v>1196</v>
+        <v>1223</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>1197</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="147" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>1198</v>
+        <v>1225</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>1199</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="148" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
-        <v>1200</v>
+        <v>1227</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>1201</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="149" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>1202</v>
+        <v>1229</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>1203</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="150" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
-        <v>1204</v>
+        <v>1231</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>1205</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="151" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>1206</v>
+        <v>1233</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>1207</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="152" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
-        <v>1208</v>
+        <v>1235</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>1209</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="153" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>1210</v>
+        <v>1237</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>1211</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="154" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
-        <v>1212</v>
+        <v>1239</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>1213</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="155" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>1214</v>
+        <v>1241</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>1215</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="156" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
-        <v>1216</v>
+        <v>1243</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>1217</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="157" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>1218</v>
+        <v>1245</v>
       </c>
       <c r="B157" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>1219</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="158" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
-        <v>1220</v>
+        <v>1247</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>1221</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="159" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>1222</v>
+        <v>1249</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>1223</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="160" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
-        <v>1224</v>
+        <v>1251</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>1225</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="161" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>1226</v>
+        <v>1253</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>1227</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="162" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
-        <v>1228</v>
+        <v>1255</v>
       </c>
       <c r="B162" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>1229</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="163" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>1230</v>
+        <v>1257</v>
       </c>
       <c r="B163" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>1231</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="164" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
-        <v>1232</v>
+        <v>1259</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>1233</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="165" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>1234</v>
+        <v>1261</v>
       </c>
       <c r="B165" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>1235</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="166" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
-        <v>1236</v>
+        <v>1263</v>
       </c>
       <c r="B166" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>1237</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="167" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>1238</v>
+        <v>1265</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>1239</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="168" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="7" t="s">
-        <v>1240</v>
+        <v>1267</v>
       </c>
       <c r="B168" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>1241</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="169" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>1242</v>
+        <v>1269</v>
       </c>
       <c r="B169" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>1243</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="170" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="7" t="s">
-        <v>1244</v>
+        <v>1271</v>
       </c>
       <c r="B170" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C170" s="7" t="s">
-        <v>1245</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="171" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>1246</v>
+        <v>1273</v>
       </c>
       <c r="B171" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C171" s="7" t="s">
-        <v>1247</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="172" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
-        <v>1248</v>
+        <v>1275</v>
       </c>
       <c r="B172" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C172" s="7" t="s">
-        <v>1249</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="173" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>1250</v>
+        <v>1277</v>
       </c>
       <c r="B173" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>1251</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="174" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
-        <v>1252</v>
+        <v>1279</v>
       </c>
       <c r="B174" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C174" s="7" t="s">
-        <v>1253</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="175" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>1254</v>
+        <v>1281</v>
       </c>
       <c r="B175" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>1255</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="176" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
-        <v>1256</v>
+        <v>1283</v>
       </c>
       <c r="B176" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>1257</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="177" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>1258</v>
+        <v>1285</v>
       </c>
       <c r="B177" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>1259</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="178" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
-        <v>1260</v>
+        <v>1287</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>1261</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="179" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>1262</v>
+        <v>1289</v>
       </c>
       <c r="B179" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>1263</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="180" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
-        <v>1264</v>
+        <v>1291</v>
       </c>
       <c r="B180" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C180" s="7" t="s">
-        <v>1265</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="181" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>1266</v>
+        <v>1293</v>
       </c>
       <c r="B181" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C181" s="7" t="s">
-        <v>1267</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="182" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="7" t="s">
-        <v>1268</v>
+        <v>1295</v>
       </c>
       <c r="B182" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C182" s="7" t="s">
-        <v>1269</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="183" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>1270</v>
+        <v>1297</v>
       </c>
       <c r="B183" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C183" s="7" t="s">
-        <v>1271</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="184" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="7" t="s">
-        <v>1272</v>
+        <v>1299</v>
       </c>
       <c r="B184" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C184" s="7" t="s">
-        <v>1273</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="185" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>1274</v>
+        <v>1301</v>
       </c>
       <c r="B185" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C185" s="7" t="s">
-        <v>1275</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="186" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="7" t="s">
-        <v>1276</v>
+        <v>1303</v>
       </c>
       <c r="B186" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C186" s="7" t="s">
-        <v>1277</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="187" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>1278</v>
+        <v>1305</v>
       </c>
       <c r="B187" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>1279</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="188" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
-        <v>1280</v>
+        <v>1307</v>
       </c>
       <c r="B188" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C188" s="7" t="s">
-        <v>1281</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="189" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>1282</v>
+        <v>1309</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C189" s="7" t="s">
-        <v>1283</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="190" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="7" t="s">
-        <v>1284</v>
+        <v>1311</v>
       </c>
       <c r="B190" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C190" s="7" t="s">
-        <v>1285</v>
+        <v>1312</v>
       </c>
     </row>
   </sheetData>
@@ -9621,10 +9697,10 @@
         <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1286</v>
+        <v>1313</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1287</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9635,7 +9711,7 @@
         <v>88</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>879</v>
+        <v>906</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9676,10 +9752,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1288</v>
+        <v>1315</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1289</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9687,10 +9763,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1290</v>
+        <v>1317</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1291</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9698,10 +9774,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1292</v>
+        <v>1319</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1293</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9709,10 +9785,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1294</v>
+        <v>1321</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1295</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9720,10 +9796,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1296</v>
+        <v>1323</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1297</v>
+        <v>1324</v>
       </c>
     </row>
   </sheetData>
@@ -9745,7 +9821,7 @@
         <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>910</v>
+        <v>937</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -9753,7 +9829,7 @@
         <v>87</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>912</v>
+        <v>939</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -9782,514 +9858,514 @@
     </row>
     <row r="6" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1298</v>
+        <v>1325</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1299</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="7" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1300</v>
+        <v>1327</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1299</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="8" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1301</v>
+        <v>1328</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1302</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="9" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1303</v>
+        <v>1330</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1302</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="10" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1304</v>
+        <v>1331</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1305</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="11" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>1306</v>
+        <v>1333</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1307</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="12" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1308</v>
+        <v>1335</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1309</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="13" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>1310</v>
+        <v>1337</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1311</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="14" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1312</v>
+        <v>1339</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>1313</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="15" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>1314</v>
+        <v>1341</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>672</v>
+        <v>699</v>
       </c>
     </row>
     <row r="16" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1315</v>
+        <v>1342</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1316</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="17" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>1317</v>
+        <v>1344</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>676</v>
+        <v>703</v>
       </c>
     </row>
     <row r="18" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1318</v>
+        <v>1345</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>1316</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="19" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>1319</v>
+        <v>1346</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>1320</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="20" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>1321</v>
+        <v>1348</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>1322</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="21" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>1323</v>
+        <v>1350</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>1324</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="22" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>1325</v>
+        <v>1352</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>1326</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="23" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>1327</v>
+        <v>1354</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>1328</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="24" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>1329</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="25" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>1330</v>
+        <v>1357</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>1331</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="26" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>1332</v>
+        <v>1359</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>1333</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="27" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>1334</v>
+        <v>1361</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>1335</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="28" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>1336</v>
+        <v>1363</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>1337</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="29" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>1338</v>
+        <v>1365</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>1339</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="30" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>1340</v>
+        <v>1367</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>1341</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="31" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>1342</v>
+        <v>1369</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>1302</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="32" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>1343</v>
+        <v>1370</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>1344</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="33" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>1345</v>
+        <v>1372</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>1346</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="34" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>1347</v>
+        <v>1374</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>1348</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="35" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>1349</v>
+        <v>1376</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>1350</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="36" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>1351</v>
+        <v>1378</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>1352</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="37" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>1353</v>
+        <v>1380</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>1354</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="38" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>1355</v>
+        <v>1382</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>1356</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="39" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>1357</v>
+        <v>1384</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>697</v>
+        <v>724</v>
       </c>
     </row>
     <row r="40" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>1358</v>
+        <v>1385</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>1359</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="41" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>1360</v>
+        <v>1387</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>1302</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="42" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>1361</v>
+        <v>1388</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>1302</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="43" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>1362</v>
+        <v>1389</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>1302</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="44" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>1363</v>
+        <v>1390</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>1302</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="45" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>1364</v>
+        <v>1391</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>1302</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="46" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>1365</v>
+        <v>1392</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>1302</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="47" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>1366</v>
+        <v>1393</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>1302</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="48" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>1367</v>
+        <v>1394</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>1302</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="49" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>1368</v>
+        <v>1395</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>1302</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="50" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>1369</v>
+        <v>1396</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>1302</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="51" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>1370</v>
+        <v>1397</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>1302</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="52" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>1371</v>
+        <v>1398</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>1302</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="53" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>1372</v>
+        <v>1399</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>672</v>
+        <v>699</v>
       </c>
     </row>
     <row r="54" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>1373</v>
+        <v>1400</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>745</v>
+        <v>772</v>
       </c>
     </row>
     <row r="55" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>1374</v>
+        <v>1401</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>1375</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="56" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>1376</v>
+        <v>1403</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>734</v>
+        <v>761</v>
       </c>
     </row>
     <row r="57" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>1377</v>
+        <v>1404</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>734</v>
+        <v>761</v>
       </c>
     </row>
     <row r="58" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>1378</v>
+        <v>1405</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>1379</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="59" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>1380</v>
+        <v>1407</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>1381</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="60" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>1382</v>
+        <v>1409</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>1302</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="61" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>1383</v>
+        <v>1410</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>1305</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="62" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>1384</v>
+        <v>1411</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>1307</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="63" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>1385</v>
+        <v>1412</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>1386</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="64" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>1387</v>
+        <v>1414</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>732</v>
+        <v>759</v>
       </c>
     </row>
     <row r="65" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>1388</v>
+        <v>1415</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>1389</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="66" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>1390</v>
+        <v>1417</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>1322</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="67" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>1391</v>
+        <v>1418</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>1392</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>1393</v>
+        <v>1420</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>1394</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>1395</v>
+        <v>1422</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>858</v>
+        <v>885</v>
       </c>
     </row>
   </sheetData>
@@ -10313,16 +10389,16 @@
         <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1396</v>
+        <v>1423</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1397</v>
+        <v>1424</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1398</v>
+        <v>1425</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1399</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -10330,16 +10406,16 @@
         <v>87</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>527</v>
+        <v>554</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>301</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1400</v>
+        <v>1427</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>1401</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -10395,13 +10471,13 @@
     </row>
     <row r="6" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1402</v>
+        <v>1429</v>
       </c>
       <c r="B6" s="7">
         <v>1.6</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1403</v>
+        <v>1430</v>
       </c>
       <c r="D6" s="7">
         <v>0.01</v>
@@ -10410,13 +10486,13 @@
     </row>
     <row r="7" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1404</v>
+        <v>1431</v>
       </c>
       <c r="B7" s="7">
         <v>20</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1405</v>
+        <v>1432</v>
       </c>
       <c r="D7" s="7">
         <v>0.01</v>
@@ -10425,13 +10501,13 @@
     </row>
     <row r="8" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1406</v>
+        <v>1433</v>
       </c>
       <c r="B8" s="7">
         <v>0.55</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1407</v>
+        <v>1434</v>
       </c>
       <c r="D8" s="7">
         <v>0.01</v>
@@ -10440,13 +10516,13 @@
     </row>
     <row r="9" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1408</v>
+        <v>1435</v>
       </c>
       <c r="B9" s="7">
         <v>0.3</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1409</v>
+        <v>1436</v>
       </c>
       <c r="D9" s="7">
         <v>0.001</v>
@@ -10455,13 +10531,13 @@
     </row>
     <row r="10" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1410</v>
+        <v>1437</v>
       </c>
       <c r="B10" s="7">
         <v>6</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1411</v>
+        <v>1438</v>
       </c>
       <c r="D10" s="7">
         <v>0.01</v>
@@ -10470,13 +10546,13 @@
     </row>
     <row r="11" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>1412</v>
+        <v>1439</v>
       </c>
       <c r="B11" s="7">
         <v>4.5</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1413</v>
+        <v>1440</v>
       </c>
       <c r="D11" s="7">
         <v>0.01</v>
@@ -10485,13 +10561,13 @@
     </row>
     <row r="12" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1414</v>
+        <v>1441</v>
       </c>
       <c r="B12" s="7">
         <v>0.12</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>1415</v>
+        <v>1442</v>
       </c>
       <c r="D12" s="7">
         <v>0</v>
@@ -10500,13 +10576,13 @@
     </row>
     <row r="13" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>1416</v>
+        <v>1443</v>
       </c>
       <c r="B13" s="7">
         <v>0.92</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>1417</v>
+        <v>1444</v>
       </c>
       <c r="D13" s="7">
         <v>0.01</v>
@@ -10515,13 +10591,13 @@
     </row>
     <row r="14" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1418</v>
+        <v>1445</v>
       </c>
       <c r="B14" s="7">
         <v>1.25</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>1419</v>
+        <v>1446</v>
       </c>
       <c r="D14" s="7">
         <v>0.01</v>
@@ -10530,13 +10606,13 @@
     </row>
     <row r="15" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>1420</v>
+        <v>1447</v>
       </c>
       <c r="B15" s="7">
         <v>1.7</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>1421</v>
+        <v>1448</v>
       </c>
       <c r="D15" s="7">
         <v>0.01</v>
@@ -10545,13 +10621,13 @@
     </row>
     <row r="16" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1422</v>
+        <v>1449</v>
       </c>
       <c r="B16" s="7">
         <v>1.5</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>1423</v>
+        <v>1450</v>
       </c>
       <c r="D16" s="7">
         <v>1</v>
@@ -10560,13 +10636,13 @@
     </row>
     <row r="17" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>1424</v>
+        <v>1451</v>
       </c>
       <c r="B17" s="7">
         <v>0.4</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>1425</v>
+        <v>1452</v>
       </c>
       <c r="D17" s="7">
         <v>0.01</v>
@@ -10577,13 +10653,13 @@
     </row>
     <row r="18" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1426</v>
+        <v>1453</v>
       </c>
       <c r="B18" s="7">
         <v>5</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1427</v>
+        <v>1454</v>
       </c>
       <c r="D18" s="7">
         <v>0</v>
@@ -10592,13 +10668,13 @@
     </row>
     <row r="19" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>1428</v>
+        <v>1455</v>
       </c>
       <c r="B19" s="7">
         <v>25</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1429</v>
+        <v>1456</v>
       </c>
       <c r="D19" s="7">
         <v>0.1</v>
@@ -10607,13 +10683,13 @@
     </row>
     <row r="20" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>1430</v>
+        <v>1457</v>
       </c>
       <c r="B20" s="7">
         <v>0.35</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>1431</v>
+        <v>1458</v>
       </c>
       <c r="D20" s="7">
         <v>0</v>
@@ -10624,13 +10700,13 @@
     </row>
     <row r="21" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>1432</v>
+        <v>1459</v>
       </c>
       <c r="B21" s="7">
         <v>0.3</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>1433</v>
+        <v>1460</v>
       </c>
       <c r="D21" s="7">
         <v>0</v>
@@ -10641,13 +10717,13 @@
     </row>
     <row r="22" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>1434</v>
+        <v>1461</v>
       </c>
       <c r="B22" s="7">
         <v>0.55</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>1435</v>
+        <v>1462</v>
       </c>
       <c r="D22" s="7">
         <v>0</v>
@@ -10658,13 +10734,13 @@
     </row>
     <row r="23" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>1436</v>
+        <v>1463</v>
       </c>
       <c r="B23" s="7">
         <v>4</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>1437</v>
+        <v>1464</v>
       </c>
       <c r="D23" s="7">
         <v>0</v>
@@ -10673,13 +10749,13 @@
     </row>
     <row r="24" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>1438</v>
+        <v>1465</v>
       </c>
       <c r="B24" s="7">
         <v>2</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>1439</v>
+        <v>1466</v>
       </c>
       <c r="D24" s="7">
         <v>0</v>
@@ -10688,13 +10764,13 @@
     </row>
     <row r="25" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>1440</v>
+        <v>1467</v>
       </c>
       <c r="B25" s="7">
         <v>9</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>1441</v>
+        <v>1468</v>
       </c>
       <c r="D25" s="7">
         <v>0</v>
@@ -10703,13 +10779,13 @@
     </row>
     <row r="26" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>1442</v>
+        <v>1469</v>
       </c>
       <c r="B26" s="7">
         <v>4</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>1443</v>
+        <v>1470</v>
       </c>
       <c r="D26" s="7">
         <v>0</v>
@@ -10718,13 +10794,13 @@
     </row>
     <row r="27" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>1444</v>
+        <v>1471</v>
       </c>
       <c r="B27" s="7">
         <v>7</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>1445</v>
+        <v>1472</v>
       </c>
       <c r="D27" s="7">
         <v>0</v>
@@ -10733,13 +10809,13 @@
     </row>
     <row r="28" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>1446</v>
+        <v>1473</v>
       </c>
       <c r="B28" s="7">
         <v>0.3</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>1447</v>
+        <v>1474</v>
       </c>
       <c r="D28" s="7">
         <v>0</v>
@@ -10750,13 +10826,13 @@
     </row>
     <row r="29" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>1448</v>
+        <v>1475</v>
       </c>
       <c r="B29" s="7">
         <v>0.2</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>1449</v>
+        <v>1476</v>
       </c>
       <c r="D29" s="7">
         <v>0</v>
@@ -10765,13 +10841,13 @@
     </row>
     <row r="30" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>1450</v>
+        <v>1477</v>
       </c>
       <c r="B30" s="7">
         <v>12</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>1451</v>
+        <v>1478</v>
       </c>
       <c r="D30" s="7">
         <v>1</v>
@@ -10782,13 +10858,13 @@
     </row>
     <row r="31" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>1452</v>
+        <v>1479</v>
       </c>
       <c r="B31" s="7">
         <v>3</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>1453</v>
+        <v>1480</v>
       </c>
       <c r="D31" s="7">
         <v>1</v>
@@ -10799,13 +10875,13 @@
     </row>
     <row r="32" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>1454</v>
+        <v>1481</v>
       </c>
       <c r="B32" s="7">
         <v>0.35</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>1455</v>
+        <v>1482</v>
       </c>
       <c r="D32" s="7">
         <v>0</v>
@@ -10816,13 +10892,13 @@
     </row>
     <row r="33" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>1456</v>
+        <v>1483</v>
       </c>
       <c r="B33" s="7">
         <v>0.5</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>1457</v>
+        <v>1484</v>
       </c>
       <c r="D33" s="7">
         <v>0</v>
@@ -10833,13 +10909,13 @@
     </row>
     <row r="34" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>1458</v>
+        <v>1485</v>
       </c>
       <c r="B34" s="7">
         <v>2</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>1459</v>
+        <v>1486</v>
       </c>
       <c r="D34" s="7">
         <v>1</v>
@@ -10850,13 +10926,13 @@
     </row>
     <row r="35" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>1460</v>
+        <v>1487</v>
       </c>
       <c r="B35" s="7">
         <v>4</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>1461</v>
+        <v>1488</v>
       </c>
       <c r="D35" s="7">
         <v>1</v>
@@ -10867,13 +10943,13 @@
     </row>
     <row r="36" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>1462</v>
+        <v>1489</v>
       </c>
       <c r="B36" s="7">
         <v>1.5</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>1463</v>
+        <v>1490</v>
       </c>
       <c r="D36" s="7">
         <v>0</v>
@@ -10882,13 +10958,13 @@
     </row>
     <row r="37" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>1464</v>
+        <v>1491</v>
       </c>
       <c r="B37" s="7">
         <v>5</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>1465</v>
+        <v>1492</v>
       </c>
       <c r="D37" s="7">
         <v>0</v>
@@ -10897,13 +10973,13 @@
     </row>
     <row r="38" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>1466</v>
+        <v>1493</v>
       </c>
       <c r="B38" s="7">
         <v>7</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>1467</v>
+        <v>1494</v>
       </c>
       <c r="D38" s="7">
         <v>0</v>
@@ -10912,13 +10988,13 @@
     </row>
     <row r="39" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>1468</v>
+        <v>1495</v>
       </c>
       <c r="B39" s="7">
         <v>9</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>1469</v>
+        <v>1496</v>
       </c>
       <c r="D39" s="7">
         <v>0</v>
@@ -10927,13 +11003,13 @@
     </row>
     <row r="40" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>1470</v>
+        <v>1497</v>
       </c>
       <c r="B40" s="7">
         <v>8</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>1471</v>
+        <v>1498</v>
       </c>
       <c r="D40" s="7">
         <v>0.1</v>
@@ -10942,13 +11018,13 @@
     </row>
     <row r="41" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>1472</v>
+        <v>1499</v>
       </c>
       <c r="B41" s="7">
         <v>4.5</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>1473</v>
+        <v>1500</v>
       </c>
       <c r="D41" s="7">
         <v>0.1</v>
@@ -10957,13 +11033,13 @@
     </row>
     <row r="42" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>1474</v>
+        <v>1501</v>
       </c>
       <c r="B42" s="7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>1475</v>
+        <v>1502</v>
       </c>
       <c r="D42" s="7">
         <v>0.1</v>
@@ -10992,22 +11068,22 @@
         <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>909</v>
+        <v>936</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1476</v>
+        <v>1503</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1477</v>
+        <v>1504</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1478</v>
+        <v>1505</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>1479</v>
+        <v>1506</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>1480</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -11015,22 +11091,22 @@
         <v>87</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>911</v>
+        <v>938</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1481</v>
+        <v>1508</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1482</v>
+        <v>1509</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>1483</v>
+        <v>1510</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>1484</v>
+        <v>1511</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>1485</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -11125,10 +11201,10 @@
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="C7" s="7" t="b">
         <v>0</v>
@@ -11167,10 +11243,10 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1075</v>
+        <v>1102</v>
       </c>
       <c r="C9" s="7" t="b">
         <v>0</v>
@@ -11188,10 +11264,10 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1106</v>
+        <v>1133</v>
       </c>
       <c r="C10" s="7" t="b">
         <v>0</v>
@@ -11305,7 +11381,7 @@
         <v>0.7</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>1255</v>
+        <v>1282</v>
       </c>
       <c r="F15" s="7">
         <v>0.8</v>
@@ -11328,7 +11404,7 @@
         <v>0.7</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>1255</v>
+        <v>1282</v>
       </c>
       <c r="F16" s="7">
         <v>0.8</v>
@@ -11353,10 +11429,10 @@
   <sheetData>
     <row r="1" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1486</v>
+        <v>1513</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1487</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11364,7 +11440,7 @@
         <v>87</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>912</v>
+        <v>939</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11393,66 +11469,66 @@
     </row>
     <row r="6" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1488</v>
+        <v>1515</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1489</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="7" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1490</v>
+        <v>1517</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1491</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>884</v>
+        <v>911</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1492</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1289</v>
+        <v>1316</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1493</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="10" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1291</v>
+        <v>1318</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1494</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="11" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>1293</v>
+        <v>1320</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1495</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="12" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1295</v>
+        <v>1322</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1496</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="13" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>1297</v>
+        <v>1324</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1497</v>
+        <v>1524</v>
       </c>
     </row>
   </sheetData>
@@ -11472,16 +11548,16 @@
   <sheetData>
     <row r="1" ht="54" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1498</v>
+        <v>1525</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1499</v>
+        <v>1526</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1500</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11489,13 +11565,13 @@
         <v>87</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>911</v>
+        <v>938</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>528</v>
+        <v>555</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>912</v>
+        <v>939</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11542,7 +11618,7 @@
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1501</v>
+        <v>1528</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>123</v>
@@ -11551,12 +11627,12 @@
         <v>1</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1502</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1503</v>
+        <v>1530</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>123</v>
@@ -11565,12 +11641,12 @@
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1504</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1505</v>
+        <v>1532</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>123</v>
@@ -11579,7 +11655,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1506</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11593,7 +11669,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11607,12 +11683,12 @@
         <v>2</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>1509</v>
+        <v>1536</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>195</v>
@@ -11621,12 +11697,12 @@
         <v>3</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1511</v>
+        <v>1538</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>197</v>
@@ -11635,12 +11711,12 @@
         <v>1</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1512</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>1513</v>
+        <v>1540</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>197</v>
@@ -11649,12 +11725,12 @@
         <v>2</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1195</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1514</v>
+        <v>1541</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>197</v>
@@ -11663,7 +11739,7 @@
         <v>3</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1197</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11677,7 +11753,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11691,7 +11767,7 @@
         <v>2</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11705,12 +11781,12 @@
         <v>3</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1515</v>
+        <v>1542</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>204</v>
@@ -11719,12 +11795,12 @@
         <v>1</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1516</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>1517</v>
+        <v>1544</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>204</v>
@@ -11733,12 +11809,12 @@
         <v>2</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1045</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>1518</v>
+        <v>1545</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>204</v>
@@ -11747,7 +11823,7 @@
         <v>3</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1047</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11761,7 +11837,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11775,7 +11851,7 @@
         <v>2</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11789,12 +11865,12 @@
         <v>3</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>1519</v>
+        <v>1546</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>211</v>
@@ -11803,12 +11879,12 @@
         <v>1</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1520</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>1521</v>
+        <v>1548</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>211</v>
@@ -11817,12 +11893,12 @@
         <v>2</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>1165</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>1522</v>
+        <v>1549</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>211</v>
@@ -11831,7 +11907,7 @@
         <v>3</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1167</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11845,7 +11921,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="28" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11859,7 +11935,7 @@
         <v>2</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="29" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11873,12 +11949,12 @@
         <v>3</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="30" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>1523</v>
+        <v>1550</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>217</v>
@@ -11887,12 +11963,12 @@
         <v>1</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1524</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="31" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>1525</v>
+        <v>1552</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>217</v>
@@ -11901,12 +11977,12 @@
         <v>2</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>1137</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="32" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>1526</v>
+        <v>1553</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>217</v>
@@ -11915,7 +11991,7 @@
         <v>3</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>1139</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="33" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11929,7 +12005,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="34" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11943,7 +12019,7 @@
         <v>2</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="35" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11957,12 +12033,12 @@
         <v>3</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="36" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>1527</v>
+        <v>1554</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>223</v>
@@ -11971,12 +12047,12 @@
         <v>1</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1528</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="37" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>1529</v>
+        <v>1556</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>223</v>
@@ -11985,12 +12061,12 @@
         <v>2</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>1225</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="38" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>1530</v>
+        <v>1557</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>223</v>
@@ -11999,12 +12075,12 @@
         <v>3</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>1227</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="39" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>1531</v>
+        <v>1558</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>232</v>
@@ -12013,12 +12089,12 @@
         <v>1</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>1255</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="40" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>1532</v>
+        <v>1559</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>232</v>
@@ -12027,12 +12103,12 @@
         <v>2</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>1533</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="41" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>1534</v>
+        <v>1561</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>232</v>
@@ -12041,12 +12117,12 @@
         <v>3</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>1535</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>1536</v>
+        <v>1563</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>236</v>
@@ -12055,12 +12131,12 @@
         <v>1</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="43" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>1537</v>
+        <v>1564</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>236</v>
@@ -12069,12 +12145,12 @@
         <v>2</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="44" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>1538</v>
+        <v>1565</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>236</v>
@@ -12083,12 +12159,12 @@
         <v>3</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="45" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>1539</v>
+        <v>1566</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>240</v>
@@ -12097,12 +12173,12 @@
         <v>1</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="46" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>1540</v>
+        <v>1567</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>240</v>
@@ -12111,12 +12187,12 @@
         <v>2</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="47" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>1541</v>
+        <v>1568</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>240</v>
@@ -12125,138 +12201,138 @@
         <v>3</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="48" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>1542</v>
+        <v>1569</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>1509</v>
+        <v>1536</v>
       </c>
       <c r="C48" s="7">
         <v>1</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="49" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>1543</v>
+        <v>1570</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>1509</v>
+        <v>1536</v>
       </c>
       <c r="C49" s="7">
         <v>2</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="50" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>1544</v>
+        <v>1571</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>1509</v>
+        <v>1536</v>
       </c>
       <c r="C50" s="7">
         <v>3</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="51" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>1545</v>
+        <v>1572</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>1546</v>
+        <v>1573</v>
       </c>
       <c r="C51" s="7">
         <v>1</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="52" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>1547</v>
+        <v>1574</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>1546</v>
+        <v>1573</v>
       </c>
       <c r="C52" s="7">
         <v>2</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="53" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>1548</v>
+        <v>1575</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>1546</v>
+        <v>1573</v>
       </c>
       <c r="C53" s="7">
         <v>3</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="54" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>1549</v>
+        <v>1576</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>1550</v>
+        <v>1577</v>
       </c>
       <c r="C54" s="7">
         <v>1</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="55" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>1551</v>
+        <v>1578</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>1550</v>
+        <v>1577</v>
       </c>
       <c r="C55" s="7">
         <v>2</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="56" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>1552</v>
+        <v>1579</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>1550</v>
+        <v>1577</v>
       </c>
       <c r="C56" s="7">
         <v>3</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="57" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>1553</v>
+        <v>1580</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>244</v>
@@ -12265,12 +12341,12 @@
         <v>1</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="58" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>1554</v>
+        <v>1581</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>244</v>
@@ -12279,12 +12355,12 @@
         <v>2</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="59" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>1555</v>
+        <v>1582</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>244</v>
@@ -12293,12 +12369,12 @@
         <v>3</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="60" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>1556</v>
+        <v>1583</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>248</v>
@@ -12307,12 +12383,12 @@
         <v>1</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="61" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>1557</v>
+        <v>1584</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>248</v>
@@ -12321,12 +12397,12 @@
         <v>2</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="62" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>1558</v>
+        <v>1585</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>248</v>
@@ -12335,12 +12411,12 @@
         <v>3</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="63" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>1559</v>
+        <v>1586</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>252</v>
@@ -12349,12 +12425,12 @@
         <v>1</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="64" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>1560</v>
+        <v>1587</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>252</v>
@@ -12363,12 +12439,12 @@
         <v>2</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="65" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>1561</v>
+        <v>1588</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>252</v>
@@ -12377,96 +12453,96 @@
         <v>3</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="66" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>1562</v>
+        <v>1589</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>1563</v>
+        <v>1590</v>
       </c>
       <c r="C66" s="7">
         <v>1</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="67" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>1564</v>
+        <v>1591</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>1563</v>
+        <v>1590</v>
       </c>
       <c r="C67" s="7">
         <v>2</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="68" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>1565</v>
+        <v>1592</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>1563</v>
+        <v>1590</v>
       </c>
       <c r="C68" s="7">
         <v>3</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="69" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>1566</v>
+        <v>1593</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>1567</v>
+        <v>1594</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="70" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>1568</v>
+        <v>1595</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>1567</v>
+        <v>1594</v>
       </c>
       <c r="C70" s="7">
         <v>2</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="71" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>1569</v>
+        <v>1596</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>1567</v>
+        <v>1594</v>
       </c>
       <c r="C71" s="7">
         <v>3</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="72" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>1570</v>
+        <v>1597</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>256</v>
@@ -12475,12 +12551,12 @@
         <v>1</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="73" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>1571</v>
+        <v>1598</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>256</v>
@@ -12489,12 +12565,12 @@
         <v>2</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="74" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>1572</v>
+        <v>1599</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>256</v>
@@ -12503,12 +12579,12 @@
         <v>3</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="75" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>1573</v>
+        <v>1600</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>260</v>
@@ -12517,12 +12593,12 @@
         <v>1</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="76" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>1574</v>
+        <v>1601</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>260</v>
@@ -12531,12 +12607,12 @@
         <v>2</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="77" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>1575</v>
+        <v>1602</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>260</v>
@@ -12545,12 +12621,12 @@
         <v>3</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="78" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>1576</v>
+        <v>1603</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>262</v>
@@ -12559,12 +12635,12 @@
         <v>1</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="79" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>1577</v>
+        <v>1604</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>262</v>
@@ -12573,12 +12649,12 @@
         <v>2</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="80" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>1578</v>
+        <v>1605</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>262</v>
@@ -12587,12 +12663,12 @@
         <v>3</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="81" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>1579</v>
+        <v>1606</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>264</v>
@@ -12601,12 +12677,12 @@
         <v>1</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="82" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>1580</v>
+        <v>1607</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>264</v>
@@ -12615,12 +12691,12 @@
         <v>2</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="83" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>1581</v>
+        <v>1608</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>264</v>
@@ -12629,54 +12705,54 @@
         <v>3</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="84" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>1582</v>
+        <v>1609</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>1583</v>
+        <v>1610</v>
       </c>
       <c r="C84" s="7">
         <v>1</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="85" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>1584</v>
+        <v>1611</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>1583</v>
+        <v>1610</v>
       </c>
       <c r="C85" s="7">
         <v>2</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="86" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>1585</v>
+        <v>1612</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>1583</v>
+        <v>1610</v>
       </c>
       <c r="C86" s="7">
         <v>3</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="87" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>1586</v>
+        <v>1613</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>268</v>
@@ -12685,12 +12761,12 @@
         <v>1</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="88" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>1587</v>
+        <v>1614</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>268</v>
@@ -12699,12 +12775,12 @@
         <v>2</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="89" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>1588</v>
+        <v>1615</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>268</v>
@@ -12713,12 +12789,12 @@
         <v>3</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="90" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>1589</v>
+        <v>1616</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>272</v>
@@ -12727,12 +12803,12 @@
         <v>1</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="91" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>1590</v>
+        <v>1617</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>272</v>
@@ -12741,12 +12817,12 @@
         <v>2</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="92" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
-        <v>1591</v>
+        <v>1618</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>272</v>
@@ -12755,12 +12831,12 @@
         <v>3</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="93" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>1592</v>
+        <v>1619</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>274</v>
@@ -12769,12 +12845,12 @@
         <v>1</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="94" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>1593</v>
+        <v>1620</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>274</v>
@@ -12783,12 +12859,12 @@
         <v>2</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="95" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>1594</v>
+        <v>1621</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>274</v>
@@ -12797,12 +12873,12 @@
         <v>3</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="96" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>1595</v>
+        <v>1622</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>276</v>
@@ -12811,12 +12887,12 @@
         <v>1</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="97" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>1596</v>
+        <v>1623</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>276</v>
@@ -12825,12 +12901,12 @@
         <v>2</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="98" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>1597</v>
+        <v>1624</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>276</v>
@@ -12839,54 +12915,54 @@
         <v>3</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="99" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>1598</v>
+        <v>1625</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>1599</v>
+        <v>1626</v>
       </c>
       <c r="C99" s="7">
         <v>1</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="100" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>1600</v>
+        <v>1627</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>1599</v>
+        <v>1626</v>
       </c>
       <c r="C100" s="7">
         <v>2</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="101" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>1601</v>
+        <v>1628</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>1599</v>
+        <v>1626</v>
       </c>
       <c r="C101" s="7">
         <v>3</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="102" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
-        <v>1602</v>
+        <v>1629</v>
       </c>
       <c r="B102" s="7" t="s">
         <v>280</v>
@@ -12895,12 +12971,12 @@
         <v>1</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="103" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>1603</v>
+        <v>1630</v>
       </c>
       <c r="B103" s="7" t="s">
         <v>280</v>
@@ -12909,12 +12985,12 @@
         <v>2</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="104" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>1604</v>
+        <v>1631</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>280</v>
@@ -12923,12 +12999,12 @@
         <v>3</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="105" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>1605</v>
+        <v>1632</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>284</v>
@@ -12937,12 +13013,12 @@
         <v>1</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="106" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>1606</v>
+        <v>1633</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>284</v>
@@ -12951,12 +13027,12 @@
         <v>2</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="107" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>1607</v>
+        <v>1634</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>284</v>
@@ -12965,12 +13041,12 @@
         <v>3</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="108" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>1608</v>
+        <v>1635</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>286</v>
@@ -12979,12 +13055,12 @@
         <v>1</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="109" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>1609</v>
+        <v>1636</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>286</v>
@@ -12993,12 +13069,12 @@
         <v>2</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="110" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>1610</v>
+        <v>1637</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>286</v>
@@ -13007,12 +13083,12 @@
         <v>3</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="111" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>1611</v>
+        <v>1638</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>288</v>
@@ -13021,12 +13097,12 @@
         <v>1</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="112" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
-        <v>1612</v>
+        <v>1639</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>288</v>
@@ -13035,12 +13111,12 @@
         <v>2</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="113" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>1613</v>
+        <v>1640</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>288</v>
@@ -13049,12 +13125,12 @@
         <v>3</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="114" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>1614</v>
+        <v>1641</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>290</v>
@@ -13063,12 +13139,12 @@
         <v>1</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>1507</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="115" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>1615</v>
+        <v>1642</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>290</v>
@@ -13077,12 +13153,12 @@
         <v>2</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>1508</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="116" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
-        <v>1616</v>
+        <v>1643</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>290</v>
@@ -13091,7 +13167,7 @@
         <v>3</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>1510</v>
+        <v>1537</v>
       </c>
     </row>
   </sheetData>
@@ -13962,31 +14038,31 @@
         <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>863</v>
+        <v>890</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>864</v>
+        <v>891</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>865</v>
+        <v>892</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>866</v>
+        <v>893</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>867</v>
+        <v>894</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>868</v>
+        <v>895</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>869</v>
+        <v>896</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>870</v>
+        <v>897</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>871</v>
+        <v>898</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -13994,31 +14070,31 @@
         <v>87</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>872</v>
+        <v>899</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>873</v>
+        <v>900</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>88</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>874</v>
+        <v>901</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>875</v>
+        <v>902</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>876</v>
+        <v>903</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>877</v>
+        <v>904</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>878</v>
+        <v>905</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>879</v>
+        <v>906</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -14125,10 +14201,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>881</v>
+        <v>908</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>233</v>
@@ -14140,7 +14216,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I6" s="7" t="b">
         <v>0</v>
@@ -14155,10 +14231,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>883</v>
+        <v>910</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>237</v>
@@ -14170,7 +14246,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I7" s="7" t="b">
         <v>1</v>
@@ -14185,10 +14261,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>884</v>
+        <v>911</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>885</v>
+        <v>912</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>141</v>
@@ -14200,7 +14276,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>886</v>
+        <v>913</v>
       </c>
       <c r="I8" s="7" t="b">
         <v>0</v>
@@ -14215,10 +14291,10 @@
         <v>2</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>887</v>
+        <v>914</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>241</v>
@@ -14230,7 +14306,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I9" s="7" t="b">
         <v>0</v>
@@ -14245,10 +14321,10 @@
         <v>2</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>888</v>
+        <v>915</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>245</v>
@@ -14260,7 +14336,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I10" s="7" t="b">
         <v>1</v>
@@ -14275,10 +14351,10 @@
         <v>2</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>889</v>
+        <v>916</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>249</v>
@@ -14290,7 +14366,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I11" s="7" t="b">
         <v>0</v>
@@ -14305,10 +14381,10 @@
         <v>2</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>884</v>
+        <v>911</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>890</v>
+        <v>917</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>146</v>
@@ -14320,7 +14396,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>886</v>
+        <v>913</v>
       </c>
       <c r="I12" s="7" t="b">
         <v>0</v>
@@ -14335,10 +14411,10 @@
         <v>3</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>891</v>
+        <v>918</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>253</v>
@@ -14350,7 +14426,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I13" s="7" t="b">
         <v>0</v>
@@ -14365,10 +14441,10 @@
         <v>3</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>892</v>
+        <v>919</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>257</v>
@@ -14380,7 +14456,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I14" s="7" t="b">
         <v>1</v>
@@ -14395,10 +14471,10 @@
         <v>3</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>893</v>
+        <v>920</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>261</v>
@@ -14410,7 +14486,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I15" s="7" t="b">
         <v>0</v>
@@ -14425,10 +14501,10 @@
         <v>3</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>894</v>
+        <v>921</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>263</v>
@@ -14440,7 +14516,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I16" s="7" t="b">
         <v>0</v>
@@ -14455,10 +14531,10 @@
         <v>3</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>884</v>
+        <v>911</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>895</v>
+        <v>922</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>151</v>
@@ -14470,7 +14546,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>886</v>
+        <v>913</v>
       </c>
       <c r="I17" s="7" t="b">
         <v>0</v>
@@ -14485,10 +14561,10 @@
         <v>4</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>896</v>
+        <v>923</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>265</v>
@@ -14500,7 +14576,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I18" s="7" t="b">
         <v>0</v>
@@ -14515,10 +14591,10 @@
         <v>4</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>897</v>
+        <v>924</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>269</v>
@@ -14530,7 +14606,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I19" s="7" t="b">
         <v>1</v>
@@ -14545,10 +14621,10 @@
         <v>4</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>898</v>
+        <v>925</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>273</v>
@@ -14560,7 +14636,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I20" s="7" t="b">
         <v>0</v>
@@ -14575,10 +14651,10 @@
         <v>4</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>899</v>
+        <v>926</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>275</v>
@@ -14590,7 +14666,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I21" s="7" t="b">
         <v>0</v>
@@ -14605,10 +14681,10 @@
         <v>4</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>884</v>
+        <v>911</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>900</v>
+        <v>927</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>156</v>
@@ -14620,7 +14696,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>886</v>
+        <v>913</v>
       </c>
       <c r="I22" s="7" t="b">
         <v>0</v>
@@ -14635,10 +14711,10 @@
         <v>5</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>901</v>
+        <v>928</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>277</v>
@@ -14650,7 +14726,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I23" s="7" t="b">
         <v>0</v>
@@ -14665,10 +14741,10 @@
         <v>5</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>902</v>
+        <v>929</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>281</v>
@@ -14680,7 +14756,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I24" s="7" t="b">
         <v>1</v>
@@ -14695,10 +14771,10 @@
         <v>5</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>903</v>
+        <v>930</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>285</v>
@@ -14710,7 +14786,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I25" s="7" t="b">
         <v>0</v>
@@ -14725,10 +14801,10 @@
         <v>5</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>904</v>
+        <v>931</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>287</v>
@@ -14740,7 +14816,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I26" s="7" t="b">
         <v>0</v>
@@ -14755,10 +14831,10 @@
         <v>5</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>880</v>
+        <v>907</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>905</v>
+        <v>932</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>289</v>
@@ -14770,7 +14846,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I27" s="7" t="b">
         <v>1</v>
@@ -14785,10 +14861,10 @@
         <v>5</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>884</v>
+        <v>911</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>906</v>
+        <v>933</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>161</v>
@@ -14800,7 +14876,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>886</v>
+        <v>913</v>
       </c>
       <c r="I28" s="7" t="b">
         <v>0</v>
@@ -14815,10 +14891,10 @@
         <v>5</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>884</v>
+        <v>911</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>907</v>
+        <v>934</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>224</v>
@@ -14830,11 +14906,11 @@
         <v>0</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>908</v>
+        <v>935</v>
       </c>
       <c r="I29" s="7"/>
       <c r="J29" s="7" t="s">
-        <v>884</v>
+        <v>911</v>
       </c>
     </row>
   </sheetData>
@@ -17284,7 +17360,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S49"/>
+  <dimension ref="A1:S57"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="5" width="14" customWidth="1"/>
@@ -19522,6 +19598,302 @@
       <c r="S49" s="7" t="s">
         <v>334</v>
       </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="F50" s="11">
+        <v>75</v>
+      </c>
+      <c r="G50" s="11"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="11">
+        <v>8</v>
+      </c>
+      <c r="J50" s="11"/>
+      <c r="K50" s="11">
+        <v>1</v>
+      </c>
+      <c r="L50" s="11"/>
+      <c r="M50" s="12"/>
+      <c r="N50" s="11"/>
+      <c r="O50" s="11"/>
+      <c r="P50" s="11"/>
+      <c r="Q50" s="12"/>
+      <c r="R50" s="12"/>
+      <c r="S50" s="7"/>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="F51" s="11">
+        <v>80</v>
+      </c>
+      <c r="G51" s="11"/>
+      <c r="H51" s="12"/>
+      <c r="I51" s="11">
+        <v>8</v>
+      </c>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11">
+        <v>1</v>
+      </c>
+      <c r="L51" s="11"/>
+      <c r="M51" s="12"/>
+      <c r="N51" s="11"/>
+      <c r="O51" s="11"/>
+      <c r="P51" s="11"/>
+      <c r="Q51" s="12"/>
+      <c r="R51" s="12"/>
+      <c r="S51" s="7"/>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="F52" s="11">
+        <v>85</v>
+      </c>
+      <c r="G52" s="11"/>
+      <c r="H52" s="12"/>
+      <c r="I52" s="11">
+        <v>8</v>
+      </c>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11">
+        <v>1</v>
+      </c>
+      <c r="L52" s="11"/>
+      <c r="M52" s="12"/>
+      <c r="N52" s="11"/>
+      <c r="O52" s="11"/>
+      <c r="P52" s="11"/>
+      <c r="Q52" s="12"/>
+      <c r="R52" s="12"/>
+      <c r="S52" s="7"/>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>441</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="F53" s="11">
+        <v>90</v>
+      </c>
+      <c r="G53" s="11"/>
+      <c r="H53" s="12"/>
+      <c r="I53" s="11">
+        <v>8</v>
+      </c>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11">
+        <v>1</v>
+      </c>
+      <c r="L53" s="11"/>
+      <c r="M53" s="12"/>
+      <c r="N53" s="11"/>
+      <c r="O53" s="11"/>
+      <c r="P53" s="11"/>
+      <c r="Q53" s="12"/>
+      <c r="R53" s="12"/>
+      <c r="S53" s="7"/>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="F54" s="11">
+        <v>85</v>
+      </c>
+      <c r="G54" s="11"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="11">
+        <v>5</v>
+      </c>
+      <c r="J54" s="11">
+        <v>2</v>
+      </c>
+      <c r="K54" s="11"/>
+      <c r="L54" s="11"/>
+      <c r="M54" s="12"/>
+      <c r="N54" s="11"/>
+      <c r="O54" s="11"/>
+      <c r="P54" s="11"/>
+      <c r="Q54" s="12"/>
+      <c r="R54" s="12"/>
+      <c r="S54" s="7"/>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A55" s="12" t="s">
+        <v>445</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="F55" s="11">
+        <v>90</v>
+      </c>
+      <c r="G55" s="11"/>
+      <c r="H55" s="12"/>
+      <c r="I55" s="11">
+        <v>5</v>
+      </c>
+      <c r="J55" s="11">
+        <v>1</v>
+      </c>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="12"/>
+      <c r="N55" s="11"/>
+      <c r="O55" s="11"/>
+      <c r="P55" s="11"/>
+      <c r="Q55" s="12"/>
+      <c r="R55" s="12"/>
+      <c r="S55" s="7"/>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="F56" s="11">
+        <v>95</v>
+      </c>
+      <c r="G56" s="11"/>
+      <c r="H56" s="12"/>
+      <c r="I56" s="11">
+        <v>5</v>
+      </c>
+      <c r="J56" s="11">
+        <v>1</v>
+      </c>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="12"/>
+      <c r="N56" s="11"/>
+      <c r="O56" s="11"/>
+      <c r="P56" s="11"/>
+      <c r="Q56" s="12"/>
+      <c r="R56" s="12"/>
+      <c r="S56" s="7"/>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A57" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="F57" s="11">
+        <v>100</v>
+      </c>
+      <c r="G57" s="11"/>
+      <c r="H57" s="12"/>
+      <c r="I57" s="11">
+        <v>5</v>
+      </c>
+      <c r="J57" s="11">
+        <v>1</v>
+      </c>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="12"/>
+      <c r="N57" s="11"/>
+      <c r="O57" s="11"/>
+      <c r="P57" s="11"/>
+      <c r="Q57" s="12"/>
+      <c r="R57" s="12"/>
+      <c r="S57" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="4">
@@ -19544,7 +19916,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -19568,88 +19940,88 @@
         <v>65</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>433</v>
+        <v>452</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>437</v>
+        <v>456</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>439</v>
+        <v>458</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>449</v>
+        <v>468</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="Y1" s="4" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="Z1" s="4" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="AA1" s="4" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="AC1" s="4" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
@@ -19660,85 +20032,85 @@
         <v>88</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="N2" s="9" t="s">
-        <v>471</v>
+        <v>490</v>
       </c>
       <c r="O2" s="9" t="s">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>475</v>
+        <v>494</v>
       </c>
       <c r="S2" s="5" t="s">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>477</v>
+        <v>496</v>
       </c>
       <c r="U2" s="5" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>479</v>
+        <v>498</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>480</v>
+        <v>499</v>
       </c>
       <c r="X2" s="5" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
       <c r="Y2" s="5" t="s">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="Z2" s="5" t="s">
-        <v>483</v>
+        <v>502</v>
       </c>
       <c r="AA2" s="5" t="s">
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="AB2" s="5" t="s">
-        <v>485</v>
+        <v>504</v>
       </c>
       <c r="AC2" s="5" t="s">
-        <v>486</v>
+        <v>505</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
@@ -20013,10 +20385,10 @@
         <v>313</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="D6" s="12">
         <v>0.8</v>
@@ -20082,10 +20454,10 @@
         <v>327</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="D7" s="14">
         <v>0.8</v>
@@ -20151,10 +20523,10 @@
         <v>340</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="D8" s="16">
         <v>0.8</v>
@@ -20220,10 +20592,10 @@
         <v>353</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="D9" s="19">
         <v>0.75</v>
@@ -20289,10 +20661,10 @@
         <v>368</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="D10" s="7">
         <v>0.8</v>
@@ -20315,10 +20687,10 @@
       <c r="R10" s="21"/>
       <c r="S10" s="7"/>
       <c r="T10" s="7" t="s">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="U10" s="7" t="s">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="V10" s="21">
         <v>1</v>
@@ -20340,10 +20712,10 @@
         <v>378</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>500</v>
+        <v>519</v>
       </c>
       <c r="D11" s="7">
         <v>0.8</v>
@@ -20366,10 +20738,10 @@
       <c r="R11" s="21"/>
       <c r="S11" s="7"/>
       <c r="T11" s="7" t="s">
-        <v>501</v>
+        <v>520</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>502</v>
+        <v>521</v>
       </c>
       <c r="V11" s="21">
         <v>1</v>
@@ -20391,10 +20763,10 @@
         <v>387</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>504</v>
+        <v>523</v>
       </c>
       <c r="D12" s="7">
         <v>0.8</v>
@@ -20417,10 +20789,10 @@
       <c r="R12" s="21"/>
       <c r="S12" s="7"/>
       <c r="T12" s="7" t="s">
-        <v>505</v>
+        <v>524</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="V12" s="21">
         <v>2</v>
@@ -20442,10 +20814,10 @@
         <v>397</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>508</v>
+        <v>527</v>
       </c>
       <c r="D13" s="7">
         <v>0.8</v>
@@ -20468,10 +20840,10 @@
       <c r="R13" s="21"/>
       <c r="S13" s="7"/>
       <c r="T13" s="7" t="s">
-        <v>509</v>
+        <v>528</v>
       </c>
       <c r="U13" s="7" t="s">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="V13" s="21">
         <v>2</v>
@@ -20493,10 +20865,10 @@
         <v>406</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="D14" s="7">
         <v>0.8</v>
@@ -20525,10 +20897,10 @@
         <v>1</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>513</v>
+        <v>532</v>
       </c>
       <c r="U14" s="7" t="s">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="V14" s="21">
         <v>3</v>
@@ -20548,10 +20920,10 @@
         <v>415</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="D15" s="7">
         <v>0.8</v>
@@ -20572,10 +20944,10 @@
       <c r="R15" s="21"/>
       <c r="S15" s="7"/>
       <c r="T15" s="7" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="U15" s="7" t="s">
-        <v>518</v>
+        <v>537</v>
       </c>
       <c r="V15" s="21">
         <v>3</v>
@@ -20599,10 +20971,10 @@
         <v>425</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>520</v>
+        <v>539</v>
       </c>
       <c r="D16" s="7">
         <v>0.8</v>
@@ -20626,7 +20998,7 @@
         <v>424</v>
       </c>
       <c r="U16" s="7" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="V16" s="21">
         <v>0</v>
@@ -20640,6 +21012,110 @@
       <c r="AA16" s="7"/>
       <c r="AB16" s="7"/>
       <c r="AC16" s="7"/>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="D17" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="E17" s="11">
+        <v>20</v>
+      </c>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11">
+        <v>3</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11">
+        <v>1</v>
+      </c>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="U17" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="V17" s="21">
+        <v>4</v>
+      </c>
+      <c r="W17" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X17" s="21"/>
+      <c r="Y17" s="21"/>
+      <c r="Z17" s="7"/>
+      <c r="AA17" s="7"/>
+      <c r="AB17" s="7"/>
+      <c r="AC17" s="7"/>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>545</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="D18" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11">
+        <v>6</v>
+      </c>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="U18" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="V18" s="21">
+        <v>5</v>
+      </c>
+      <c r="W18" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18" s="21"/>
+      <c r="Y18" s="21"/>
+      <c r="Z18" s="7"/>
+      <c r="AA18" s="7"/>
+      <c r="AB18" s="7"/>
+      <c r="AC18" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20662,16 +21138,16 @@
         <v>65</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>522</v>
+        <v>549</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>523</v>
+        <v>550</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>524</v>
+        <v>551</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>525</v>
+        <v>552</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -20679,16 +21155,16 @@
         <v>87</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>526</v>
+        <v>553</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>88</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>527</v>
+        <v>554</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>528</v>
+        <v>555</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -20744,13 +21220,13 @@
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>529</v>
+        <v>556</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>530</v>
+        <v>557</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>531</v>
+        <v>558</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>118</v>
@@ -20761,16 +21237,16 @@
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>532</v>
+        <v>559</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>530</v>
+        <v>557</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>533</v>
+        <v>560</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>534</v>
+        <v>561</v>
       </c>
       <c r="E7" s="13">
         <v>1</v>
@@ -20778,13 +21254,13 @@
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>535</v>
+        <v>562</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>530</v>
+        <v>557</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>536</v>
+        <v>563</v>
       </c>
       <c r="D8" s="16" t="s">
         <v>190</v>
@@ -20795,13 +21271,13 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>537</v>
+        <v>564</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>530</v>
+        <v>557</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>538</v>
+        <v>565</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>120</v>
@@ -20812,16 +21288,16 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>539</v>
+        <v>566</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>530</v>
+        <v>557</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>540</v>
+        <v>567</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>541</v>
+        <v>568</v>
       </c>
       <c r="E10" s="15">
         <v>4</v>
@@ -20829,16 +21305,16 @@
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>542</v>
+        <v>569</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>530</v>
+        <v>557</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>543</v>
+        <v>570</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>544</v>
+        <v>571</v>
       </c>
       <c r="E11" s="13">
         <v>5</v>
@@ -20846,13 +21322,13 @@
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>545</v>
+        <v>572</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>530</v>
+        <v>557</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>546</v>
+        <v>573</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>207</v>
@@ -20863,13 +21339,13 @@
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>547</v>
+        <v>574</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>530</v>
+        <v>557</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>548</v>
+        <v>575</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>213</v>
@@ -20880,13 +21356,13 @@
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>549</v>
+        <v>576</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>530</v>
+        <v>557</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>550</v>
+        <v>577</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>219</v>
@@ -20897,16 +21373,16 @@
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>551</v>
+        <v>578</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>530</v>
+        <v>557</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>552</v>
+        <v>579</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>553</v>
+        <v>580</v>
       </c>
       <c r="E15" s="13">
         <v>9</v>
@@ -20914,13 +21390,13 @@
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>554</v>
+        <v>581</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>81</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>555</v>
+        <v>582</v>
       </c>
       <c r="D16" s="16" t="s">
         <v>122</v>
@@ -20931,13 +21407,13 @@
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>556</v>
+        <v>583</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>81</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>557</v>
+        <v>584</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>189</v>
@@ -20948,13 +21424,13 @@
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>558</v>
+        <v>585</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>81</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>559</v>
+        <v>586</v>
       </c>
       <c r="D18" s="16" t="s">
         <v>199</v>
@@ -20965,13 +21441,13 @@
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>560</v>
+        <v>587</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>81</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>561</v>
+        <v>588</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>206</v>
@@ -20982,16 +21458,16 @@
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>562</v>
+        <v>589</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>81</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>563</v>
+        <v>590</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>564</v>
+        <v>591</v>
       </c>
       <c r="E20" s="21">
         <v>2</v>
@@ -20999,16 +21475,16 @@
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>565</v>
+        <v>592</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>81</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>566</v>
+        <v>593</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>567</v>
+        <v>594</v>
       </c>
       <c r="E21" s="21">
         <v>5</v>

--- a/excel/斗鸡配置.xlsx
+++ b/excel/斗鸡配置.xlsx
@@ -1938,49 +1938,49 @@
     <t>BattleViewComp_001</t>
   </si>
   <si>
-    <t>贴身啄</t>
+    <t>鸡啄米</t>
   </si>
   <si>
     <t>BattleViewComp_002</t>
   </si>
   <si>
-    <t>跳踢</t>
+    <t>金鸡独立</t>
   </si>
   <si>
     <t>BattleViewComp_003</t>
   </si>
   <si>
-    <t>飞扑</t>
+    <t>乌鸦坐飞鸡</t>
   </si>
   <si>
     <t>BattleViewComp_004</t>
   </si>
   <si>
-    <t>腾空下砸</t>
+    <t>天外飞鸡</t>
   </si>
   <si>
     <t>BattleViewComp_005</t>
   </si>
   <si>
-    <t>扑翅冲撞</t>
+    <t>铁头功</t>
   </si>
   <si>
     <t>BattleViewComp_006</t>
   </si>
   <si>
-    <t>转身扫尾</t>
+    <t>神龙摆尾</t>
   </si>
   <si>
     <t>BattleViewComp_007</t>
   </si>
   <si>
-    <t>连啄</t>
+    <t>连珠神啄</t>
   </si>
   <si>
     <t>BattleViewComp_008</t>
   </si>
   <si>
-    <t>假动作偷袭</t>
+    <t>金蝉脱壳</t>
   </si>
   <si>
     <t>BattleViewComp_009</t>

--- a/excel/斗鸡配置.xlsx
+++ b/excel/斗鸡配置.xlsx
@@ -10549,7 +10549,7 @@
         <v>1439</v>
       </c>
       <c r="B11" s="7">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>1440</v>

--- a/excel/斗鸡配置.xlsx
+++ b/excel/斗鸡配置.xlsx
@@ -10519,7 +10519,7 @@
         <v>1435</v>
       </c>
       <c r="B9" s="7">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>1436</v>
@@ -10549,7 +10549,7 @@
         <v>1439</v>
       </c>
       <c r="B11" s="7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>1440</v>

--- a/excel/斗鸡配置.xlsx
+++ b/excel/斗鸡配置.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3262" uniqueCount="1644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3250" uniqueCount="1641">
   <si>
     <t>斗鸡配置</t>
   </si>
@@ -2787,9 +2787,6 @@
     <t>青竹溪 · 热身赛2</t>
   </si>
   <si>
-    <t>青竹溪 · 热身赛3</t>
-  </si>
-  <si>
     <t>青竹溪 · 肯德鸡正式赛</t>
   </si>
   <si>
@@ -2802,9 +2799,6 @@
     <t>金穗田 · 热身赛3</t>
   </si>
   <si>
-    <t>金穗田 · 热身赛4</t>
-  </si>
-  <si>
     <t>金穗田 · 哈鸡米正式赛</t>
   </si>
   <si>
@@ -2815,9 +2809,6 @@
   </si>
   <si>
     <t>古祠镇 · 热身赛3</t>
-  </si>
-  <si>
-    <t>古祠镇 · 热身赛4</t>
   </si>
   <si>
     <t>古祠镇 · 新一鸡正式赛</t>
@@ -7593,10 +7584,10 @@
         <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -7604,10 +7595,10 @@
         <v>87</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -7645,2037 +7636,2037 @@
     </row>
     <row r="6" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
     </row>
     <row r="7" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
     </row>
     <row r="8" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
     </row>
     <row r="9" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
     </row>
     <row r="10" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
     </row>
     <row r="11" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
     </row>
     <row r="12" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
     </row>
     <row r="13" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
     </row>
     <row r="14" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
     </row>
     <row r="15" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
     </row>
     <row r="16" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
     </row>
     <row r="17" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
     </row>
     <row r="18" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
     </row>
     <row r="19" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
     </row>
     <row r="20" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
     </row>
     <row r="21" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
     </row>
     <row r="22" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
     </row>
     <row r="23" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
     </row>
     <row r="24" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
     </row>
     <row r="25" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
     </row>
     <row r="26" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
     </row>
     <row r="27" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
     </row>
     <row r="28" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
     </row>
     <row r="29" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
     </row>
     <row r="30" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
     </row>
     <row r="31" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
     </row>
     <row r="32" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
     </row>
     <row r="33" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
     </row>
     <row r="34" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
     </row>
     <row r="35" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
     </row>
     <row r="36" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="37" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="38" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="39" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="40" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="41" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="42" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="43" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="44" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="45" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="46" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="47" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="48" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="49" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="50" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="51" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="52" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="53" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="54" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="55" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="56" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="57" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="B57" s="7" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C57" s="7" t="s">
         <v>1041</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="58" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="59" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="60" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="61" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="62" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="63" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="64" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="65" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="66" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="67" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="68" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="69" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="70" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="71" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="72" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="73" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="74" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="75" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="76" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="77" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="78" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="79" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="80" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="81" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="82" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="83" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="84" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="85" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="86" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="87" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="B87" s="7" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C87" s="7" t="s">
         <v>1102</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="88" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="89" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="90" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="91" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="92" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="93" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="94" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="95" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="96" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="97" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="98" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="99" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="100" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="101" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="102" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="B102" s="7" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C102" s="7" t="s">
         <v>1133</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="103" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="104" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="105" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="106" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="107" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="108" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="109" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="110" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="111" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="112" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="113" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="114" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="115" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="116" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="117" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="118" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="119" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="120" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="121" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="122" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="123" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="124" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="125" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="126" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="127" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="128" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="129" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="130" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="131" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="132" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="133" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="134" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="135" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="136" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="137" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="138" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="139" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="140" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="141" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="142" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="143" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="144" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="7" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="145" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="146" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="147" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="148" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="149" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="150" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="151" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="152" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="153" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="154" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="155" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="156" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="157" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="B157" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="158" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="159" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="160" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="161" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="162" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="B162" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="163" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="B163" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="164" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="165" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="B165" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="166" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="B166" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="167" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="168" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="7" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="B168" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="169" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="B169" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="170" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="7" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="B170" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C170" s="7" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="171" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="B171" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C171" s="7" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="172" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="B172" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C172" s="7" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="173" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="B173" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="174" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="B174" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C174" s="7" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="175" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="B175" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="176" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="B176" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="177" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="B177" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="178" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="179" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="B179" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="180" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="B180" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C180" s="7" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="181" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="B181" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C181" s="7" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="182" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="7" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="B182" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C182" s="7" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="183" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="B183" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C183" s="7" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="184" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="7" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="B184" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C184" s="7" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="185" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="B185" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C185" s="7" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="186" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="7" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="B186" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C186" s="7" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="187" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="B187" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="188" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="B188" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C188" s="7" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="189" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C189" s="7" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="190" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="7" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="B190" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C190" s="7" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
     </row>
   </sheetData>
@@ -9697,10 +9688,10 @@
         <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9752,10 +9743,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9763,10 +9754,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9774,10 +9765,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9785,10 +9776,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9796,10 +9787,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
     </row>
   </sheetData>
@@ -9821,7 +9812,7 @@
         <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -9829,7 +9820,7 @@
         <v>87</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -9858,79 +9849,79 @@
     </row>
     <row r="6" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="7" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="8" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="9" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="10" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="11" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="12" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="13" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="14" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="15" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>699</v>
@@ -9938,15 +9929,15 @@
     </row>
     <row r="16" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="17" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>703</v>
@@ -9954,175 +9945,175 @@
     </row>
     <row r="18" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="19" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="20" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="21" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="22" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="23" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="24" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="25" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="26" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="27" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>1362</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="28" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="29" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="30" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="31" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="32" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="33" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="34" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="35" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="36" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="37" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="38" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>1383</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="39" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>1384</v>
+        <v>1381</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>724</v>
@@ -10130,111 +10121,111 @@
     </row>
     <row r="40" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="41" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="42" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="43" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="44" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="45" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="46" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>1392</v>
+        <v>1389</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="47" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="48" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>1394</v>
+        <v>1391</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="49" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>1395</v>
+        <v>1392</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="50" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>1396</v>
+        <v>1393</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="51" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>1397</v>
+        <v>1394</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="52" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>1398</v>
+        <v>1395</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="53" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>1399</v>
+        <v>1396</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>699</v>
@@ -10242,7 +10233,7 @@
     </row>
     <row r="54" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>772</v>
@@ -10250,15 +10241,15 @@
     </row>
     <row r="55" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="56" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>1403</v>
+        <v>1400</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>761</v>
@@ -10266,7 +10257,7 @@
     </row>
     <row r="57" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>1404</v>
+        <v>1401</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>761</v>
@@ -10274,55 +10265,55 @@
     </row>
     <row r="58" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>1405</v>
+        <v>1402</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>1406</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="59" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>1407</v>
+        <v>1404</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>1408</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="60" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>1409</v>
+        <v>1406</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="61" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="62" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="63" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>1412</v>
+        <v>1409</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>1413</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="64" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>1414</v>
+        <v>1411</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>759</v>
@@ -10330,39 +10321,39 @@
     </row>
     <row r="65" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>1415</v>
+        <v>1412</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>1416</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="66" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>1417</v>
+        <v>1414</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="67" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>1418</v>
+        <v>1415</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>1419</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>1420</v>
+        <v>1417</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>1421</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>885</v>
@@ -10389,16 +10380,16 @@
         <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>1423</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>1424</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>1425</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>1426</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -10412,10 +10403,10 @@
         <v>301</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>1428</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -10471,13 +10462,13 @@
     </row>
     <row r="6" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="B6" s="7">
         <v>1.6</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="D6" s="7">
         <v>0.01</v>
@@ -10486,13 +10477,13 @@
     </row>
     <row r="7" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="B7" s="7">
         <v>20</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1432</v>
+        <v>1429</v>
       </c>
       <c r="D7" s="7">
         <v>0.01</v>
@@ -10501,13 +10492,13 @@
     </row>
     <row r="8" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1433</v>
+        <v>1430</v>
       </c>
       <c r="B8" s="7">
         <v>0.55</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="D8" s="7">
         <v>0.01</v>
@@ -10516,13 +10507,13 @@
     </row>
     <row r="9" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1435</v>
+        <v>1432</v>
       </c>
       <c r="B9" s="7">
         <v>0.32</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1436</v>
+        <v>1433</v>
       </c>
       <c r="D9" s="7">
         <v>0.001</v>
@@ -10531,13 +10522,13 @@
     </row>
     <row r="10" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="B10" s="7">
         <v>6</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="D10" s="7">
         <v>0.01</v>
@@ -10546,13 +10537,13 @@
     </row>
     <row r="11" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="B11" s="7">
         <v>8</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="D11" s="7">
         <v>0.01</v>
@@ -10561,13 +10552,13 @@
     </row>
     <row r="12" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="B12" s="7">
         <v>0.12</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>1442</v>
+        <v>1439</v>
       </c>
       <c r="D12" s="7">
         <v>0</v>
@@ -10576,13 +10567,13 @@
     </row>
     <row r="13" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>1443</v>
+        <v>1440</v>
       </c>
       <c r="B13" s="7">
         <v>0.92</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>1444</v>
+        <v>1441</v>
       </c>
       <c r="D13" s="7">
         <v>0.01</v>
@@ -10591,13 +10582,13 @@
     </row>
     <row r="14" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="B14" s="7">
         <v>1.25</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="D14" s="7">
         <v>0.01</v>
@@ -10606,13 +10597,13 @@
     </row>
     <row r="15" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>1447</v>
+        <v>1444</v>
       </c>
       <c r="B15" s="7">
         <v>1.7</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="D15" s="7">
         <v>0.01</v>
@@ -10621,13 +10612,13 @@
     </row>
     <row r="16" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="B16" s="7">
         <v>1.5</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="D16" s="7">
         <v>1</v>
@@ -10636,13 +10627,13 @@
     </row>
     <row r="17" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="B17" s="7">
         <v>0.4</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>1452</v>
+        <v>1449</v>
       </c>
       <c r="D17" s="7">
         <v>0.01</v>
@@ -10653,13 +10644,13 @@
     </row>
     <row r="18" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1453</v>
+        <v>1450</v>
       </c>
       <c r="B18" s="7">
         <v>5</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1454</v>
+        <v>1451</v>
       </c>
       <c r="D18" s="7">
         <v>0</v>
@@ -10668,13 +10659,13 @@
     </row>
     <row r="19" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="B19" s="7">
         <v>25</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1456</v>
+        <v>1453</v>
       </c>
       <c r="D19" s="7">
         <v>0.1</v>
@@ -10683,13 +10674,13 @@
     </row>
     <row r="20" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>1457</v>
+        <v>1454</v>
       </c>
       <c r="B20" s="7">
         <v>0.35</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="D20" s="7">
         <v>0</v>
@@ -10700,13 +10691,13 @@
     </row>
     <row r="21" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>1459</v>
+        <v>1456</v>
       </c>
       <c r="B21" s="7">
         <v>0.3</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>1460</v>
+        <v>1457</v>
       </c>
       <c r="D21" s="7">
         <v>0</v>
@@ -10717,13 +10708,13 @@
     </row>
     <row r="22" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>1461</v>
+        <v>1458</v>
       </c>
       <c r="B22" s="7">
         <v>0.55</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>1462</v>
+        <v>1459</v>
       </c>
       <c r="D22" s="7">
         <v>0</v>
@@ -10734,13 +10725,13 @@
     </row>
     <row r="23" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>1463</v>
+        <v>1460</v>
       </c>
       <c r="B23" s="7">
         <v>4</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>1464</v>
+        <v>1461</v>
       </c>
       <c r="D23" s="7">
         <v>0</v>
@@ -10749,13 +10740,13 @@
     </row>
     <row r="24" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>1465</v>
+        <v>1462</v>
       </c>
       <c r="B24" s="7">
         <v>2</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>1466</v>
+        <v>1463</v>
       </c>
       <c r="D24" s="7">
         <v>0</v>
@@ -10764,13 +10755,13 @@
     </row>
     <row r="25" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
       <c r="B25" s="7">
         <v>9</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="D25" s="7">
         <v>0</v>
@@ -10779,13 +10770,13 @@
     </row>
     <row r="26" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="B26" s="7">
         <v>4</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>1470</v>
+        <v>1467</v>
       </c>
       <c r="D26" s="7">
         <v>0</v>
@@ -10794,13 +10785,13 @@
     </row>
     <row r="27" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
       <c r="B27" s="7">
         <v>7</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
       <c r="D27" s="7">
         <v>0</v>
@@ -10809,13 +10800,13 @@
     </row>
     <row r="28" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>1473</v>
+        <v>1470</v>
       </c>
       <c r="B28" s="7">
         <v>0.3</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
       <c r="D28" s="7">
         <v>0</v>
@@ -10826,13 +10817,13 @@
     </row>
     <row r="29" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>1475</v>
+        <v>1472</v>
       </c>
       <c r="B29" s="7">
         <v>0.2</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>1476</v>
+        <v>1473</v>
       </c>
       <c r="D29" s="7">
         <v>0</v>
@@ -10841,13 +10832,13 @@
     </row>
     <row r="30" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
       <c r="B30" s="7">
         <v>12</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
       <c r="D30" s="7">
         <v>1</v>
@@ -10858,13 +10849,13 @@
     </row>
     <row r="31" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
       <c r="B31" s="7">
         <v>3</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
       <c r="D31" s="7">
         <v>1</v>
@@ -10875,13 +10866,13 @@
     </row>
     <row r="32" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
       <c r="B32" s="7">
         <v>0.35</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="D32" s="7">
         <v>0</v>
@@ -10892,13 +10883,13 @@
     </row>
     <row r="33" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="B33" s="7">
         <v>0.5</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="D33" s="7">
         <v>0</v>
@@ -10909,13 +10900,13 @@
     </row>
     <row r="34" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>1485</v>
+        <v>1482</v>
       </c>
       <c r="B34" s="7">
         <v>2</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>1486</v>
+        <v>1483</v>
       </c>
       <c r="D34" s="7">
         <v>1</v>
@@ -10926,13 +10917,13 @@
     </row>
     <row r="35" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>1487</v>
+        <v>1484</v>
       </c>
       <c r="B35" s="7">
         <v>4</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>1488</v>
+        <v>1485</v>
       </c>
       <c r="D35" s="7">
         <v>1</v>
@@ -10943,13 +10934,13 @@
     </row>
     <row r="36" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>1489</v>
+        <v>1486</v>
       </c>
       <c r="B36" s="7">
         <v>1.5</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>1490</v>
+        <v>1487</v>
       </c>
       <c r="D36" s="7">
         <v>0</v>
@@ -10958,13 +10949,13 @@
     </row>
     <row r="37" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
       <c r="B37" s="7">
         <v>5</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>1492</v>
+        <v>1489</v>
       </c>
       <c r="D37" s="7">
         <v>0</v>
@@ -10973,13 +10964,13 @@
     </row>
     <row r="38" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
       <c r="B38" s="7">
         <v>7</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>1494</v>
+        <v>1491</v>
       </c>
       <c r="D38" s="7">
         <v>0</v>
@@ -10988,13 +10979,13 @@
     </row>
     <row r="39" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="B39" s="7">
         <v>9</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="D39" s="7">
         <v>0</v>
@@ -11003,13 +10994,13 @@
     </row>
     <row r="40" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="B40" s="7">
         <v>8</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="D40" s="7">
         <v>0.1</v>
@@ -11018,13 +11009,13 @@
     </row>
     <row r="41" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
       <c r="B41" s="7">
         <v>4.5</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
       <c r="D41" s="7">
         <v>0.1</v>
@@ -11033,13 +11024,13 @@
     </row>
     <row r="42" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
       <c r="B42" s="7">
         <v>6</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="D42" s="7">
         <v>0.1</v>
@@ -11068,22 +11059,22 @@
         <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>1501</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>1502</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>1503</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>1504</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>1505</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>1506</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>1507</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -11091,22 +11082,22 @@
         <v>87</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>1506</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>1508</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>1509</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>1510</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>1511</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>1512</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -11201,10 +11192,10 @@
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C7" s="7" t="b">
         <v>0</v>
@@ -11243,10 +11234,10 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C9" s="7" t="b">
         <v>0</v>
@@ -11264,10 +11255,10 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C10" s="7" t="b">
         <v>0</v>
@@ -11381,7 +11372,7 @@
         <v>0.7</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="F15" s="7">
         <v>0.8</v>
@@ -11404,7 +11395,7 @@
         <v>0.7</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="F16" s="7">
         <v>0.8</v>
@@ -11429,10 +11420,10 @@
   <sheetData>
     <row r="1" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11440,7 +11431,7 @@
         <v>87</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11469,18 +11460,18 @@
     </row>
     <row r="6" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1516</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="7" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1517</v>
+        <v>1514</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11488,47 +11479,47 @@
         <v>911</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1519</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1520</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="10" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1521</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="11" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1522</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="12" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1523</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="13" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1524</v>
+        <v>1521</v>
       </c>
     </row>
   </sheetData>
@@ -11548,16 +11539,16 @@
   <sheetData>
     <row r="1" ht="54" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1527</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11565,13 +11556,13 @@
         <v>87</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>555</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11618,7 +11609,7 @@
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1528</v>
+        <v>1525</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>123</v>
@@ -11627,12 +11618,12 @@
         <v>1</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1529</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1530</v>
+        <v>1527</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>123</v>
@@ -11641,12 +11632,12 @@
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1531</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1532</v>
+        <v>1529</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>123</v>
@@ -11655,7 +11646,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11669,7 +11660,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11683,12 +11674,12 @@
         <v>2</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>195</v>
@@ -11697,12 +11688,12 @@
         <v>3</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>197</v>
@@ -11711,12 +11702,12 @@
         <v>1</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1539</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>1540</v>
+        <v>1537</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>197</v>
@@ -11725,12 +11716,12 @@
         <v>2</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>197</v>
@@ -11739,7 +11730,7 @@
         <v>3</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11753,7 +11744,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11767,7 +11758,7 @@
         <v>2</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11781,12 +11772,12 @@
         <v>3</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1542</v>
+        <v>1539</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>204</v>
@@ -11795,12 +11786,12 @@
         <v>1</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1543</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>204</v>
@@ -11809,12 +11800,12 @@
         <v>2</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>1545</v>
+        <v>1542</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>204</v>
@@ -11823,7 +11814,7 @@
         <v>3</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11837,7 +11828,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11851,7 +11842,7 @@
         <v>2</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11865,12 +11856,12 @@
         <v>3</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>1546</v>
+        <v>1543</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>211</v>
@@ -11879,12 +11870,12 @@
         <v>1</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1547</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>1548</v>
+        <v>1545</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>211</v>
@@ -11893,12 +11884,12 @@
         <v>2</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>1549</v>
+        <v>1546</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>211</v>
@@ -11907,7 +11898,7 @@
         <v>3</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11921,7 +11912,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="28" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11935,7 +11926,7 @@
         <v>2</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="29" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11949,12 +11940,12 @@
         <v>3</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="30" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>217</v>
@@ -11963,12 +11954,12 @@
         <v>1</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1551</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="31" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>217</v>
@@ -11977,12 +11968,12 @@
         <v>2</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="32" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>1553</v>
+        <v>1550</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>217</v>
@@ -11991,7 +11982,7 @@
         <v>3</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="33" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12005,7 +11996,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="34" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12019,7 +12010,7 @@
         <v>2</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="35" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12033,12 +12024,12 @@
         <v>3</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="36" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>1554</v>
+        <v>1551</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>223</v>
@@ -12047,12 +12038,12 @@
         <v>1</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1555</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="37" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>223</v>
@@ -12061,12 +12052,12 @@
         <v>2</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="38" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>1557</v>
+        <v>1554</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>223</v>
@@ -12075,12 +12066,12 @@
         <v>3</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="39" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>1558</v>
+        <v>1555</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>232</v>
@@ -12089,12 +12080,12 @@
         <v>1</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="40" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>232</v>
@@ -12103,12 +12094,12 @@
         <v>2</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>1560</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="41" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>1561</v>
+        <v>1558</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>232</v>
@@ -12117,12 +12108,12 @@
         <v>3</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>236</v>
@@ -12131,12 +12122,12 @@
         <v>1</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="43" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>236</v>
@@ -12145,12 +12136,12 @@
         <v>2</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="44" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>236</v>
@@ -12159,12 +12150,12 @@
         <v>3</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="45" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>240</v>
@@ -12173,12 +12164,12 @@
         <v>1</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="46" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>240</v>
@@ -12187,12 +12178,12 @@
         <v>2</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="47" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>240</v>
@@ -12201,138 +12192,138 @@
         <v>3</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="48" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
       <c r="C48" s="7">
         <v>1</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="49" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
       <c r="C49" s="7">
         <v>2</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="50" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>1571</v>
+        <v>1568</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>1536</v>
+        <v>1533</v>
       </c>
       <c r="C50" s="7">
         <v>3</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="51" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="C51" s="7">
         <v>1</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="52" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="C52" s="7">
         <v>2</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="53" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>1575</v>
+        <v>1572</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="C53" s="7">
         <v>3</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="54" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>1577</v>
+        <v>1574</v>
       </c>
       <c r="C54" s="7">
         <v>1</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="55" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>1577</v>
+        <v>1574</v>
       </c>
       <c r="C55" s="7">
         <v>2</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="56" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>1577</v>
+        <v>1574</v>
       </c>
       <c r="C56" s="7">
         <v>3</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="57" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>244</v>
@@ -12341,12 +12332,12 @@
         <v>1</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="58" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>244</v>
@@ -12355,12 +12346,12 @@
         <v>2</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="59" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>244</v>
@@ -12369,12 +12360,12 @@
         <v>3</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="60" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>248</v>
@@ -12383,12 +12374,12 @@
         <v>1</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="61" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>248</v>
@@ -12397,12 +12388,12 @@
         <v>2</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="62" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>248</v>
@@ -12411,12 +12402,12 @@
         <v>3</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="63" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>252</v>
@@ -12425,12 +12416,12 @@
         <v>1</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="64" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>252</v>
@@ -12439,12 +12430,12 @@
         <v>2</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="65" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>252</v>
@@ -12453,96 +12444,96 @@
         <v>3</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="66" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
       <c r="C66" s="7">
         <v>1</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="67" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>1591</v>
+        <v>1588</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
       <c r="C67" s="7">
         <v>2</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="68" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>1592</v>
+        <v>1589</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>1590</v>
+        <v>1587</v>
       </c>
       <c r="C68" s="7">
         <v>3</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="69" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>1593</v>
+        <v>1590</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="70" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="C70" s="7">
         <v>2</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="71" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>1594</v>
+        <v>1591</v>
       </c>
       <c r="C71" s="7">
         <v>3</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="72" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>256</v>
@@ -12551,12 +12542,12 @@
         <v>1</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="73" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>256</v>
@@ -12565,12 +12556,12 @@
         <v>2</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="74" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>1599</v>
+        <v>1596</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>256</v>
@@ -12579,12 +12570,12 @@
         <v>3</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="75" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>260</v>
@@ -12593,12 +12584,12 @@
         <v>1</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="76" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>1601</v>
+        <v>1598</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>260</v>
@@ -12607,12 +12598,12 @@
         <v>2</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="77" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>1602</v>
+        <v>1599</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>260</v>
@@ -12621,12 +12612,12 @@
         <v>3</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="78" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>1603</v>
+        <v>1600</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>262</v>
@@ -12635,12 +12626,12 @@
         <v>1</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="79" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>1604</v>
+        <v>1601</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>262</v>
@@ -12649,12 +12640,12 @@
         <v>2</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="80" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>262</v>
@@ -12663,12 +12654,12 @@
         <v>3</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="81" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>1606</v>
+        <v>1603</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>264</v>
@@ -12677,12 +12668,12 @@
         <v>1</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="82" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>1607</v>
+        <v>1604</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>264</v>
@@ -12691,12 +12682,12 @@
         <v>2</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="83" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>1608</v>
+        <v>1605</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>264</v>
@@ -12705,54 +12696,54 @@
         <v>3</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="84" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>1609</v>
+        <v>1606</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="C84" s="7">
         <v>1</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="85" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="C85" s="7">
         <v>2</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="86" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>1612</v>
+        <v>1609</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
       <c r="C86" s="7">
         <v>3</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="87" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>1613</v>
+        <v>1610</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>268</v>
@@ -12761,12 +12752,12 @@
         <v>1</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="88" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>1614</v>
+        <v>1611</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>268</v>
@@ -12775,12 +12766,12 @@
         <v>2</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="89" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>1615</v>
+        <v>1612</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>268</v>
@@ -12789,12 +12780,12 @@
         <v>3</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="90" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>1616</v>
+        <v>1613</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>272</v>
@@ -12803,12 +12794,12 @@
         <v>1</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="91" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>272</v>
@@ -12817,12 +12808,12 @@
         <v>2</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="92" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>272</v>
@@ -12831,12 +12822,12 @@
         <v>3</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="93" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>1619</v>
+        <v>1616</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>274</v>
@@ -12845,12 +12836,12 @@
         <v>1</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="94" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>1620</v>
+        <v>1617</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>274</v>
@@ -12859,12 +12850,12 @@
         <v>2</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="95" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>1621</v>
+        <v>1618</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>274</v>
@@ -12873,12 +12864,12 @@
         <v>3</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="96" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>1622</v>
+        <v>1619</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>276</v>
@@ -12887,12 +12878,12 @@
         <v>1</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="97" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>1623</v>
+        <v>1620</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>276</v>
@@ -12901,12 +12892,12 @@
         <v>2</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="98" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>1624</v>
+        <v>1621</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>276</v>
@@ -12915,54 +12906,54 @@
         <v>3</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="99" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>1625</v>
+        <v>1622</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="C99" s="7">
         <v>1</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="100" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="C100" s="7">
         <v>2</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="101" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>1628</v>
+        <v>1625</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="C101" s="7">
         <v>3</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="102" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
-        <v>1629</v>
+        <v>1626</v>
       </c>
       <c r="B102" s="7" t="s">
         <v>280</v>
@@ -12971,12 +12962,12 @@
         <v>1</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="103" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>1630</v>
+        <v>1627</v>
       </c>
       <c r="B103" s="7" t="s">
         <v>280</v>
@@ -12985,12 +12976,12 @@
         <v>2</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="104" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>1631</v>
+        <v>1628</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>280</v>
@@ -12999,12 +12990,12 @@
         <v>3</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="105" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>284</v>
@@ -13013,12 +13004,12 @@
         <v>1</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="106" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>1633</v>
+        <v>1630</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>284</v>
@@ -13027,12 +13018,12 @@
         <v>2</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="107" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>1634</v>
+        <v>1631</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>284</v>
@@ -13041,12 +13032,12 @@
         <v>3</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="108" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>1635</v>
+        <v>1632</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>286</v>
@@ -13055,12 +13046,12 @@
         <v>1</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="109" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>1636</v>
+        <v>1633</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>286</v>
@@ -13069,12 +13060,12 @@
         <v>2</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="110" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>1637</v>
+        <v>1634</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>286</v>
@@ -13083,12 +13074,12 @@
         <v>3</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="111" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>1638</v>
+        <v>1635</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>288</v>
@@ -13097,12 +13088,12 @@
         <v>1</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="112" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
-        <v>1639</v>
+        <v>1636</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>288</v>
@@ -13111,12 +13102,12 @@
         <v>2</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="113" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>1640</v>
+        <v>1637</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>288</v>
@@ -13125,12 +13116,12 @@
         <v>3</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="114" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>1641</v>
+        <v>1638</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>290</v>
@@ -13139,12 +13130,12 @@
         <v>1</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>1534</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="115" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>1642</v>
+        <v>1639</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>290</v>
@@ -13153,12 +13144,12 @@
         <v>2</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="116" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>290</v>
@@ -13167,7 +13158,7 @@
         <v>3</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>1537</v>
+        <v>1534</v>
       </c>
     </row>
   </sheetData>
@@ -14344,38 +14335,20 @@
       <c r="J10" s="7"/>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>6</v>
-      </c>
-      <c r="B11" s="7">
-        <v>2</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>907</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>916</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="F11" s="7">
-        <v>70</v>
-      </c>
-      <c r="G11" s="7">
-        <v>0</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>909</v>
-      </c>
-      <c r="I11" s="7" t="b">
-        <v>0</v>
-      </c>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12" s="7">
         <v>2</v>
@@ -14384,7 +14357,7 @@
         <v>911</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>146</v>
@@ -14405,7 +14378,7 @@
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" s="7">
         <v>3</v>
@@ -14414,7 +14387,7 @@
         <v>907</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>253</v>
@@ -14435,7 +14408,7 @@
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" s="7">
         <v>3</v>
@@ -14444,7 +14417,7 @@
         <v>907</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>257</v>
@@ -14465,7 +14438,7 @@
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" s="7">
         <v>3</v>
@@ -14474,7 +14447,7 @@
         <v>907</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>261</v>
@@ -14494,38 +14467,20 @@
       <c r="J15" s="7"/>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>11</v>
-      </c>
-      <c r="B16" s="7">
-        <v>3</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>907</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>921</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="F16" s="7">
-        <v>80</v>
-      </c>
-      <c r="G16" s="7">
-        <v>0</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>909</v>
-      </c>
-      <c r="I16" s="7" t="b">
-        <v>0</v>
-      </c>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
       <c r="J16" s="7"/>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B17" s="7">
         <v>3</v>
@@ -14534,7 +14489,7 @@
         <v>911</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>151</v>
@@ -14555,7 +14510,7 @@
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B18" s="7">
         <v>4</v>
@@ -14564,7 +14519,7 @@
         <v>907</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>265</v>
@@ -14585,7 +14540,7 @@
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B19" s="7">
         <v>4</v>
@@ -14594,7 +14549,7 @@
         <v>907</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>269</v>
@@ -14615,7 +14570,7 @@
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B20" s="7">
         <v>4</v>
@@ -14624,7 +14579,7 @@
         <v>907</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>273</v>
@@ -14644,38 +14599,20 @@
       <c r="J20" s="7"/>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
-        <v>16</v>
-      </c>
-      <c r="B21" s="7">
-        <v>4</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>907</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>926</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="F21" s="7">
-        <v>80</v>
-      </c>
-      <c r="G21" s="7">
-        <v>0</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>909</v>
-      </c>
-      <c r="I21" s="7" t="b">
-        <v>0</v>
-      </c>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
       <c r="J21" s="7"/>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B22" s="7">
         <v>4</v>
@@ -14684,7 +14621,7 @@
         <v>911</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>156</v>
@@ -14705,7 +14642,7 @@
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B23" s="7">
         <v>5</v>
@@ -14714,7 +14651,7 @@
         <v>907</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>277</v>
@@ -14735,7 +14672,7 @@
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B24" s="7">
         <v>5</v>
@@ -14744,7 +14681,7 @@
         <v>907</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>281</v>
@@ -14765,7 +14702,7 @@
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B25" s="7">
         <v>5</v>
@@ -14774,7 +14711,7 @@
         <v>907</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>285</v>
@@ -14795,7 +14732,7 @@
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B26" s="7">
         <v>5</v>
@@ -14804,7 +14741,7 @@
         <v>907</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>287</v>
@@ -14825,7 +14762,7 @@
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B27" s="7">
         <v>5</v>
@@ -14834,7 +14771,7 @@
         <v>907</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>289</v>
@@ -14855,7 +14792,7 @@
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B28" s="7">
         <v>5</v>
@@ -14864,7 +14801,7 @@
         <v>911</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>161</v>
@@ -14885,7 +14822,7 @@
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B29" s="7">
         <v>5</v>
@@ -14894,7 +14831,7 @@
         <v>911</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>224</v>
@@ -14906,7 +14843,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="I29" s="7"/>
       <c r="J29" s="7" t="s">

--- a/excel/斗鸡配置.xlsx
+++ b/excel/斗鸡配置.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3250" uniqueCount="1641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3244" uniqueCount="1635">
   <si>
     <t>斗鸡配置</t>
   </si>
@@ -4501,24 +4501,6 @@
   </si>
   <si>
     <t>首条弹幕延迟（秒）</t>
-  </si>
-  <si>
-    <t>danmaku_warmupLimit</t>
-  </si>
-  <si>
-    <t>热身赛弹幕总条数</t>
-  </si>
-  <si>
-    <t>danmaku_officialLimit</t>
-  </si>
-  <si>
-    <t>正式赛弹幕总条数</t>
-  </si>
-  <si>
-    <t>danmaku_bossLimit</t>
-  </si>
-  <si>
-    <t>Boss弹幕总条数</t>
   </si>
   <si>
     <t>danmaku_travelSeconds</t>
@@ -10366,7 +10348,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -10952,13 +10934,13 @@
         <v>1488</v>
       </c>
       <c r="B37" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>1489</v>
       </c>
       <c r="D37" s="7">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E37" s="7"/>
     </row>
@@ -10967,13 +10949,13 @@
         <v>1490</v>
       </c>
       <c r="B38" s="7">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>1491</v>
       </c>
       <c r="D38" s="7">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E38" s="7"/>
     </row>
@@ -10982,60 +10964,15 @@
         <v>1492</v>
       </c>
       <c r="B39" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>1493</v>
       </c>
       <c r="D39" s="7">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E39" s="7"/>
-    </row>
-    <row r="40" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
-        <v>1494</v>
-      </c>
-      <c r="B40" s="7">
-        <v>8</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>1495</v>
-      </c>
-      <c r="D40" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="E40" s="7"/>
-    </row>
-    <row r="41" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>1496</v>
-      </c>
-      <c r="B41" s="7">
-        <v>4.5</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>1497</v>
-      </c>
-      <c r="D41" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="E41" s="7"/>
-    </row>
-    <row r="42" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
-        <v>1498</v>
-      </c>
-      <c r="B42" s="7">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>1499</v>
-      </c>
-      <c r="D42" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="E42" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11062,19 +10999,19 @@
         <v>933</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1500</v>
+        <v>1494</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1501</v>
+        <v>1495</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1502</v>
+        <v>1496</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>1503</v>
+        <v>1497</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>1504</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -11085,19 +11022,19 @@
         <v>935</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>1505</v>
+        <v>1499</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1506</v>
+        <v>1500</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>1507</v>
+        <v>1501</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>1508</v>
+        <v>1502</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>1509</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -11420,10 +11357,10 @@
   <sheetData>
     <row r="1" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1510</v>
+        <v>1504</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1511</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11460,18 +11397,18 @@
     </row>
     <row r="6" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1512</v>
+        <v>1506</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1513</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="7" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1514</v>
+        <v>1508</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1515</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11479,7 +11416,7 @@
         <v>911</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1516</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11487,7 +11424,7 @@
         <v>1313</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1517</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="10" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11495,7 +11432,7 @@
         <v>1315</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1518</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="11" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11503,7 +11440,7 @@
         <v>1317</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1519</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="12" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11511,7 +11448,7 @@
         <v>1319</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1520</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="13" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11519,7 +11456,7 @@
         <v>1321</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1521</v>
+        <v>1515</v>
       </c>
     </row>
   </sheetData>
@@ -11539,16 +11476,16 @@
   <sheetData>
     <row r="1" ht="54" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1522</v>
+        <v>1516</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1523</v>
+        <v>1517</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1524</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11609,7 +11546,7 @@
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1525</v>
+        <v>1519</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>123</v>
@@ -11618,12 +11555,12 @@
         <v>1</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1526</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1527</v>
+        <v>1521</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>123</v>
@@ -11632,12 +11569,12 @@
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1528</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1529</v>
+        <v>1523</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>123</v>
@@ -11646,7 +11583,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1530</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11660,7 +11597,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11674,12 +11611,12 @@
         <v>2</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>1533</v>
+        <v>1527</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>195</v>
@@ -11688,12 +11625,12 @@
         <v>3</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1535</v>
+        <v>1529</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>197</v>
@@ -11702,12 +11639,12 @@
         <v>1</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1536</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>1537</v>
+        <v>1531</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>197</v>
@@ -11721,7 +11658,7 @@
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1538</v>
+        <v>1532</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>197</v>
@@ -11744,7 +11681,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11758,7 +11695,7 @@
         <v>2</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11772,12 +11709,12 @@
         <v>3</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1539</v>
+        <v>1533</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>204</v>
@@ -11786,12 +11723,12 @@
         <v>1</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1540</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>1541</v>
+        <v>1535</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>204</v>
@@ -11805,7 +11742,7 @@
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>1542</v>
+        <v>1536</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>204</v>
@@ -11828,7 +11765,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11842,7 +11779,7 @@
         <v>2</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11856,12 +11793,12 @@
         <v>3</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>1543</v>
+        <v>1537</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>211</v>
@@ -11870,12 +11807,12 @@
         <v>1</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1544</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>1545</v>
+        <v>1539</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>211</v>
@@ -11889,7 +11826,7 @@
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>1546</v>
+        <v>1540</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>211</v>
@@ -11912,7 +11849,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="28" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11926,7 +11863,7 @@
         <v>2</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="29" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11940,12 +11877,12 @@
         <v>3</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="30" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>1547</v>
+        <v>1541</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>217</v>
@@ -11954,12 +11891,12 @@
         <v>1</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1548</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="31" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>1549</v>
+        <v>1543</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>217</v>
@@ -11973,7 +11910,7 @@
     </row>
     <row r="32" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>1550</v>
+        <v>1544</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>217</v>
@@ -11996,7 +11933,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="34" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12010,7 +11947,7 @@
         <v>2</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="35" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -12024,12 +11961,12 @@
         <v>3</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="36" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>1551</v>
+        <v>1545</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>223</v>
@@ -12038,12 +11975,12 @@
         <v>1</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1552</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="37" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>1553</v>
+        <v>1547</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>223</v>
@@ -12057,7 +11994,7 @@
     </row>
     <row r="38" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>1554</v>
+        <v>1548</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>223</v>
@@ -12071,7 +12008,7 @@
     </row>
     <row r="39" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>232</v>
@@ -12085,7 +12022,7 @@
     </row>
     <row r="40" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>1556</v>
+        <v>1550</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>232</v>
@@ -12094,12 +12031,12 @@
         <v>2</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>1557</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="41" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>1558</v>
+        <v>1552</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>232</v>
@@ -12108,12 +12045,12 @@
         <v>3</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>1559</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>1560</v>
+        <v>1554</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>236</v>
@@ -12122,12 +12059,12 @@
         <v>1</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="43" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>1561</v>
+        <v>1555</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>236</v>
@@ -12136,12 +12073,12 @@
         <v>2</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="44" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>1562</v>
+        <v>1556</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>236</v>
@@ -12150,12 +12087,12 @@
         <v>3</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="45" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>1563</v>
+        <v>1557</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>240</v>
@@ -12164,12 +12101,12 @@
         <v>1</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="46" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>1564</v>
+        <v>1558</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>240</v>
@@ -12178,12 +12115,12 @@
         <v>2</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="47" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>1565</v>
+        <v>1559</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>240</v>
@@ -12192,138 +12129,138 @@
         <v>3</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="48" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>1566</v>
+        <v>1560</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>1533</v>
+        <v>1527</v>
       </c>
       <c r="C48" s="7">
         <v>1</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="49" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>1567</v>
+        <v>1561</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>1533</v>
+        <v>1527</v>
       </c>
       <c r="C49" s="7">
         <v>2</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="50" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>1568</v>
+        <v>1562</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>1533</v>
+        <v>1527</v>
       </c>
       <c r="C50" s="7">
         <v>3</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="51" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>1569</v>
+        <v>1563</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>1570</v>
+        <v>1564</v>
       </c>
       <c r="C51" s="7">
         <v>1</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="52" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>1571</v>
+        <v>1565</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>1570</v>
+        <v>1564</v>
       </c>
       <c r="C52" s="7">
         <v>2</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="53" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>1572</v>
+        <v>1566</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>1570</v>
+        <v>1564</v>
       </c>
       <c r="C53" s="7">
         <v>3</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="54" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>1573</v>
+        <v>1567</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>1574</v>
+        <v>1568</v>
       </c>
       <c r="C54" s="7">
         <v>1</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="55" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>1575</v>
+        <v>1569</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>1574</v>
+        <v>1568</v>
       </c>
       <c r="C55" s="7">
         <v>2</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="56" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>1576</v>
+        <v>1570</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>1574</v>
+        <v>1568</v>
       </c>
       <c r="C56" s="7">
         <v>3</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="57" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>1577</v>
+        <v>1571</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>244</v>
@@ -12332,12 +12269,12 @@
         <v>1</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="58" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>1578</v>
+        <v>1572</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>244</v>
@@ -12346,12 +12283,12 @@
         <v>2</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="59" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>1579</v>
+        <v>1573</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>244</v>
@@ -12360,12 +12297,12 @@
         <v>3</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="60" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>1580</v>
+        <v>1574</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>248</v>
@@ -12374,12 +12311,12 @@
         <v>1</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="61" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>1581</v>
+        <v>1575</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>248</v>
@@ -12388,12 +12325,12 @@
         <v>2</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="62" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>1582</v>
+        <v>1576</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>248</v>
@@ -12402,12 +12339,12 @@
         <v>3</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="63" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>252</v>
@@ -12416,12 +12353,12 @@
         <v>1</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="64" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>252</v>
@@ -12430,12 +12367,12 @@
         <v>2</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="65" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>1585</v>
+        <v>1579</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>252</v>
@@ -12444,96 +12381,96 @@
         <v>3</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="66" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>1586</v>
+        <v>1580</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>1587</v>
+        <v>1581</v>
       </c>
       <c r="C66" s="7">
         <v>1</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="67" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>1588</v>
+        <v>1582</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>1587</v>
+        <v>1581</v>
       </c>
       <c r="C67" s="7">
         <v>2</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="68" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>1589</v>
+        <v>1583</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>1587</v>
+        <v>1581</v>
       </c>
       <c r="C68" s="7">
         <v>3</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="69" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>1590</v>
+        <v>1584</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>1591</v>
+        <v>1585</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="70" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>1592</v>
+        <v>1586</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>1591</v>
+        <v>1585</v>
       </c>
       <c r="C70" s="7">
         <v>2</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="71" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>1593</v>
+        <v>1587</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>1591</v>
+        <v>1585</v>
       </c>
       <c r="C71" s="7">
         <v>3</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="72" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>1594</v>
+        <v>1588</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>256</v>
@@ -12542,12 +12479,12 @@
         <v>1</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="73" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>1595</v>
+        <v>1589</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>256</v>
@@ -12556,12 +12493,12 @@
         <v>2</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="74" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>1596</v>
+        <v>1590</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>256</v>
@@ -12570,12 +12507,12 @@
         <v>3</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="75" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>1597</v>
+        <v>1591</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>260</v>
@@ -12584,12 +12521,12 @@
         <v>1</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="76" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>1598</v>
+        <v>1592</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>260</v>
@@ -12598,12 +12535,12 @@
         <v>2</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="77" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>1599</v>
+        <v>1593</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>260</v>
@@ -12612,12 +12549,12 @@
         <v>3</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="78" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>1600</v>
+        <v>1594</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>262</v>
@@ -12626,12 +12563,12 @@
         <v>1</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="79" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>1601</v>
+        <v>1595</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>262</v>
@@ -12640,12 +12577,12 @@
         <v>2</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="80" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>1602</v>
+        <v>1596</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>262</v>
@@ -12654,12 +12591,12 @@
         <v>3</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="81" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>1603</v>
+        <v>1597</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>264</v>
@@ -12668,12 +12605,12 @@
         <v>1</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="82" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>1604</v>
+        <v>1598</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>264</v>
@@ -12682,12 +12619,12 @@
         <v>2</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="83" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>1605</v>
+        <v>1599</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>264</v>
@@ -12696,54 +12633,54 @@
         <v>3</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="84" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>1606</v>
+        <v>1600</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>1607</v>
+        <v>1601</v>
       </c>
       <c r="C84" s="7">
         <v>1</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="85" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>1608</v>
+        <v>1602</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>1607</v>
+        <v>1601</v>
       </c>
       <c r="C85" s="7">
         <v>2</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="86" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>1609</v>
+        <v>1603</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>1607</v>
+        <v>1601</v>
       </c>
       <c r="C86" s="7">
         <v>3</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="87" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>1610</v>
+        <v>1604</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>268</v>
@@ -12752,12 +12689,12 @@
         <v>1</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="88" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>1611</v>
+        <v>1605</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>268</v>
@@ -12766,12 +12703,12 @@
         <v>2</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="89" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>1612</v>
+        <v>1606</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>268</v>
@@ -12780,12 +12717,12 @@
         <v>3</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="90" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>1613</v>
+        <v>1607</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>272</v>
@@ -12794,12 +12731,12 @@
         <v>1</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="91" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>1614</v>
+        <v>1608</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>272</v>
@@ -12808,12 +12745,12 @@
         <v>2</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="92" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
-        <v>1615</v>
+        <v>1609</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>272</v>
@@ -12822,12 +12759,12 @@
         <v>3</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="93" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>1616</v>
+        <v>1610</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>274</v>
@@ -12836,12 +12773,12 @@
         <v>1</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="94" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>1617</v>
+        <v>1611</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>274</v>
@@ -12850,12 +12787,12 @@
         <v>2</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="95" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>1618</v>
+        <v>1612</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>274</v>
@@ -12864,12 +12801,12 @@
         <v>3</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="96" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>1619</v>
+        <v>1613</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>276</v>
@@ -12878,12 +12815,12 @@
         <v>1</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="97" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>1620</v>
+        <v>1614</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>276</v>
@@ -12892,12 +12829,12 @@
         <v>2</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="98" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>1621</v>
+        <v>1615</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>276</v>
@@ -12906,54 +12843,54 @@
         <v>3</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="99" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>1622</v>
+        <v>1616</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>1623</v>
+        <v>1617</v>
       </c>
       <c r="C99" s="7">
         <v>1</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="100" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>1624</v>
+        <v>1618</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>1623</v>
+        <v>1617</v>
       </c>
       <c r="C100" s="7">
         <v>2</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="101" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>1625</v>
+        <v>1619</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>1623</v>
+        <v>1617</v>
       </c>
       <c r="C101" s="7">
         <v>3</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="102" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
-        <v>1626</v>
+        <v>1620</v>
       </c>
       <c r="B102" s="7" t="s">
         <v>280</v>
@@ -12962,12 +12899,12 @@
         <v>1</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="103" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>1627</v>
+        <v>1621</v>
       </c>
       <c r="B103" s="7" t="s">
         <v>280</v>
@@ -12976,12 +12913,12 @@
         <v>2</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="104" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>1628</v>
+        <v>1622</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>280</v>
@@ -12990,12 +12927,12 @@
         <v>3</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="105" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>1629</v>
+        <v>1623</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>284</v>
@@ -13004,12 +12941,12 @@
         <v>1</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="106" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>1630</v>
+        <v>1624</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>284</v>
@@ -13018,12 +12955,12 @@
         <v>2</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="107" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>1631</v>
+        <v>1625</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>284</v>
@@ -13032,12 +12969,12 @@
         <v>3</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="108" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>1632</v>
+        <v>1626</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>286</v>
@@ -13046,12 +12983,12 @@
         <v>1</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="109" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>1633</v>
+        <v>1627</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>286</v>
@@ -13060,12 +12997,12 @@
         <v>2</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="110" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>1634</v>
+        <v>1628</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>286</v>
@@ -13074,12 +13011,12 @@
         <v>3</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="111" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>1635</v>
+        <v>1629</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>288</v>
@@ -13088,12 +13025,12 @@
         <v>1</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="112" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
-        <v>1636</v>
+        <v>1630</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>288</v>
@@ -13102,12 +13039,12 @@
         <v>2</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="113" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>1637</v>
+        <v>1631</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>288</v>
@@ -13116,12 +13053,12 @@
         <v>3</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="114" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>1638</v>
+        <v>1632</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>290</v>
@@ -13130,12 +13067,12 @@
         <v>1</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>1531</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="115" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>1639</v>
+        <v>1633</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>290</v>
@@ -13144,12 +13081,12 @@
         <v>2</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>1532</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="116" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
-        <v>1640</v>
+        <v>1634</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>290</v>
@@ -13158,7 +13095,7 @@
         <v>3</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>1534</v>
+        <v>1528</v>
       </c>
     </row>
   </sheetData>

--- a/excel/斗鸡配置.xlsx
+++ b/excel/斗鸡配置.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3244" uniqueCount="1635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3240" uniqueCount="1634">
   <si>
     <t>斗鸡配置</t>
   </si>
@@ -2763,13 +2763,10 @@
     <t>battle</t>
   </si>
   <si>
-    <t>鸡鸣村 · 热身赛1</t>
+    <t>鸡鸣村 · 热身赛</t>
   </si>
   <si>
     <t>warmup</t>
-  </si>
-  <si>
-    <t>鸡鸣村 · 热身赛2</t>
   </si>
   <si>
     <t>boss</t>
@@ -7566,10 +7563,10 @@
         <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>933</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -7577,10 +7574,10 @@
         <v>87</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>935</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -7618,2037 +7615,2037 @@
     </row>
     <row r="6" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="7" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="8" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="9" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="10" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="11" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="12" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="13" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="14" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="15" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="16" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="17" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="18" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="19" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="20" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="21" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="22" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="23" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="24" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="25" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="26" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="27" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="28" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="29" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="30" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="31" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="32" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="33" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="34" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="35" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="36" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="37" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="38" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="39" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="40" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="41" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="42" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="43" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="44" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="45" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="46" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="47" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="48" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="49" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="50" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="51" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="52" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="53" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="54" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="55" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>194</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="56" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B56" s="7" t="s">
         <v>1037</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="C56" s="7" t="s">
         <v>1038</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="57" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C57" s="7" t="s">
         <v>1040</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="58" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C58" s="7" t="s">
         <v>1042</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="59" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C59" s="7" t="s">
         <v>1044</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="60" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C60" s="7" t="s">
         <v>1046</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="61" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C61" s="7" t="s">
         <v>1048</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="62" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C62" s="7" t="s">
         <v>1050</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="63" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C63" s="7" t="s">
         <v>1052</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="64" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C64" s="7" t="s">
         <v>1054</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="65" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C65" s="7" t="s">
         <v>1056</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="66" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C66" s="7" t="s">
         <v>1058</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>1059</v>
       </c>
     </row>
     <row r="67" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C67" s="7" t="s">
         <v>1060</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="68" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C68" s="7" t="s">
         <v>1062</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="69" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C69" s="7" t="s">
         <v>1064</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="70" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C70" s="7" t="s">
         <v>1066</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="71" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="72" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="73" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="74" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="75" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="76" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="77" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="78" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="79" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="80" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="81" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="82" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="83" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="84" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="85" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>202</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="86" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B86" s="7" t="s">
         <v>1098</v>
       </c>
-      <c r="B86" s="7" t="s">
+      <c r="C86" s="7" t="s">
         <v>1099</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="87" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C87" s="7" t="s">
         <v>1101</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="88" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C88" s="7" t="s">
         <v>1103</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="89" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C89" s="7" t="s">
         <v>1105</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="90" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C90" s="7" t="s">
         <v>1107</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="91" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C91" s="7" t="s">
         <v>1109</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="92" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C92" s="7" t="s">
         <v>1111</v>
-      </c>
-      <c r="B92" s="7" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="93" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C93" s="7" t="s">
         <v>1113</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="94" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C94" s="7" t="s">
         <v>1115</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="95" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C95" s="7" t="s">
         <v>1117</v>
-      </c>
-      <c r="B95" s="7" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="96" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C96" s="7" t="s">
         <v>1119</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="97" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C97" s="7" t="s">
         <v>1121</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="98" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C98" s="7" t="s">
         <v>1123</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="99" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C99" s="7" t="s">
         <v>1125</v>
-      </c>
-      <c r="B99" s="7" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="100" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C100" s="7" t="s">
         <v>1127</v>
-      </c>
-      <c r="B100" s="7" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="101" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B101" s="7" t="s">
         <v>1129</v>
       </c>
-      <c r="B101" s="7" t="s">
+      <c r="C101" s="7" t="s">
         <v>1130</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="102" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C102" s="7" t="s">
         <v>1132</v>
-      </c>
-      <c r="B102" s="7" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="103" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C103" s="7" t="s">
         <v>1134</v>
-      </c>
-      <c r="B103" s="7" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="104" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C104" s="7" t="s">
         <v>1136</v>
-      </c>
-      <c r="B104" s="7" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="105" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C105" s="7" t="s">
         <v>1138</v>
-      </c>
-      <c r="B105" s="7" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="106" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C106" s="7" t="s">
         <v>1140</v>
-      </c>
-      <c r="B106" s="7" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="107" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C107" s="7" t="s">
         <v>1142</v>
-      </c>
-      <c r="B107" s="7" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="108" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C108" s="7" t="s">
         <v>1144</v>
-      </c>
-      <c r="B108" s="7" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="109" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C109" s="7" t="s">
         <v>1146</v>
-      </c>
-      <c r="B109" s="7" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="110" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C110" s="7" t="s">
         <v>1148</v>
-      </c>
-      <c r="B110" s="7" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="111" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C111" s="7" t="s">
         <v>1150</v>
-      </c>
-      <c r="B111" s="7" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="112" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C112" s="7" t="s">
         <v>1152</v>
-      </c>
-      <c r="B112" s="7" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="113" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C113" s="7" t="s">
         <v>1154</v>
-      </c>
-      <c r="B113" s="7" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C113" s="7" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="114" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C114" s="7" t="s">
         <v>1156</v>
-      </c>
-      <c r="B114" s="7" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C114" s="7" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="115" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C115" s="7" t="s">
         <v>1158</v>
-      </c>
-      <c r="B115" s="7" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="116" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="117" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="118" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="119" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="120" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="121" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="122" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="123" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="124" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="125" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="126" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="127" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="128" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="129" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>215</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="130" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="131" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="132" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="133" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="134" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="135" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="136" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="137" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="138" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="139" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="140" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="141" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="142" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="143" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="144" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="7" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>209</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="145" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="146" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="147" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="148" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="149" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="150" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="151" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="B151" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="152" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="B152" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="153" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B153" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="154" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B154" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="155" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="B155" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="156" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="157" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B157" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="158" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B158" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="159" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="B159" s="7" t="s">
         <v>196</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="160" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="161" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="B161" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="162" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="B162" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="163" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B163" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="164" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="B164" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="165" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B165" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="166" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="B166" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="167" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="168" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="7" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B168" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="169" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="B169" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="170" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="7" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B170" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C170" s="7" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="171" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B171" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C171" s="7" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="172" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B172" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C172" s="7" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="173" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="B173" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="174" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B174" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C174" s="7" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="175" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="B175" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="176" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="B176" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="177" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="B177" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="178" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="179" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B179" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="180" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B180" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C180" s="7" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="181" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="B181" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C181" s="7" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="182" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="7" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B182" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C182" s="7" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="183" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B183" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C183" s="7" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="184" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="7" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="B184" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C184" s="7" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="185" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="B185" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C185" s="7" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="186" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="7" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="B186" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C186" s="7" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="187" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B187" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="188" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="B188" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C188" s="7" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="189" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C189" s="7" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="190" ht="62.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="7" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="B190" s="7" t="s">
         <v>231</v>
       </c>
       <c r="C190" s="7" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
   </sheetData>
@@ -9670,10 +9667,10 @@
         <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>1310</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>1311</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9725,10 +9722,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>1312</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9736,10 +9733,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>1314</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>1315</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9747,10 +9744,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>1316</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>1317</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9758,10 +9755,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>1318</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -9769,10 +9766,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>1320</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>1321</v>
       </c>
     </row>
   </sheetData>
@@ -9794,7 +9791,7 @@
         <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -9802,7 +9799,7 @@
         <v>87</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -9831,79 +9828,79 @@
     </row>
     <row r="6" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>1322</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>1323</v>
       </c>
     </row>
     <row r="7" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="8" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>1325</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="9" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="10" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>1328</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>1329</v>
       </c>
     </row>
     <row r="11" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>1330</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="12" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>1332</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="13" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>1334</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>1335</v>
       </c>
     </row>
     <row r="14" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>1336</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>1337</v>
       </c>
     </row>
     <row r="15" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>699</v>
@@ -9911,15 +9908,15 @@
     </row>
     <row r="16" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>1339</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="17" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>703</v>
@@ -9927,175 +9924,175 @@
     </row>
     <row r="18" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="19" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>1343</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>1344</v>
       </c>
     </row>
     <row r="20" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>1345</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>1346</v>
       </c>
     </row>
     <row r="21" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>1347</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>1348</v>
       </c>
     </row>
     <row r="22" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B22" s="7" t="s">
         <v>1349</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="23" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>1351</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>1352</v>
       </c>
     </row>
     <row r="24" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="25" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>1354</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>1355</v>
       </c>
     </row>
     <row r="26" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>1356</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>1357</v>
       </c>
     </row>
     <row r="27" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>1358</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>1359</v>
       </c>
     </row>
     <row r="28" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>1360</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>1361</v>
       </c>
     </row>
     <row r="29" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>1362</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>1363</v>
       </c>
     </row>
     <row r="30" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>1364</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>1365</v>
       </c>
     </row>
     <row r="31" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="32" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>1367</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>1368</v>
       </c>
     </row>
     <row r="33" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>1369</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>1370</v>
       </c>
     </row>
     <row r="34" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>1371</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>1372</v>
       </c>
     </row>
     <row r="35" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>1373</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>1374</v>
       </c>
     </row>
     <row r="36" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B36" s="7" t="s">
         <v>1375</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>1376</v>
       </c>
     </row>
     <row r="37" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>1377</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>1378</v>
       </c>
     </row>
     <row r="38" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>1379</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>1380</v>
       </c>
     </row>
     <row r="39" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>724</v>
@@ -10103,111 +10100,111 @@
     </row>
     <row r="40" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B40" s="7" t="s">
         <v>1382</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>1383</v>
       </c>
     </row>
     <row r="41" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="42" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="43" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="44" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="45" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="46" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="47" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="48" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="49" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="50" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="51" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="52" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="53" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>699</v>
@@ -10215,7 +10212,7 @@
     </row>
     <row r="54" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>772</v>
@@ -10223,15 +10220,15 @@
     </row>
     <row r="55" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B55" s="7" t="s">
         <v>1398</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>1399</v>
       </c>
     </row>
     <row r="56" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>761</v>
@@ -10239,7 +10236,7 @@
     </row>
     <row r="57" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>761</v>
@@ -10247,55 +10244,55 @@
     </row>
     <row r="58" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B58" s="7" t="s">
         <v>1402</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="59" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B59" s="7" t="s">
         <v>1404</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>1405</v>
       </c>
     </row>
     <row r="60" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="61" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="62" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="63" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B63" s="7" t="s">
         <v>1409</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>1410</v>
       </c>
     </row>
     <row r="64" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>759</v>
@@ -10303,39 +10300,39 @@
     </row>
     <row r="65" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B65" s="7" t="s">
         <v>1412</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>1413</v>
       </c>
     </row>
     <row r="66" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="67" ht="62.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B67" s="7" t="s">
         <v>1415</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>1416</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B68" s="7" t="s">
         <v>1417</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>1418</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>885</v>
@@ -10362,16 +10359,16 @@
         <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>1420</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>1421</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>1422</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>1423</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -10385,10 +10382,10 @@
         <v>301</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>1424</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>1425</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -10444,13 +10441,13 @@
     </row>
     <row r="6" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B6" s="7">
         <v>1.6</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="D6" s="7">
         <v>0.01</v>
@@ -10459,13 +10456,13 @@
     </row>
     <row r="7" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B7" s="7">
         <v>20</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="D7" s="7">
         <v>0.01</v>
@@ -10474,13 +10471,13 @@
     </row>
     <row r="8" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="B8" s="7">
         <v>0.55</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="D8" s="7">
         <v>0.01</v>
@@ -10489,13 +10486,13 @@
     </row>
     <row r="9" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="B9" s="7">
         <v>0.32</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="D9" s="7">
         <v>0.001</v>
@@ -10504,13 +10501,13 @@
     </row>
     <row r="10" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B10" s="7">
         <v>6</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="D10" s="7">
         <v>0.01</v>
@@ -10519,13 +10516,13 @@
     </row>
     <row r="11" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B11" s="7">
         <v>8</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="D11" s="7">
         <v>0.01</v>
@@ -10534,13 +10531,13 @@
     </row>
     <row r="12" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="B12" s="7">
         <v>0.12</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="D12" s="7">
         <v>0</v>
@@ -10549,13 +10546,13 @@
     </row>
     <row r="13" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B13" s="7">
         <v>0.92</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="D13" s="7">
         <v>0.01</v>
@@ -10564,13 +10561,13 @@
     </row>
     <row r="14" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B14" s="7">
         <v>1.25</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="D14" s="7">
         <v>0.01</v>
@@ -10579,13 +10576,13 @@
     </row>
     <row r="15" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="B15" s="7">
         <v>1.7</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="D15" s="7">
         <v>0.01</v>
@@ -10594,13 +10591,13 @@
     </row>
     <row r="16" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="B16" s="7">
         <v>1.5</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="D16" s="7">
         <v>1</v>
@@ -10609,13 +10606,13 @@
     </row>
     <row r="17" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B17" s="7">
         <v>0.4</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="D17" s="7">
         <v>0.01</v>
@@ -10626,13 +10623,13 @@
     </row>
     <row r="18" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="B18" s="7">
         <v>5</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="D18" s="7">
         <v>0</v>
@@ -10641,13 +10638,13 @@
     </row>
     <row r="19" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="B19" s="7">
         <v>25</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="D19" s="7">
         <v>0.1</v>
@@ -10656,13 +10653,13 @@
     </row>
     <row r="20" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B20" s="7">
         <v>0.35</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="D20" s="7">
         <v>0</v>
@@ -10673,13 +10670,13 @@
     </row>
     <row r="21" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="B21" s="7">
         <v>0.3</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="D21" s="7">
         <v>0</v>
@@ -10690,13 +10687,13 @@
     </row>
     <row r="22" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B22" s="7">
         <v>0.55</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="D22" s="7">
         <v>0</v>
@@ -10707,13 +10704,13 @@
     </row>
     <row r="23" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="B23" s="7">
         <v>4</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="D23" s="7">
         <v>0</v>
@@ -10722,13 +10719,13 @@
     </row>
     <row r="24" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="B24" s="7">
         <v>2</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="D24" s="7">
         <v>0</v>
@@ -10737,13 +10734,13 @@
     </row>
     <row r="25" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="B25" s="7">
         <v>9</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="D25" s="7">
         <v>0</v>
@@ -10752,13 +10749,13 @@
     </row>
     <row r="26" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="B26" s="7">
         <v>4</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="D26" s="7">
         <v>0</v>
@@ -10767,13 +10764,13 @@
     </row>
     <row r="27" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="B27" s="7">
         <v>7</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="D27" s="7">
         <v>0</v>
@@ -10782,13 +10779,13 @@
     </row>
     <row r="28" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B28" s="7">
         <v>0.3</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="D28" s="7">
         <v>0</v>
@@ -10799,13 +10796,13 @@
     </row>
     <row r="29" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="B29" s="7">
         <v>0.2</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="D29" s="7">
         <v>0</v>
@@ -10814,13 +10811,13 @@
     </row>
     <row r="30" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B30" s="7">
         <v>12</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="D30" s="7">
         <v>1</v>
@@ -10831,13 +10828,13 @@
     </row>
     <row r="31" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="B31" s="7">
         <v>3</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="D31" s="7">
         <v>1</v>
@@ -10848,13 +10845,13 @@
     </row>
     <row r="32" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B32" s="7">
         <v>0.35</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="D32" s="7">
         <v>0</v>
@@ -10865,13 +10862,13 @@
     </row>
     <row r="33" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="B33" s="7">
         <v>0.5</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="D33" s="7">
         <v>0</v>
@@ -10882,13 +10879,13 @@
     </row>
     <row r="34" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="B34" s="7">
         <v>2</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="D34" s="7">
         <v>1</v>
@@ -10899,13 +10896,13 @@
     </row>
     <row r="35" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="B35" s="7">
         <v>4</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="D35" s="7">
         <v>1</v>
@@ -10916,13 +10913,13 @@
     </row>
     <row r="36" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B36" s="7">
         <v>1.5</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="D36" s="7">
         <v>0</v>
@@ -10931,13 +10928,13 @@
     </row>
     <row r="37" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="B37" s="7">
         <v>8</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="D37" s="7">
         <v>0.1</v>
@@ -10946,13 +10943,13 @@
     </row>
     <row r="38" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="B38" s="7">
         <v>4.5</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="D38" s="7">
         <v>0.1</v>
@@ -10961,13 +10958,13 @@
     </row>
     <row r="39" ht="62.1" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="B39" s="7">
         <v>6</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="D39" s="7">
         <v>0.1</v>
@@ -10996,22 +10993,22 @@
         <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>1494</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>1495</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>1496</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>1497</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>1498</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -11019,22 +11016,22 @@
         <v>87</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>1499</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>1500</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>1501</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>1502</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>1503</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -11129,10 +11126,10 @@
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C7" s="7" t="b">
         <v>0</v>
@@ -11171,10 +11168,10 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="C9" s="7" t="b">
         <v>0</v>
@@ -11192,10 +11189,10 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="C10" s="7" t="b">
         <v>0</v>
@@ -11309,7 +11306,7 @@
         <v>0.7</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="F15" s="7">
         <v>0.8</v>
@@ -11332,7 +11329,7 @@
         <v>0.7</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="F16" s="7">
         <v>0.8</v>
@@ -11357,10 +11354,10 @@
   <sheetData>
     <row r="1" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1504</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11368,7 +11365,7 @@
         <v>87</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11397,66 +11394,66 @@
     </row>
     <row r="6" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>1506</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>1507</v>
       </c>
     </row>
     <row r="7" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>1508</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>1509</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="10" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="11" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="12" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="13" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
     </row>
   </sheetData>
@@ -11476,16 +11473,16 @@
   <sheetData>
     <row r="1" ht="54" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>1517</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>1518</v>
       </c>
     </row>
     <row r="2" ht="38.1" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11493,13 +11490,13 @@
         <v>87</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>555</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11546,7 +11543,7 @@
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>123</v>
@@ -11555,12 +11552,12 @@
         <v>1</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>123</v>
@@ -11569,12 +11566,12 @@
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>123</v>
@@ -11583,7 +11580,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11597,7 +11594,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11611,12 +11608,12 @@
         <v>2</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>195</v>
@@ -11625,12 +11622,12 @@
         <v>3</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>197</v>
@@ -11639,12 +11636,12 @@
         <v>1</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>197</v>
@@ -11653,12 +11650,12 @@
         <v>2</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>197</v>
@@ -11667,7 +11664,7 @@
         <v>3</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11681,7 +11678,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11695,7 +11692,7 @@
         <v>2</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11709,12 +11706,12 @@
         <v>3</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>204</v>
@@ -11723,12 +11720,12 @@
         <v>1</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>204</v>
@@ -11737,12 +11734,12 @@
         <v>2</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>204</v>
@@ -11751,7 +11748,7 @@
         <v>3</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="21" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11765,7 +11762,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11779,7 +11776,7 @@
         <v>2</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11793,12 +11790,12 @@
         <v>3</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>211</v>
@@ -11807,12 +11804,12 @@
         <v>1</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>211</v>
@@ -11821,12 +11818,12 @@
         <v>2</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>211</v>
@@ -11835,7 +11832,7 @@
         <v>3</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="27" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11849,7 +11846,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="28" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11863,7 +11860,7 @@
         <v>2</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="29" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11877,12 +11874,12 @@
         <v>3</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="30" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>217</v>
@@ -11891,12 +11888,12 @@
         <v>1</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="31" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>217</v>
@@ -11905,12 +11902,12 @@
         <v>2</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="32" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>217</v>
@@ -11919,7 +11916,7 @@
         <v>3</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="33" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11933,7 +11930,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="34" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11947,7 +11944,7 @@
         <v>2</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="35" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11961,12 +11958,12 @@
         <v>3</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="36" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>223</v>
@@ -11975,12 +11972,12 @@
         <v>1</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="37" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>223</v>
@@ -11989,12 +11986,12 @@
         <v>2</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="38" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>223</v>
@@ -12003,12 +12000,12 @@
         <v>3</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="39" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>232</v>
@@ -12017,12 +12014,12 @@
         <v>1</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="40" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>232</v>
@@ -12031,12 +12028,12 @@
         <v>2</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="41" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>232</v>
@@ -12045,12 +12042,12 @@
         <v>3</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>236</v>
@@ -12059,12 +12056,12 @@
         <v>1</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="43" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>236</v>
@@ -12073,12 +12070,12 @@
         <v>2</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="44" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>236</v>
@@ -12087,12 +12084,12 @@
         <v>3</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="45" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>240</v>
@@ -12101,12 +12098,12 @@
         <v>1</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="46" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>240</v>
@@ -12115,12 +12112,12 @@
         <v>2</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="47" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>240</v>
@@ -12129,138 +12126,138 @@
         <v>3</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="48" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C48" s="7">
         <v>1</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="49" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C49" s="7">
         <v>2</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="50" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="C50" s="7">
         <v>3</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="51" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>1563</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>1564</v>
       </c>
       <c r="C51" s="7">
         <v>1</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="52" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="C52" s="7">
         <v>2</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="53" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="C53" s="7">
         <v>3</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="54" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B54" s="7" t="s">
         <v>1567</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>1568</v>
       </c>
       <c r="C54" s="7">
         <v>1</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="55" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="C55" s="7">
         <v>2</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="56" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="C56" s="7">
         <v>3</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="57" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>244</v>
@@ -12269,12 +12266,12 @@
         <v>1</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="58" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>244</v>
@@ -12283,12 +12280,12 @@
         <v>2</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="59" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>244</v>
@@ -12297,12 +12294,12 @@
         <v>3</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="60" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>248</v>
@@ -12311,12 +12308,12 @@
         <v>1</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="61" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>248</v>
@@ -12325,12 +12322,12 @@
         <v>2</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="62" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>248</v>
@@ -12339,12 +12336,12 @@
         <v>3</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="63" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>252</v>
@@ -12353,12 +12350,12 @@
         <v>1</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="64" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>252</v>
@@ -12367,12 +12364,12 @@
         <v>2</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="65" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>252</v>
@@ -12381,96 +12378,96 @@
         <v>3</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="66" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B66" s="7" t="s">
         <v>1580</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>1581</v>
       </c>
       <c r="C66" s="7">
         <v>1</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="67" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="C67" s="7">
         <v>2</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="68" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="C68" s="7">
         <v>3</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="69" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B69" s="7" t="s">
         <v>1584</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>1585</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="70" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="C70" s="7">
         <v>2</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="71" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="C71" s="7">
         <v>3</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="72" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>256</v>
@@ -12479,12 +12476,12 @@
         <v>1</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="73" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>256</v>
@@ -12493,12 +12490,12 @@
         <v>2</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="74" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>256</v>
@@ -12507,12 +12504,12 @@
         <v>3</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="75" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>260</v>
@@ -12521,12 +12518,12 @@
         <v>1</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="76" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>260</v>
@@ -12535,12 +12532,12 @@
         <v>2</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="77" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>260</v>
@@ -12549,12 +12546,12 @@
         <v>3</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="78" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>262</v>
@@ -12563,12 +12560,12 @@
         <v>1</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="79" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>262</v>
@@ -12577,12 +12574,12 @@
         <v>2</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="80" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>262</v>
@@ -12591,12 +12588,12 @@
         <v>3</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="81" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>264</v>
@@ -12605,12 +12602,12 @@
         <v>1</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="82" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>264</v>
@@ -12619,12 +12616,12 @@
         <v>2</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="83" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>264</v>
@@ -12633,54 +12630,54 @@
         <v>3</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="84" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B84" s="7" t="s">
         <v>1600</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>1601</v>
       </c>
       <c r="C84" s="7">
         <v>1</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="85" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="C85" s="7">
         <v>2</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="86" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="C86" s="7">
         <v>3</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="87" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>268</v>
@@ -12689,12 +12686,12 @@
         <v>1</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="88" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>268</v>
@@ -12703,12 +12700,12 @@
         <v>2</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="89" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>268</v>
@@ -12717,12 +12714,12 @@
         <v>3</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="90" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>272</v>
@@ -12731,12 +12728,12 @@
         <v>1</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="91" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>272</v>
@@ -12745,12 +12742,12 @@
         <v>2</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="92" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>272</v>
@@ -12759,12 +12756,12 @@
         <v>3</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="93" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>274</v>
@@ -12773,12 +12770,12 @@
         <v>1</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="94" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>274</v>
@@ -12787,12 +12784,12 @@
         <v>2</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="95" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>274</v>
@@ -12801,12 +12798,12 @@
         <v>3</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="96" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>276</v>
@@ -12815,12 +12812,12 @@
         <v>1</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="97" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>276</v>
@@ -12829,12 +12826,12 @@
         <v>2</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="98" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>276</v>
@@ -12843,54 +12840,54 @@
         <v>3</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="99" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B99" s="7" t="s">
         <v>1616</v>
-      </c>
-      <c r="B99" s="7" t="s">
-        <v>1617</v>
       </c>
       <c r="C99" s="7">
         <v>1</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="100" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="C100" s="7">
         <v>2</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="101" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="C101" s="7">
         <v>3</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="102" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="B102" s="7" t="s">
         <v>280</v>
@@ -12899,12 +12896,12 @@
         <v>1</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="103" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="B103" s="7" t="s">
         <v>280</v>
@@ -12913,12 +12910,12 @@
         <v>2</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="104" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>280</v>
@@ -12927,12 +12924,12 @@
         <v>3</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="105" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>284</v>
@@ -12941,12 +12938,12 @@
         <v>1</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="106" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>284</v>
@@ -12955,12 +12952,12 @@
         <v>2</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="107" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>284</v>
@@ -12969,12 +12966,12 @@
         <v>3</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="108" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>286</v>
@@ -12983,12 +12980,12 @@
         <v>1</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="109" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>286</v>
@@ -12997,12 +12994,12 @@
         <v>2</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="110" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>286</v>
@@ -13011,12 +13008,12 @@
         <v>3</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="111" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>288</v>
@@ -13025,12 +13022,12 @@
         <v>1</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="112" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>288</v>
@@ -13039,12 +13036,12 @@
         <v>2</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="113" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>288</v>
@@ -13053,12 +13050,12 @@
         <v>3</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="114" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>290</v>
@@ -13067,12 +13064,12 @@
         <v>1</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="115" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>290</v>
@@ -13081,12 +13078,12 @@
         <v>2</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="116" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>290</v>
@@ -13095,7 +13092,7 @@
         <v>3</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
   </sheetData>
@@ -14138,7 +14135,7 @@
         <v>233</v>
       </c>
       <c r="F6" s="7">
-        <v>50</v>
+        <v>168</v>
       </c>
       <c r="G6" s="7">
         <v>0</v>
@@ -14147,7 +14144,7 @@
         <v>909</v>
       </c>
       <c r="I6" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="7"/>
     </row>
@@ -14159,25 +14156,25 @@
         <v>1</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>237</v>
+        <v>141</v>
       </c>
       <c r="F7" s="7">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G7" s="7">
         <v>0</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="I7" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="7"/>
     </row>
@@ -14186,25 +14183,25 @@
         <v>3</v>
       </c>
       <c r="B8" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>141</v>
+        <v>241</v>
       </c>
       <c r="F8" s="7">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="G8" s="7">
         <v>0</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="I8" s="7" t="b">
         <v>0</v>
@@ -14225,10 +14222,10 @@
         <v>914</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F9" s="7">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G9" s="7">
         <v>0</v>
@@ -14237,7 +14234,7 @@
         <v>909</v>
       </c>
       <c r="I9" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="7"/>
     </row>
@@ -14249,73 +14246,91 @@
         <v>2</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>915</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>245</v>
+        <v>146</v>
       </c>
       <c r="F10" s="7">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G10" s="7">
         <v>0</v>
       </c>
       <c r="H10" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="I10" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="7"/>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>6</v>
+      </c>
+      <c r="B11" s="7">
+        <v>3</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>907</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>916</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F11" s="7">
+        <v>50</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>909</v>
       </c>
-      <c r="I10" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" s="7"/>
-    </row>
-    <row r="11" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
+      <c r="I11" s="7" t="b">
+        <v>0</v>
+      </c>
       <c r="J11" s="7"/>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>146</v>
+        <v>257</v>
       </c>
       <c r="F12" s="7">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="G12" s="7">
         <v>0</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="I12" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="7"/>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" s="7">
         <v>3</v>
@@ -14324,13 +14339,13 @@
         <v>907</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="F13" s="7">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G13" s="7">
         <v>0</v>
@@ -14345,52 +14360,52 @@
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" s="7">
         <v>3</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>257</v>
+        <v>151</v>
       </c>
       <c r="F14" s="7">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="G14" s="7">
         <v>0</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="I14" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" s="7"/>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B15" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>907</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F15" s="7">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="G15" s="7">
         <v>0</v>
@@ -14404,41 +14419,59 @@
       <c r="J15" s="7"/>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
+      <c r="A16" s="7">
+        <v>11</v>
+      </c>
+      <c r="B16" s="7">
+        <v>4</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>907</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>921</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="F16" s="7">
+        <v>60</v>
+      </c>
+      <c r="G16" s="7">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>909</v>
+      </c>
+      <c r="I16" s="7" t="b">
+        <v>1</v>
+      </c>
       <c r="J16" s="7"/>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B17" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>151</v>
+        <v>273</v>
       </c>
       <c r="F17" s="7">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="G17" s="7">
         <v>0</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="I17" s="7" t="b">
         <v>0</v>
@@ -14447,28 +14480,28 @@
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B18" s="7">
         <v>4</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>265</v>
+        <v>156</v>
       </c>
       <c r="F18" s="7">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="G18" s="7">
         <v>0</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="I18" s="7" t="b">
         <v>0</v>
@@ -14477,22 +14510,22 @@
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B19" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>907</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F19" s="7">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G19" s="7">
         <v>0</v>
@@ -14501,28 +14534,28 @@
         <v>909</v>
       </c>
       <c r="I19" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="7"/>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B20" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>907</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="F20" s="7">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G20" s="7">
         <v>0</v>
@@ -14531,46 +14564,64 @@
         <v>909</v>
       </c>
       <c r="I20" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="7"/>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
+      <c r="A21" s="7">
+        <v>16</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>907</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>926</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="F21" s="7">
+        <v>70</v>
+      </c>
+      <c r="G21" s="7">
+        <v>0</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>909</v>
+      </c>
+      <c r="I21" s="7" t="b">
+        <v>0</v>
+      </c>
       <c r="J21" s="7"/>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B22" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>156</v>
+        <v>287</v>
       </c>
       <c r="F22" s="7">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="G22" s="7">
         <v>0</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="I22" s="7" t="b">
         <v>0</v>
@@ -14579,7 +14630,7 @@
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B23" s="7">
         <v>5</v>
@@ -14588,13 +14639,13 @@
         <v>907</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="F23" s="7">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="G23" s="7">
         <v>0</v>
@@ -14603,189 +14654,117 @@
         <v>909</v>
       </c>
       <c r="I23" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="7"/>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B24" s="7">
         <v>5</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>281</v>
+        <v>161</v>
       </c>
       <c r="F24" s="7">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="G24" s="7">
         <v>0</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="I24" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="7"/>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B25" s="7">
         <v>5</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>285</v>
+        <v>224</v>
       </c>
       <c r="F25" s="7">
-        <v>70</v>
+        <v>99999</v>
       </c>
       <c r="G25" s="7">
         <v>0</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>909</v>
-      </c>
-      <c r="I25" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J25" s="7"/>
+        <v>931</v>
+      </c>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7" t="s">
+        <v>910</v>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
-        <v>18</v>
-      </c>
-      <c r="B26" s="7">
-        <v>5</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>907</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>928</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="F26" s="7">
-        <v>80</v>
-      </c>
-      <c r="G26" s="7">
-        <v>0</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>909</v>
-      </c>
-      <c r="I26" s="7" t="b">
-        <v>0</v>
-      </c>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
       <c r="J26" s="7"/>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
-        <v>19</v>
-      </c>
-      <c r="B27" s="7">
-        <v>5</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>907</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>929</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="F27" s="7">
-        <v>90</v>
-      </c>
-      <c r="G27" s="7">
-        <v>0</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>909</v>
-      </c>
-      <c r="I27" s="7" t="b">
-        <v>1</v>
-      </c>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
       <c r="J27" s="7"/>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
-        <v>20</v>
-      </c>
-      <c r="B28" s="7">
-        <v>5</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>930</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="F28" s="7">
-        <v>180</v>
-      </c>
-      <c r="G28" s="7">
-        <v>0</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>913</v>
-      </c>
-      <c r="I28" s="7" t="b">
-        <v>0</v>
-      </c>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
       <c r="J28" s="7"/>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
-        <v>21</v>
-      </c>
-      <c r="B29" s="7">
-        <v>5</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>931</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="F29" s="7">
-        <v>99999</v>
-      </c>
-      <c r="G29" s="7">
-        <v>0</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>932</v>
-      </c>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
       <c r="I29" s="7"/>
-      <c r="J29" s="7" t="s">
-        <v>911</v>
-      </c>
+      <c r="J29" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/斗鸡配置.xlsx
+++ b/excel/斗鸡配置.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3297" uniqueCount="1674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3301" uniqueCount="1678">
   <si>
     <t>斗鸡配置</t>
   </si>
@@ -4639,6 +4639,18 @@
   </si>
   <si>
     <t>普通弹幕间隔（秒）</t>
+  </si>
+  <si>
+    <t>battle_bossSkillCooldown</t>
+  </si>
+  <si>
+    <t>Boss绝招冷却（秒，不跟战斗时长缩放）</t>
+  </si>
+  <si>
+    <t>battle_bossSkillMapLimit</t>
+  </si>
+  <si>
+    <t>Boss绝招是否受玩家地图解锁限制：0不限制（全技能），1仅本图已解锁</t>
   </si>
   <si>
     <t>允许重复</t>
@@ -10255,7 +10267,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
@@ -10856,6 +10868,37 @@
       </c>
       <c r="D39">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D40">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -10883,19 +10926,19 @@
         <v>971</v>
       </c>
       <c r="C1" t="s">
-        <v>1534</v>
+        <v>1538</v>
       </c>
       <c r="D1" t="s">
-        <v>1535</v>
+        <v>1539</v>
       </c>
       <c r="E1" t="s">
-        <v>1536</v>
+        <v>1540</v>
       </c>
       <c r="F1" t="s">
-        <v>1537</v>
+        <v>1541</v>
       </c>
       <c r="G1" t="s">
-        <v>1538</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="2" ht="38.15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10906,19 +10949,19 @@
         <v>973</v>
       </c>
       <c r="C2" t="s">
-        <v>1539</v>
+        <v>1543</v>
       </c>
       <c r="D2" t="s">
-        <v>1540</v>
+        <v>1544</v>
       </c>
       <c r="E2" t="s">
-        <v>1541</v>
+        <v>1545</v>
       </c>
       <c r="F2" t="s">
-        <v>1542</v>
+        <v>1546</v>
       </c>
       <c r="G2" t="s">
-        <v>1543</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -11232,10 +11275,10 @@
   <sheetData>
     <row r="1" ht="54" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1544</v>
+        <v>1548</v>
       </c>
       <c r="B1" t="s">
-        <v>1545</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="2" ht="38.15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11272,18 +11315,18 @@
     </row>
     <row r="6" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1546</v>
+        <v>1550</v>
       </c>
       <c r="B6" t="s">
-        <v>1547</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="7" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1548</v>
+        <v>1552</v>
       </c>
       <c r="B7" t="s">
-        <v>1549</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11299,7 +11342,7 @@
         <v>1351</v>
       </c>
       <c r="B9" t="s">
-        <v>1550</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="10" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11307,7 +11350,7 @@
         <v>1353</v>
       </c>
       <c r="B10" t="s">
-        <v>1551</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="11" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11315,7 +11358,7 @@
         <v>1355</v>
       </c>
       <c r="B11" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="12" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11323,7 +11366,7 @@
         <v>1357</v>
       </c>
       <c r="B12" t="s">
-        <v>1553</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="13" ht="90" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -11331,7 +11374,7 @@
         <v>1359</v>
       </c>
       <c r="B13" t="s">
-        <v>1554</v>
+        <v>1558</v>
       </c>
     </row>
   </sheetData>
@@ -11351,16 +11394,16 @@
   <sheetData>
     <row r="1" ht="54" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1555</v>
+        <v>1559</v>
       </c>
       <c r="B1" t="s">
         <v>86</v>
       </c>
       <c r="C1" t="s">
-        <v>1556</v>
+        <v>1560</v>
       </c>
       <c r="D1" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="2" ht="38.15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11421,7 +11464,7 @@
     </row>
     <row r="6" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="B6" t="s">
         <v>123</v>
@@ -11430,12 +11473,12 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>1559</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1560</v>
+        <v>1564</v>
       </c>
       <c r="B7" t="s">
         <v>123</v>
@@ -11444,12 +11487,12 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="B8" t="s">
         <v>123</v>
@@ -11458,7 +11501,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11472,7 +11515,7 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11486,12 +11529,12 @@
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
       <c r="B11" t="s">
         <v>195</v>
@@ -11500,12 +11543,12 @@
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="B12" t="s">
         <v>197</v>
@@ -11514,12 +11557,12 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>1569</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1570</v>
+        <v>1574</v>
       </c>
       <c r="B13" t="s">
         <v>197</v>
@@ -11533,7 +11576,7 @@
     </row>
     <row r="14" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1571</v>
+        <v>1575</v>
       </c>
       <c r="B14" t="s">
         <v>197</v>
@@ -11556,7 +11599,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11570,7 +11613,7 @@
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11584,12 +11627,12 @@
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="18" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1572</v>
+        <v>1576</v>
       </c>
       <c r="B18" t="s">
         <v>204</v>
@@ -11598,12 +11641,12 @@
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>1573</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="19" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
       <c r="B19" t="s">
         <v>204</v>
@@ -11617,7 +11660,7 @@
     </row>
     <row r="20" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1575</v>
+        <v>1579</v>
       </c>
       <c r="B20" t="s">
         <v>204</v>
@@ -11640,7 +11683,7 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="22" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11654,7 +11697,7 @@
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11668,12 +11711,12 @@
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="24" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="B24" t="s">
         <v>211</v>
@@ -11682,12 +11725,12 @@
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="25" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="B25" t="s">
         <v>211</v>
@@ -11701,7 +11744,7 @@
     </row>
     <row r="26" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="B26" t="s">
         <v>211</v>
@@ -11724,7 +11767,7 @@
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="28" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11738,7 +11781,7 @@
         <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="29" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11752,12 +11795,12 @@
         <v>3</v>
       </c>
       <c r="D29" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="30" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>1580</v>
+        <v>1584</v>
       </c>
       <c r="B30" t="s">
         <v>217</v>
@@ -11766,12 +11809,12 @@
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>1581</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="31" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="B31" t="s">
         <v>217</v>
@@ -11785,7 +11828,7 @@
     </row>
     <row r="32" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1583</v>
+        <v>1587</v>
       </c>
       <c r="B32" t="s">
         <v>217</v>
@@ -11808,7 +11851,7 @@
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="34" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11822,7 +11865,7 @@
         <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="35" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -11836,12 +11879,12 @@
         <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="36" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1584</v>
+        <v>1588</v>
       </c>
       <c r="B36" t="s">
         <v>223</v>
@@ -11850,12 +11893,12 @@
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>1585</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="37" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>1586</v>
+        <v>1590</v>
       </c>
       <c r="B37" t="s">
         <v>223</v>
@@ -11869,7 +11912,7 @@
     </row>
     <row r="38" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>1587</v>
+        <v>1591</v>
       </c>
       <c r="B38" t="s">
         <v>223</v>
@@ -11883,7 +11926,7 @@
     </row>
     <row r="39" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1588</v>
+        <v>1592</v>
       </c>
       <c r="B39" t="s">
         <v>232</v>
@@ -11897,7 +11940,7 @@
     </row>
     <row r="40" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1589</v>
+        <v>1593</v>
       </c>
       <c r="B40" t="s">
         <v>232</v>
@@ -11906,12 +11949,12 @@
         <v>2</v>
       </c>
       <c r="D40" t="s">
-        <v>1590</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="41" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1591</v>
+        <v>1595</v>
       </c>
       <c r="B41" t="s">
         <v>232</v>
@@ -11920,12 +11963,12 @@
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>1592</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1593</v>
+        <v>1597</v>
       </c>
       <c r="B42" t="s">
         <v>236</v>
@@ -11934,12 +11977,12 @@
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="43" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1594</v>
+        <v>1598</v>
       </c>
       <c r="B43" t="s">
         <v>236</v>
@@ -11948,12 +11991,12 @@
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="44" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1595</v>
+        <v>1599</v>
       </c>
       <c r="B44" t="s">
         <v>236</v>
@@ -11962,12 +12005,12 @@
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="45" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1596</v>
+        <v>1600</v>
       </c>
       <c r="B45" t="s">
         <v>240</v>
@@ -11976,12 +12019,12 @@
         <v>1</v>
       </c>
       <c r="D45" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="46" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1597</v>
+        <v>1601</v>
       </c>
       <c r="B46" t="s">
         <v>240</v>
@@ -11990,12 +12033,12 @@
         <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="47" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1598</v>
+        <v>1602</v>
       </c>
       <c r="B47" t="s">
         <v>240</v>
@@ -12004,138 +12047,138 @@
         <v>3</v>
       </c>
       <c r="D47" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="48" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1599</v>
+        <v>1603</v>
       </c>
       <c r="B48" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
       <c r="C48">
         <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="49" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1600</v>
+        <v>1604</v>
       </c>
       <c r="B49" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
       <c r="C49">
         <v>2</v>
       </c>
       <c r="D49" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="50" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1601</v>
+        <v>1605</v>
       </c>
       <c r="B50" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
       <c r="C50">
         <v>3</v>
       </c>
       <c r="D50" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="51" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1602</v>
+        <v>1606</v>
       </c>
       <c r="B51" t="s">
-        <v>1603</v>
+        <v>1607</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="52" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1604</v>
+        <v>1608</v>
       </c>
       <c r="B52" t="s">
-        <v>1603</v>
+        <v>1607</v>
       </c>
       <c r="C52">
         <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="53" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1605</v>
+        <v>1609</v>
       </c>
       <c r="B53" t="s">
-        <v>1603</v>
+        <v>1607</v>
       </c>
       <c r="C53">
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="54" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1606</v>
+        <v>1610</v>
       </c>
       <c r="B54" t="s">
-        <v>1607</v>
+        <v>1611</v>
       </c>
       <c r="C54">
         <v>1</v>
       </c>
       <c r="D54" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="55" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="B55" t="s">
-        <v>1607</v>
+        <v>1611</v>
       </c>
       <c r="C55">
         <v>2</v>
       </c>
       <c r="D55" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="56" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>1609</v>
+        <v>1613</v>
       </c>
       <c r="B56" t="s">
-        <v>1607</v>
+        <v>1611</v>
       </c>
       <c r="C56">
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="57" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="B57" t="s">
         <v>244</v>
@@ -12144,12 +12187,12 @@
         <v>1</v>
       </c>
       <c r="D57" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="58" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1611</v>
+        <v>1615</v>
       </c>
       <c r="B58" t="s">
         <v>244</v>
@@ -12158,12 +12201,12 @@
         <v>2</v>
       </c>
       <c r="D58" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="59" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1612</v>
+        <v>1616</v>
       </c>
       <c r="B59" t="s">
         <v>244</v>
@@ -12172,12 +12215,12 @@
         <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="60" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1613</v>
+        <v>1617</v>
       </c>
       <c r="B60" t="s">
         <v>248</v>
@@ -12186,12 +12229,12 @@
         <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="61" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1614</v>
+        <v>1618</v>
       </c>
       <c r="B61" t="s">
         <v>248</v>
@@ -12200,12 +12243,12 @@
         <v>2</v>
       </c>
       <c r="D61" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="62" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="B62" t="s">
         <v>248</v>
@@ -12214,12 +12257,12 @@
         <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="63" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="B63" t="s">
         <v>252</v>
@@ -12228,12 +12271,12 @@
         <v>1</v>
       </c>
       <c r="D63" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="64" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="B64" t="s">
         <v>252</v>
@@ -12242,12 +12285,12 @@
         <v>2</v>
       </c>
       <c r="D64" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="65" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1618</v>
+        <v>1622</v>
       </c>
       <c r="B65" t="s">
         <v>252</v>
@@ -12256,96 +12299,96 @@
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="66" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1619</v>
+        <v>1623</v>
       </c>
       <c r="B66" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="C66">
         <v>1</v>
       </c>
       <c r="D66" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="67" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1621</v>
+        <v>1625</v>
       </c>
       <c r="B67" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="C67">
         <v>2</v>
       </c>
       <c r="D67" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="68" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1622</v>
+        <v>1626</v>
       </c>
       <c r="B68" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="C68">
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="69" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1623</v>
+        <v>1627</v>
       </c>
       <c r="B69" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
       <c r="C69">
         <v>1</v>
       </c>
       <c r="D69" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="70" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1625</v>
+        <v>1629</v>
       </c>
       <c r="B70" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
       <c r="C70">
         <v>2</v>
       </c>
       <c r="D70" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="71" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1626</v>
+        <v>1630</v>
       </c>
       <c r="B71" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
       <c r="C71">
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="72" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="B72" t="s">
         <v>256</v>
@@ -12354,12 +12397,12 @@
         <v>1</v>
       </c>
       <c r="D72" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="73" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
       <c r="B73" t="s">
         <v>256</v>
@@ -12368,12 +12411,12 @@
         <v>2</v>
       </c>
       <c r="D73" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="74" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1629</v>
+        <v>1633</v>
       </c>
       <c r="B74" t="s">
         <v>256</v>
@@ -12382,12 +12425,12 @@
         <v>3</v>
       </c>
       <c r="D74" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="75" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>1630</v>
+        <v>1634</v>
       </c>
       <c r="B75" t="s">
         <v>260</v>
@@ -12396,12 +12439,12 @@
         <v>1</v>
       </c>
       <c r="D75" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="76" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="B76" t="s">
         <v>260</v>
@@ -12410,12 +12453,12 @@
         <v>2</v>
       </c>
       <c r="D76" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="77" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="B77" t="s">
         <v>260</v>
@@ -12424,12 +12467,12 @@
         <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="78" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>1633</v>
+        <v>1637</v>
       </c>
       <c r="B78" t="s">
         <v>262</v>
@@ -12438,12 +12481,12 @@
         <v>1</v>
       </c>
       <c r="D78" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="79" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>1634</v>
+        <v>1638</v>
       </c>
       <c r="B79" t="s">
         <v>262</v>
@@ -12452,12 +12495,12 @@
         <v>2</v>
       </c>
       <c r="D79" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="80" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>1635</v>
+        <v>1639</v>
       </c>
       <c r="B80" t="s">
         <v>262</v>
@@ -12466,12 +12509,12 @@
         <v>3</v>
       </c>
       <c r="D80" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="81" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>1636</v>
+        <v>1640</v>
       </c>
       <c r="B81" t="s">
         <v>264</v>
@@ -12480,12 +12523,12 @@
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="82" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
       <c r="B82" t="s">
         <v>264</v>
@@ -12494,12 +12537,12 @@
         <v>2</v>
       </c>
       <c r="D82" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="83" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>1638</v>
+        <v>1642</v>
       </c>
       <c r="B83" t="s">
         <v>264</v>
@@ -12508,54 +12551,54 @@
         <v>3</v>
       </c>
       <c r="D83" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="84" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>1639</v>
+        <v>1643</v>
       </c>
       <c r="B84" t="s">
-        <v>1640</v>
+        <v>1644</v>
       </c>
       <c r="C84">
         <v>1</v>
       </c>
       <c r="D84" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="85" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>1641</v>
+        <v>1645</v>
       </c>
       <c r="B85" t="s">
-        <v>1640</v>
+        <v>1644</v>
       </c>
       <c r="C85">
         <v>2</v>
       </c>
       <c r="D85" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="86" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="B86" t="s">
-        <v>1640</v>
+        <v>1644</v>
       </c>
       <c r="C86">
         <v>3</v>
       </c>
       <c r="D86" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="87" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1643</v>
+        <v>1647</v>
       </c>
       <c r="B87" t="s">
         <v>268</v>
@@ -12564,12 +12607,12 @@
         <v>1</v>
       </c>
       <c r="D87" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="88" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1644</v>
+        <v>1648</v>
       </c>
       <c r="B88" t="s">
         <v>268</v>
@@ -12578,12 +12621,12 @@
         <v>2</v>
       </c>
       <c r="D88" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="89" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1645</v>
+        <v>1649</v>
       </c>
       <c r="B89" t="s">
         <v>268</v>
@@ -12592,12 +12635,12 @@
         <v>3</v>
       </c>
       <c r="D89" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="90" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1646</v>
+        <v>1650</v>
       </c>
       <c r="B90" t="s">
         <v>272</v>
@@ -12606,12 +12649,12 @@
         <v>1</v>
       </c>
       <c r="D90" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="91" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1647</v>
+        <v>1651</v>
       </c>
       <c r="B91" t="s">
         <v>272</v>
@@ -12620,12 +12663,12 @@
         <v>2</v>
       </c>
       <c r="D91" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="92" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1648</v>
+        <v>1652</v>
       </c>
       <c r="B92" t="s">
         <v>272</v>
@@ -12634,12 +12677,12 @@
         <v>3</v>
       </c>
       <c r="D92" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="93" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1649</v>
+        <v>1653</v>
       </c>
       <c r="B93" t="s">
         <v>274</v>
@@ -12648,12 +12691,12 @@
         <v>1</v>
       </c>
       <c r="D93" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="94" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1650</v>
+        <v>1654</v>
       </c>
       <c r="B94" t="s">
         <v>274</v>
@@ -12662,12 +12705,12 @@
         <v>2</v>
       </c>
       <c r="D94" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="95" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1651</v>
+        <v>1655</v>
       </c>
       <c r="B95" t="s">
         <v>274</v>
@@ -12676,12 +12719,12 @@
         <v>3</v>
       </c>
       <c r="D95" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="96" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1652</v>
+        <v>1656</v>
       </c>
       <c r="B96" t="s">
         <v>276</v>
@@ -12690,12 +12733,12 @@
         <v>1</v>
       </c>
       <c r="D96" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="97" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1653</v>
+        <v>1657</v>
       </c>
       <c r="B97" t="s">
         <v>276</v>
@@ -12704,12 +12747,12 @@
         <v>2</v>
       </c>
       <c r="D97" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="98" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1654</v>
+        <v>1658</v>
       </c>
       <c r="B98" t="s">
         <v>276</v>
@@ -12718,54 +12761,54 @@
         <v>3</v>
       </c>
       <c r="D98" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="99" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>1655</v>
+        <v>1659</v>
       </c>
       <c r="B99" t="s">
-        <v>1656</v>
+        <v>1660</v>
       </c>
       <c r="C99">
         <v>1</v>
       </c>
       <c r="D99" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="100" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1657</v>
+        <v>1661</v>
       </c>
       <c r="B100" t="s">
-        <v>1656</v>
+        <v>1660</v>
       </c>
       <c r="C100">
         <v>2</v>
       </c>
       <c r="D100" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="101" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1658</v>
+        <v>1662</v>
       </c>
       <c r="B101" t="s">
-        <v>1656</v>
+        <v>1660</v>
       </c>
       <c r="C101">
         <v>3</v>
       </c>
       <c r="D101" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="102" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="B102" t="s">
         <v>280</v>
@@ -12774,12 +12817,12 @@
         <v>1</v>
       </c>
       <c r="D102" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="103" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1660</v>
+        <v>1664</v>
       </c>
       <c r="B103" t="s">
         <v>280</v>
@@ -12788,12 +12831,12 @@
         <v>2</v>
       </c>
       <c r="D103" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="104" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1661</v>
+        <v>1665</v>
       </c>
       <c r="B104" t="s">
         <v>280</v>
@@ -12802,12 +12845,12 @@
         <v>3</v>
       </c>
       <c r="D104" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="105" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1662</v>
+        <v>1666</v>
       </c>
       <c r="B105" t="s">
         <v>284</v>
@@ -12816,12 +12859,12 @@
         <v>1</v>
       </c>
       <c r="D105" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="106" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1663</v>
+        <v>1667</v>
       </c>
       <c r="B106" t="s">
         <v>284</v>
@@ -12830,12 +12873,12 @@
         <v>2</v>
       </c>
       <c r="D106" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="107" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1664</v>
+        <v>1668</v>
       </c>
       <c r="B107" t="s">
         <v>284</v>
@@ -12844,12 +12887,12 @@
         <v>3</v>
       </c>
       <c r="D107" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="108" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1665</v>
+        <v>1669</v>
       </c>
       <c r="B108" t="s">
         <v>286</v>
@@ -12858,12 +12901,12 @@
         <v>1</v>
       </c>
       <c r="D108" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="109" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1666</v>
+        <v>1670</v>
       </c>
       <c r="B109" t="s">
         <v>286</v>
@@ -12872,12 +12915,12 @@
         <v>2</v>
       </c>
       <c r="D109" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="110" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1667</v>
+        <v>1671</v>
       </c>
       <c r="B110" t="s">
         <v>286</v>
@@ -12886,12 +12929,12 @@
         <v>3</v>
       </c>
       <c r="D110" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="111" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1668</v>
+        <v>1672</v>
       </c>
       <c r="B111" t="s">
         <v>288</v>
@@ -12900,12 +12943,12 @@
         <v>1</v>
       </c>
       <c r="D111" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="112" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1669</v>
+        <v>1673</v>
       </c>
       <c r="B112" t="s">
         <v>288</v>
@@ -12914,12 +12957,12 @@
         <v>2</v>
       </c>
       <c r="D112" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="113" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1670</v>
+        <v>1674</v>
       </c>
       <c r="B113" t="s">
         <v>288</v>
@@ -12928,12 +12971,12 @@
         <v>3</v>
       </c>
       <c r="D113" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="114" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1671</v>
+        <v>1675</v>
       </c>
       <c r="B114" t="s">
         <v>290</v>
@@ -12942,12 +12985,12 @@
         <v>1</v>
       </c>
       <c r="D114" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="115" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1672</v>
+        <v>1676</v>
       </c>
       <c r="B115" t="s">
         <v>290</v>
@@ -12956,12 +12999,12 @@
         <v>2</v>
       </c>
       <c r="D115" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="116" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>1673</v>
+        <v>1677</v>
       </c>
       <c r="B116" t="s">
         <v>290</v>
@@ -12970,7 +13013,7 @@
         <v>3</v>
       </c>
       <c r="D116" t="s">
-        <v>1567</v>
+        <v>1571</v>
       </c>
     </row>
   </sheetData>

--- a/excel/斗鸡配置.xlsx
+++ b/excel/斗鸡配置.xlsx
@@ -10889,7 +10889,7 @@
         <v>1536</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" t="s">
         <v>1537</v>
